--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -1892,19 +1892,19 @@
         <v>112</v>
       </c>
       <c r="D33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>23</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" s="1">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="H33" s="1">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="I33" s="2">
         <v>6.3</v>
@@ -1927,19 +1927,19 @@
         <v>113</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I34" s="2">
         <v>6.7</v>
@@ -1997,7 +1997,7 @@
         <v>115</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -2006,19 +2006,19 @@
         <v>6</v>
       </c>
       <c r="G36" s="1">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="H36" s="1">
-        <v>33.3</v>
+        <v>31.6</v>
       </c>
       <c r="I36" s="2">
         <v>6.6</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2029,28 +2029,28 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E37">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F37">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37" s="1">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="H37" s="1">
-        <v>44.1</v>
+        <v>43.8</v>
       </c>
       <c r="I37" s="2">
         <v>6.3</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2580,19 +2580,19 @@
         <v>122</v>
       </c>
       <c r="D53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G53" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="H53" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="I53" s="2">
         <v>6</v>
@@ -2615,22 +2615,22 @@
         <v>122</v>
       </c>
       <c r="D54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
       <c r="G54" s="1">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H54" s="1">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I54" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -2650,19 +2650,19 @@
         <v>123</v>
       </c>
       <c r="D55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E55">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F55">
         <v>21</v>
       </c>
       <c r="G55" s="1">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="H55" s="1">
-        <v>53.8</v>
+        <v>52.5</v>
       </c>
       <c r="I55" s="2">
         <v>5.9</v>
@@ -2752,19 +2752,19 @@
         <v>100</v>
       </c>
       <c r="D58">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E58">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F58">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G58" s="1">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="H58" s="1">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="I58" s="2">
         <v>6.1</v>
@@ -2924,22 +2924,22 @@
         <v>122</v>
       </c>
       <c r="D63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E63">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H63" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I63" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -2959,22 +2959,22 @@
         <v>123</v>
       </c>
       <c r="D64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E64">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F64">
         <v>3</v>
       </c>
       <c r="G64" s="1">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="H64" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I64" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -3029,19 +3029,19 @@
         <v>112</v>
       </c>
       <c r="D66">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E66">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F66">
         <v>12</v>
       </c>
       <c r="G66" s="1">
-        <v>69.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H66" s="1">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="I66" s="2">
         <v>6.3</v>
@@ -3166,10 +3166,10 @@
         <v>100</v>
       </c>
       <c r="D70">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E70">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F70">
         <v>29</v>
@@ -3548,19 +3548,19 @@
         <v>112</v>
       </c>
       <c r="D81">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E81">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F81">
         <v>11</v>
       </c>
       <c r="G81" s="1">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H81" s="1">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="I81" s="2">
         <v>5.8</v>
@@ -3583,19 +3583,19 @@
         <v>113</v>
       </c>
       <c r="D82">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F82">
         <v>7</v>
       </c>
       <c r="G82" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H82" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I82" s="2">
         <v>6.5</v>
@@ -3653,7 +3653,7 @@
         <v>115</v>
       </c>
       <c r="D84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E84">
         <v>9</v>
@@ -3662,19 +3662,19 @@
         <v>9</v>
       </c>
       <c r="G84" s="1">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="H84" s="1">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="I84" s="2">
         <v>5.6</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3685,28 +3685,28 @@
         <v>100</v>
       </c>
       <c r="D85">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E85">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F85">
         <v>48</v>
       </c>
       <c r="G85" s="1">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="H85" s="1">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="I85" s="2">
         <v>5.9</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4445,19 +4445,19 @@
         <v>112</v>
       </c>
       <c r="D108">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E108">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F108">
         <v>18</v>
       </c>
       <c r="G108" s="1">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="H108" s="1">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I108" s="2">
         <v>6.4</v>
@@ -4547,19 +4547,19 @@
         <v>100</v>
       </c>
       <c r="D111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E111">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F111">
         <v>25</v>
       </c>
       <c r="G111" s="1">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="H111" s="1">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="I111" s="2">
         <v>7.8</v>
@@ -4652,19 +4652,19 @@
         <v>122</v>
       </c>
       <c r="D114">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E114">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F114">
         <v>9</v>
       </c>
       <c r="G114" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H114" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I114" s="2">
         <v>6.3</v>
@@ -4687,19 +4687,19 @@
         <v>123</v>
       </c>
       <c r="D115">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E115">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F115">
         <v>9</v>
       </c>
       <c r="G115" s="1">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="H115" s="1">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="I115" s="2">
         <v>6.3</v>
@@ -4789,19 +4789,19 @@
         <v>100</v>
       </c>
       <c r="D118">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E118">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F118">
         <v>66</v>
       </c>
       <c r="G118" s="1">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="H118" s="1">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="I118" s="2">
         <v>6.2</v>
@@ -5375,19 +5375,19 @@
         <v>113</v>
       </c>
       <c r="D135">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E135">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F135">
         <v>14</v>
       </c>
       <c r="G135" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H135" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I135" s="2">
         <v>5.9</v>
@@ -5547,19 +5547,19 @@
         <v>100</v>
       </c>
       <c r="D140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E140">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F140">
         <v>35</v>
       </c>
       <c r="G140" s="1">
-        <v>74.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H140" s="1">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I140" s="2">
         <v>6.9</v>
@@ -6028,22 +6028,22 @@
         <v>122</v>
       </c>
       <c r="D154">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E154">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F154">
         <v>3</v>
       </c>
       <c r="G154" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I154" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -6063,7 +6063,7 @@
         <v>123</v>
       </c>
       <c r="D155">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E155">
         <v>36</v>
@@ -6072,19 +6072,19 @@
         <v>3</v>
       </c>
       <c r="G155" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H155" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I155" s="2">
         <v>9.5</v>
       </c>
       <c r="J155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K155" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6165,28 +6165,28 @@
         <v>100</v>
       </c>
       <c r="D158">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E158">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F158">
         <v>18</v>
       </c>
       <c r="G158" s="1">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="H158" s="1">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I158" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6442,19 +6442,19 @@
         <v>122</v>
       </c>
       <c r="D166">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E166">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F166">
         <v>5</v>
       </c>
       <c r="G166" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H166" s="1">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="I166" s="2">
         <v>7.7</v>
@@ -6477,19 +6477,19 @@
         <v>123</v>
       </c>
       <c r="D167">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E167">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F167">
         <v>6</v>
       </c>
       <c r="G167" s="1">
-        <v>82.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H167" s="1">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="I167" s="2">
         <v>7.1</v>
@@ -6649,19 +6649,19 @@
         <v>100</v>
       </c>
       <c r="D172">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E172">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F172">
         <v>83</v>
       </c>
       <c r="G172" s="1">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H172" s="1">
-        <v>29.9</v>
+        <v>29.6</v>
       </c>
       <c r="I172" s="2">
         <v>7</v>
@@ -6719,19 +6719,19 @@
         <v>112</v>
       </c>
       <c r="D174">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E174">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F174">
         <v>9</v>
       </c>
       <c r="G174" s="1">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H174" s="1">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="I174" s="2">
         <v>6.9</v>
@@ -6754,22 +6754,22 @@
         <v>113</v>
       </c>
       <c r="D175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F175">
         <v>7</v>
       </c>
       <c r="G175" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H175" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I175" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>115</v>
       </c>
       <c r="D177">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E177">
         <v>13</v>
@@ -6833,19 +6833,19 @@
         <v>5</v>
       </c>
       <c r="G177" s="1">
-        <v>72.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H177" s="1">
-        <v>27.8</v>
+        <v>26.3</v>
       </c>
       <c r="I177" s="2">
         <v>7.2</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -6926,28 +6926,28 @@
         <v>100</v>
       </c>
       <c r="D180">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E180">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F180">
         <v>28</v>
       </c>
       <c r="G180" s="1">
-        <v>87.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H180" s="1">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="I180" s="2">
         <v>7.5</v>
       </c>
       <c r="J180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K180" s="1">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7649,19 +7649,19 @@
         <v>112</v>
       </c>
       <c r="D201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E201">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F201">
         <v>10</v>
       </c>
       <c r="G201" s="1">
-        <v>74.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H201" s="1">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="I201" s="2">
         <v>5.7</v>
@@ -7684,19 +7684,19 @@
         <v>113</v>
       </c>
       <c r="D202">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E202">
         <v>19</v>
       </c>
       <c r="F202">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G202" s="1">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
       <c r="H202" s="1">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="I202" s="2">
         <v>5.5</v>
@@ -7719,7 +7719,7 @@
         <v>115</v>
       </c>
       <c r="D203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E203">
         <v>14</v>
@@ -7728,19 +7728,19 @@
         <v>4</v>
       </c>
       <c r="G203" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H203" s="1">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="I203" s="2">
         <v>6.4</v>
       </c>
       <c r="J203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -7751,28 +7751,28 @@
         <v>100</v>
       </c>
       <c r="D204">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E204">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F204">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G204" s="1">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="H204" s="1">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="I204" s="2">
         <v>5.9</v>
       </c>
       <c r="J204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K204" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -7786,7 +7786,7 @@
         <v>122</v>
       </c>
       <c r="D205">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E205">
         <v>31</v>
@@ -7795,19 +7795,19 @@
         <v>3</v>
       </c>
       <c r="G205" s="1">
-        <v>91.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H205" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I205" s="2">
         <v>8.4</v>
       </c>
       <c r="J205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" s="1">
-        <v>0</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -7821,19 +7821,19 @@
         <v>123</v>
       </c>
       <c r="D206">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E206">
         <v>39</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H206" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I206" s="2">
         <v>8.6</v>
@@ -7958,28 +7958,28 @@
         <v>100</v>
       </c>
       <c r="D210">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E210">
         <v>156</v>
       </c>
       <c r="F210">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G210" s="1">
-        <v>93.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H210" s="1">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I210" s="2">
         <v>8.1</v>
       </c>
       <c r="J210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -7993,22 +7993,22 @@
         <v>123</v>
       </c>
       <c r="D211">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E211">
         <v>36</v>
       </c>
       <c r="F211">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G211" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H211" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I211" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J211">
         <v>0</v>
@@ -8025,22 +8025,22 @@
         <v>100</v>
       </c>
       <c r="D212">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E212">
         <v>36</v>
       </c>
       <c r="F212">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G212" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H212" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I212" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -8261,7 +8261,7 @@
         <v>115</v>
       </c>
       <c r="D219">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="J219">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K219" s="1">
         <v>100</v>
@@ -8395,7 +8395,7 @@
         <v>100</v>
       </c>
       <c r="D223">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E223">
         <v>84</v>
@@ -8404,19 +8404,19 @@
         <v>35</v>
       </c>
       <c r="G223" s="1">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="H223" s="1">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="I223" s="2">
         <v>6.8</v>
       </c>
       <c r="J223">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K223" s="1">
-        <v>32</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -8698,7 +8698,7 @@
         <v>113</v>
       </c>
       <c r="D232">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="J232">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K232" s="1">
         <v>100</v>
@@ -8762,7 +8762,7 @@
         <v>115</v>
       </c>
       <c r="D234">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -8777,7 +8777,7 @@
         <v>0</v>
       </c>
       <c r="J234">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K234" s="1">
         <v>100</v>
@@ -9097,7 +9097,7 @@
         <v>112</v>
       </c>
       <c r="D244">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -9112,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="J244">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K244" s="1">
         <v>100</v>
@@ -9129,19 +9129,19 @@
         <v>113</v>
       </c>
       <c r="D245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E245">
         <v>21</v>
       </c>
       <c r="F245">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G245" s="1">
-        <v>52.5</v>
+        <v>53.8</v>
       </c>
       <c r="H245" s="1">
-        <v>47.5</v>
+        <v>46.2</v>
       </c>
       <c r="I245" s="2">
         <v>5.9</v>
@@ -9199,7 +9199,7 @@
         <v>115</v>
       </c>
       <c r="D247">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E247">
         <v>14</v>
@@ -9208,19 +9208,19 @@
         <v>4</v>
       </c>
       <c r="G247" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H247" s="1">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="I247" s="2">
         <v>7.1</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K247" s="1">
-        <v>0</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9301,19 +9301,19 @@
         <v>100</v>
       </c>
       <c r="D250">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E250">
         <v>95</v>
       </c>
       <c r="F250">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G250" s="1">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="H250" s="1">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="I250" s="2">
         <v>6.6</v>
@@ -9322,7 +9322,7 @@
         <v>39</v>
       </c>
       <c r="K250" s="1">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -9816,9 +9816,6 @@
       <c r="H2" s="1">
         <v>100</v>
       </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
       <c r="J2">
         <v>30</v>
       </c>
@@ -9851,9 +9848,6 @@
       <c r="H3" s="1">
         <v>100</v>
       </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>25</v>
       </c>
@@ -9886,9 +9880,6 @@
       <c r="H4" s="1">
         <v>100</v>
       </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
       <c r="J4">
         <v>16</v>
       </c>
@@ -9921,9 +9912,6 @@
       <c r="H5" s="1">
         <v>100</v>
       </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
       <c r="J5">
         <v>17</v>
       </c>
@@ -9956,9 +9944,6 @@
       <c r="H6" s="1">
         <v>85.7</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
       <c r="J6">
         <v>14</v>
       </c>
@@ -9988,9 +9973,6 @@
       <c r="H7" s="1">
         <v>98</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
       <c r="J7">
         <v>102</v>
       </c>
@@ -10023,9 +10005,6 @@
       <c r="H8" s="1">
         <v>100</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
       <c r="J8">
         <v>29</v>
       </c>
@@ -10058,9 +10037,6 @@
       <c r="H9" s="1">
         <v>100</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
       <c r="J9">
         <v>42</v>
       </c>
@@ -10093,9 +10069,6 @@
       <c r="H10" s="1">
         <v>100</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
       <c r="J10">
         <v>36</v>
       </c>
@@ -10128,9 +10101,6 @@
       <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
       <c r="J11">
         <v>43</v>
       </c>
@@ -10163,9 +10133,6 @@
       <c r="H12" s="1">
         <v>100</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
       <c r="J12">
         <v>32</v>
       </c>
@@ -10198,9 +10165,6 @@
       <c r="H13" s="1">
         <v>100</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
       <c r="J13">
         <v>37</v>
       </c>
@@ -10230,9 +10194,6 @@
       <c r="H14" s="1">
         <v>100</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
       <c r="J14">
         <v>219</v>
       </c>
@@ -10265,9 +10226,6 @@
       <c r="H15" s="1">
         <v>100</v>
       </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
       <c r="J15">
         <v>42</v>
       </c>
@@ -10300,9 +10258,6 @@
       <c r="H16" s="1">
         <v>100</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
       <c r="J16">
         <v>42</v>
       </c>
@@ -10335,9 +10290,6 @@
       <c r="H17" s="1">
         <v>100</v>
       </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
       <c r="J17">
         <v>37</v>
       </c>
@@ -10370,9 +10322,6 @@
       <c r="H18" s="1">
         <v>100</v>
       </c>
-      <c r="I18" s="2">
-        <v>0</v>
-      </c>
       <c r="J18">
         <v>37</v>
       </c>
@@ -10402,9 +10351,6 @@
       <c r="H19" s="1">
         <v>100</v>
       </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
       <c r="J19">
         <v>158</v>
       </c>
@@ -10437,9 +10383,6 @@
       <c r="H20" s="1">
         <v>100</v>
       </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
       <c r="J20">
         <v>44</v>
       </c>
@@ -10472,9 +10415,6 @@
       <c r="H21" s="1">
         <v>100</v>
       </c>
-      <c r="I21" s="2">
-        <v>0</v>
-      </c>
       <c r="J21">
         <v>37</v>
       </c>
@@ -10507,9 +10447,6 @@
       <c r="H22" s="1">
         <v>100</v>
       </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
       <c r="J22">
         <v>27</v>
       </c>
@@ -10542,9 +10479,6 @@
       <c r="H23" s="1">
         <v>100</v>
       </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
       <c r="J23">
         <v>26</v>
       </c>
@@ -10574,9 +10508,6 @@
       <c r="H24" s="1">
         <v>100</v>
       </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
       <c r="J24">
         <v>134</v>
       </c>
@@ -10609,9 +10540,6 @@
       <c r="H25" s="1">
         <v>85.7</v>
       </c>
-      <c r="I25" s="2">
-        <v>0</v>
-      </c>
       <c r="J25">
         <v>14</v>
       </c>
@@ -10641,9 +10569,6 @@
       <c r="H26" s="1">
         <v>85.7</v>
       </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
       <c r="J26">
         <v>14</v>
       </c>
@@ -10676,9 +10601,6 @@
       <c r="H27" s="1">
         <v>100</v>
       </c>
-      <c r="I27" s="2">
-        <v>0</v>
-      </c>
       <c r="J27">
         <v>30</v>
       </c>
@@ -10711,9 +10633,6 @@
       <c r="H28" s="1">
         <v>100</v>
       </c>
-      <c r="I28" s="2">
-        <v>0</v>
-      </c>
       <c r="J28">
         <v>32</v>
       </c>
@@ -10746,9 +10665,6 @@
       <c r="H29" s="1">
         <v>100</v>
       </c>
-      <c r="I29" s="2">
-        <v>0</v>
-      </c>
       <c r="J29">
         <v>37</v>
       </c>
@@ -10781,9 +10697,6 @@
       <c r="H30" s="1">
         <v>93.90000000000001</v>
       </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
       <c r="J30">
         <v>33</v>
       </c>
@@ -10813,9 +10726,6 @@
       <c r="H31" s="1">
         <v>98.5</v>
       </c>
-      <c r="I31" s="2">
-        <v>0</v>
-      </c>
       <c r="J31">
         <v>132</v>
       </c>
@@ -10848,9 +10758,6 @@
       <c r="H32" s="1">
         <v>100</v>
       </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
       <c r="J32">
         <v>36</v>
       </c>
@@ -10869,13 +10776,13 @@
         <v>112</v>
       </c>
       <c r="D33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -10883,11 +10790,8 @@
       <c r="H33" s="1">
         <v>100</v>
       </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
       <c r="J33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -10904,13 +10808,13 @@
         <v>113</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -10918,11 +10822,8 @@
       <c r="H34" s="1">
         <v>100</v>
       </c>
-      <c r="I34" s="2">
-        <v>0</v>
-      </c>
       <c r="J34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -10953,9 +10854,6 @@
       <c r="H35" s="1">
         <v>100</v>
       </c>
-      <c r="I35" s="2">
-        <v>0</v>
-      </c>
       <c r="J35">
         <v>37</v>
       </c>
@@ -10974,7 +10872,7 @@
         <v>115</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -10986,13 +10884,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
-      </c>
-      <c r="I36" s="2">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="J36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -11006,25 +10901,22 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J37">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -11055,9 +10947,6 @@
       <c r="H38" s="1">
         <v>100</v>
       </c>
-      <c r="I38" s="2">
-        <v>0</v>
-      </c>
       <c r="J38">
         <v>32</v>
       </c>
@@ -11090,9 +10979,6 @@
       <c r="H39" s="1">
         <v>96.7</v>
       </c>
-      <c r="I39" s="2">
-        <v>0</v>
-      </c>
       <c r="J39">
         <v>30</v>
       </c>
@@ -11125,9 +11011,6 @@
       <c r="H40" s="1">
         <v>100</v>
       </c>
-      <c r="I40" s="2">
-        <v>0</v>
-      </c>
       <c r="J40">
         <v>28</v>
       </c>
@@ -11157,9 +11040,6 @@
       <c r="H41" s="1">
         <v>98.90000000000001</v>
       </c>
-      <c r="I41" s="2">
-        <v>0</v>
-      </c>
       <c r="J41">
         <v>90</v>
       </c>
@@ -11192,9 +11072,6 @@
       <c r="H42" s="1">
         <v>100</v>
       </c>
-      <c r="I42" s="2">
-        <v>0</v>
-      </c>
       <c r="J42">
         <v>36</v>
       </c>
@@ -11227,9 +11104,6 @@
       <c r="H43" s="1">
         <v>100</v>
       </c>
-      <c r="I43" s="2">
-        <v>0</v>
-      </c>
       <c r="J43">
         <v>25</v>
       </c>
@@ -11259,9 +11133,6 @@
       <c r="H44" s="1">
         <v>100</v>
       </c>
-      <c r="I44" s="2">
-        <v>0</v>
-      </c>
       <c r="J44">
         <v>61</v>
       </c>
@@ -11294,9 +11165,6 @@
       <c r="H45" s="1">
         <v>100</v>
       </c>
-      <c r="I45" s="2">
-        <v>0</v>
-      </c>
       <c r="J45">
         <v>37</v>
       </c>
@@ -11329,9 +11197,6 @@
       <c r="H46" s="1">
         <v>100</v>
       </c>
-      <c r="I46" s="2">
-        <v>0</v>
-      </c>
       <c r="J46">
         <v>33</v>
       </c>
@@ -11364,9 +11229,6 @@
       <c r="H47" s="1">
         <v>100</v>
       </c>
-      <c r="I47" s="2">
-        <v>0</v>
-      </c>
       <c r="J47">
         <v>16</v>
       </c>
@@ -11399,9 +11261,6 @@
       <c r="H48" s="1">
         <v>100</v>
       </c>
-      <c r="I48" s="2">
-        <v>0</v>
-      </c>
       <c r="J48">
         <v>26</v>
       </c>
@@ -11434,9 +11293,6 @@
       <c r="H49" s="1">
         <v>85.7</v>
       </c>
-      <c r="I49" s="2">
-        <v>0</v>
-      </c>
       <c r="J49">
         <v>14</v>
       </c>
@@ -11466,9 +11322,6 @@
       <c r="H50" s="1">
         <v>98.40000000000001</v>
       </c>
-      <c r="I50" s="2">
-        <v>0</v>
-      </c>
       <c r="J50">
         <v>126</v>
       </c>
@@ -11501,9 +11354,6 @@
       <c r="H51" s="1">
         <v>100</v>
       </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
       <c r="J51">
         <v>27</v>
       </c>
@@ -11536,9 +11386,6 @@
       <c r="H52" s="1">
         <v>100</v>
       </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
       <c r="J52">
         <v>24</v>
       </c>
@@ -11557,13 +11404,13 @@
         <v>122</v>
       </c>
       <c r="D53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
@@ -11571,11 +11418,8 @@
       <c r="H53" s="1">
         <v>100</v>
       </c>
-      <c r="I53" s="2">
-        <v>0</v>
-      </c>
       <c r="J53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -11592,13 +11436,13 @@
         <v>122</v>
       </c>
       <c r="D54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -11606,11 +11450,8 @@
       <c r="H54" s="1">
         <v>100</v>
       </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
       <c r="J54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -11627,13 +11468,13 @@
         <v>123</v>
       </c>
       <c r="D55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -11641,11 +11482,8 @@
       <c r="H55" s="1">
         <v>100</v>
       </c>
-      <c r="I55" s="2">
-        <v>0</v>
-      </c>
       <c r="J55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K55" s="1">
         <v>100</v>
@@ -11676,9 +11514,6 @@
       <c r="H56" s="1">
         <v>100</v>
       </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
       <c r="J56">
         <v>39</v>
       </c>
@@ -11711,9 +11546,6 @@
       <c r="H57" s="1">
         <v>100</v>
       </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
       <c r="J57">
         <v>30</v>
       </c>
@@ -11729,13 +11561,13 @@
         <v>100</v>
       </c>
       <c r="D58">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
@@ -11743,11 +11575,8 @@
       <c r="H58" s="1">
         <v>100</v>
       </c>
-      <c r="I58" s="2">
-        <v>0</v>
-      </c>
       <c r="J58">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -11778,9 +11607,6 @@
       <c r="H59" s="1">
         <v>100</v>
       </c>
-      <c r="I59" s="2">
-        <v>0</v>
-      </c>
       <c r="J59">
         <v>42</v>
       </c>
@@ -11813,9 +11639,6 @@
       <c r="H60" s="1">
         <v>100</v>
       </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
       <c r="J60">
         <v>33</v>
       </c>
@@ -11845,9 +11668,6 @@
       <c r="H61" s="1">
         <v>100</v>
       </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
       <c r="J61">
         <v>75</v>
       </c>
@@ -11880,9 +11700,6 @@
       <c r="H62" s="1">
         <v>100</v>
       </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
       <c r="J62">
         <v>27</v>
       </c>
@@ -11901,13 +11718,13 @@
         <v>122</v>
       </c>
       <c r="D63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -11915,11 +11732,8 @@
       <c r="H63" s="1">
         <v>100</v>
       </c>
-      <c r="I63" s="2">
-        <v>0</v>
-      </c>
       <c r="J63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -11936,13 +11750,13 @@
         <v>123</v>
       </c>
       <c r="D64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -11950,11 +11764,8 @@
       <c r="H64" s="1">
         <v>100</v>
       </c>
-      <c r="I64" s="2">
-        <v>0</v>
-      </c>
       <c r="J64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -11985,9 +11796,6 @@
       <c r="H65" s="1">
         <v>100</v>
       </c>
-      <c r="I65" s="2">
-        <v>0</v>
-      </c>
       <c r="J65">
         <v>39</v>
       </c>
@@ -12006,13 +11814,13 @@
         <v>112</v>
       </c>
       <c r="D66">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -12020,11 +11828,8 @@
       <c r="H66" s="1">
         <v>100</v>
       </c>
-      <c r="I66" s="2">
-        <v>0</v>
-      </c>
       <c r="J66">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -12055,9 +11860,6 @@
       <c r="H67" s="1">
         <v>100</v>
       </c>
-      <c r="I67" s="2">
-        <v>0</v>
-      </c>
       <c r="J67">
         <v>32</v>
       </c>
@@ -12090,9 +11892,6 @@
       <c r="H68" s="1">
         <v>100</v>
       </c>
-      <c r="I68" s="2">
-        <v>0</v>
-      </c>
       <c r="J68">
         <v>30</v>
       </c>
@@ -12125,9 +11924,6 @@
       <c r="H69" s="1">
         <v>100</v>
       </c>
-      <c r="I69" s="2">
-        <v>0</v>
-      </c>
       <c r="J69">
         <v>28</v>
       </c>
@@ -12143,13 +11939,13 @@
         <v>100</v>
       </c>
       <c r="D70">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
@@ -12157,11 +11953,8 @@
       <c r="H70" s="1">
         <v>100</v>
       </c>
-      <c r="I70" s="2">
-        <v>0</v>
-      </c>
       <c r="J70">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -12192,9 +11985,6 @@
       <c r="H71" s="1">
         <v>100</v>
       </c>
-      <c r="I71" s="2">
-        <v>0</v>
-      </c>
       <c r="J71">
         <v>37</v>
       </c>
@@ -12227,9 +12017,6 @@
       <c r="H72" s="1">
         <v>100</v>
       </c>
-      <c r="I72" s="2">
-        <v>0</v>
-      </c>
       <c r="J72">
         <v>30</v>
       </c>
@@ -12262,9 +12049,6 @@
       <c r="H73" s="1">
         <v>100</v>
       </c>
-      <c r="I73" s="2">
-        <v>0</v>
-      </c>
       <c r="J73">
         <v>38</v>
       </c>
@@ -12297,9 +12081,6 @@
       <c r="H74" s="1">
         <v>100</v>
       </c>
-      <c r="I74" s="2">
-        <v>0</v>
-      </c>
       <c r="J74">
         <v>25</v>
       </c>
@@ -12332,9 +12113,6 @@
       <c r="H75" s="1">
         <v>93.90000000000001</v>
       </c>
-      <c r="I75" s="2">
-        <v>0</v>
-      </c>
       <c r="J75">
         <v>33</v>
       </c>
@@ -12367,9 +12145,6 @@
       <c r="H76" s="1">
         <v>100</v>
       </c>
-      <c r="I76" s="2">
-        <v>0</v>
-      </c>
       <c r="J76">
         <v>27</v>
       </c>
@@ -12402,9 +12177,6 @@
       <c r="H77" s="1">
         <v>100</v>
       </c>
-      <c r="I77" s="2">
-        <v>0</v>
-      </c>
       <c r="J77">
         <v>35</v>
       </c>
@@ -12437,9 +12209,6 @@
       <c r="H78" s="1">
         <v>100</v>
       </c>
-      <c r="I78" s="2">
-        <v>0</v>
-      </c>
       <c r="J78">
         <v>16</v>
       </c>
@@ -12469,9 +12238,6 @@
       <c r="H79" s="1">
         <v>99.2</v>
       </c>
-      <c r="I79" s="2">
-        <v>0</v>
-      </c>
       <c r="J79">
         <v>241</v>
       </c>
@@ -12504,9 +12270,6 @@
       <c r="H80" s="1">
         <v>100</v>
       </c>
-      <c r="I80" s="2">
-        <v>0</v>
-      </c>
       <c r="J80">
         <v>36</v>
       </c>
@@ -12525,13 +12288,13 @@
         <v>112</v>
       </c>
       <c r="D81">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="F81">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
@@ -12539,11 +12302,8 @@
       <c r="H81" s="1">
         <v>100</v>
       </c>
-      <c r="I81" s="2">
-        <v>0</v>
-      </c>
       <c r="J81">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -12560,13 +12320,13 @@
         <v>113</v>
       </c>
       <c r="D82">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -12574,11 +12334,8 @@
       <c r="H82" s="1">
         <v>100</v>
       </c>
-      <c r="I82" s="2">
-        <v>0</v>
-      </c>
       <c r="J82">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -12609,9 +12366,6 @@
       <c r="H83" s="1">
         <v>100</v>
       </c>
-      <c r="I83" s="2">
-        <v>0</v>
-      </c>
       <c r="J83">
         <v>37</v>
       </c>
@@ -12630,7 +12384,7 @@
         <v>115</v>
       </c>
       <c r="D84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -12642,13 +12396,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>100</v>
-      </c>
-      <c r="I84" s="2">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="J84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -12662,25 +12413,22 @@
         <v>100</v>
       </c>
       <c r="D85">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G85" s="1">
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>100</v>
-      </c>
-      <c r="I85" s="2">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J85">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -12711,9 +12459,6 @@
       <c r="H86" s="1">
         <v>100</v>
       </c>
-      <c r="I86" s="2">
-        <v>0</v>
-      </c>
       <c r="J86">
         <v>29</v>
       </c>
@@ -12746,9 +12491,6 @@
       <c r="H87" s="1">
         <v>100</v>
       </c>
-      <c r="I87" s="2">
-        <v>0</v>
-      </c>
       <c r="J87">
         <v>42</v>
       </c>
@@ -12781,9 +12523,6 @@
       <c r="H88" s="1">
         <v>100</v>
       </c>
-      <c r="I88" s="2">
-        <v>0</v>
-      </c>
       <c r="J88">
         <v>36</v>
       </c>
@@ -12816,9 +12555,6 @@
       <c r="H89" s="1">
         <v>100</v>
       </c>
-      <c r="I89" s="2">
-        <v>0</v>
-      </c>
       <c r="J89">
         <v>44</v>
       </c>
@@ -12851,9 +12587,6 @@
       <c r="H90" s="1">
         <v>100</v>
       </c>
-      <c r="I90" s="2">
-        <v>0</v>
-      </c>
       <c r="J90">
         <v>32</v>
       </c>
@@ -12886,9 +12619,6 @@
       <c r="H91" s="1">
         <v>100</v>
       </c>
-      <c r="I91" s="2">
-        <v>0</v>
-      </c>
       <c r="J91">
         <v>37</v>
       </c>
@@ -12921,9 +12651,6 @@
       <c r="H92" s="1">
         <v>100</v>
       </c>
-      <c r="I92" s="2">
-        <v>0</v>
-      </c>
       <c r="J92">
         <v>24</v>
       </c>
@@ -12953,9 +12680,6 @@
       <c r="H93" s="1">
         <v>100</v>
       </c>
-      <c r="I93" s="2">
-        <v>0</v>
-      </c>
       <c r="J93">
         <v>244</v>
       </c>
@@ -12988,9 +12712,6 @@
       <c r="H94" s="1">
         <v>0</v>
       </c>
-      <c r="I94" s="2">
-        <v>0</v>
-      </c>
       <c r="J94">
         <v>23</v>
       </c>
@@ -13023,9 +12744,6 @@
       <c r="H95" s="1">
         <v>0</v>
       </c>
-      <c r="I95" s="2">
-        <v>0</v>
-      </c>
       <c r="J95">
         <v>37</v>
       </c>
@@ -13058,9 +12776,6 @@
       <c r="H96" s="1">
         <v>0</v>
       </c>
-      <c r="I96" s="2">
-        <v>0</v>
-      </c>
       <c r="J96">
         <v>26</v>
       </c>
@@ -13093,9 +12808,6 @@
       <c r="H97" s="1">
         <v>0</v>
       </c>
-      <c r="I97" s="2">
-        <v>0</v>
-      </c>
       <c r="J97">
         <v>28</v>
       </c>
@@ -13128,9 +12840,6 @@
       <c r="H98" s="1">
         <v>0</v>
       </c>
-      <c r="I98" s="2">
-        <v>0</v>
-      </c>
       <c r="J98">
         <v>16</v>
       </c>
@@ -13163,9 +12872,6 @@
       <c r="H99" s="1">
         <v>100</v>
       </c>
-      <c r="I99" s="2">
-        <v>0</v>
-      </c>
       <c r="J99">
         <v>26</v>
       </c>
@@ -13195,9 +12901,6 @@
       <c r="H100" s="1">
         <v>16.7</v>
       </c>
-      <c r="I100" s="2">
-        <v>0</v>
-      </c>
       <c r="J100">
         <v>156</v>
       </c>
@@ -13230,9 +12933,6 @@
       <c r="H101" s="1">
         <v>0</v>
       </c>
-      <c r="I101" s="2">
-        <v>0</v>
-      </c>
       <c r="J101">
         <v>30</v>
       </c>
@@ -13265,9 +12965,6 @@
       <c r="H102" s="1">
         <v>0</v>
       </c>
-      <c r="I102" s="2">
-        <v>0</v>
-      </c>
       <c r="J102">
         <v>38</v>
       </c>
@@ -13300,9 +12997,6 @@
       <c r="H103" s="1">
         <v>0</v>
       </c>
-      <c r="I103" s="2">
-        <v>0</v>
-      </c>
       <c r="J103">
         <v>25</v>
       </c>
@@ -13335,9 +13029,6 @@
       <c r="H104" s="1">
         <v>0</v>
       </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
       <c r="J104">
         <v>33</v>
       </c>
@@ -13370,9 +13061,6 @@
       <c r="H105" s="1">
         <v>0</v>
       </c>
-      <c r="I105" s="2">
-        <v>0</v>
-      </c>
       <c r="J105">
         <v>35</v>
       </c>
@@ -13405,9 +13093,6 @@
       <c r="H106" s="1">
         <v>0</v>
       </c>
-      <c r="I106" s="2">
-        <v>0</v>
-      </c>
       <c r="J106">
         <v>28</v>
       </c>
@@ -13437,9 +13122,6 @@
       <c r="H107" s="1">
         <v>0</v>
       </c>
-      <c r="I107" s="2">
-        <v>0</v>
-      </c>
       <c r="J107">
         <v>189</v>
       </c>
@@ -13458,13 +13140,13 @@
         <v>112</v>
       </c>
       <c r="D108">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G108" s="1">
         <v>0</v>
@@ -13472,11 +13154,8 @@
       <c r="H108" s="1">
         <v>100</v>
       </c>
-      <c r="I108" s="2">
-        <v>0</v>
-      </c>
       <c r="J108">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K108" s="1">
         <v>100</v>
@@ -13507,9 +13186,6 @@
       <c r="H109" s="1">
         <v>100</v>
       </c>
-      <c r="I109" s="2">
-        <v>0</v>
-      </c>
       <c r="J109">
         <v>36</v>
       </c>
@@ -13542,9 +13218,6 @@
       <c r="H110" s="1">
         <v>100</v>
       </c>
-      <c r="I110" s="2">
-        <v>0</v>
-      </c>
       <c r="J110">
         <v>30</v>
       </c>
@@ -13560,13 +13233,13 @@
         <v>100</v>
       </c>
       <c r="D111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G111" s="1">
         <v>0</v>
@@ -13574,11 +13247,8 @@
       <c r="H111" s="1">
         <v>100</v>
       </c>
-      <c r="I111" s="2">
-        <v>0</v>
-      </c>
       <c r="J111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K111" s="1">
         <v>100</v>
@@ -13609,9 +13279,6 @@
       <c r="H112" s="1">
         <v>100</v>
       </c>
-      <c r="I112" s="2">
-        <v>0</v>
-      </c>
       <c r="J112">
         <v>27</v>
       </c>
@@ -13644,9 +13311,6 @@
       <c r="H113" s="1">
         <v>100</v>
       </c>
-      <c r="I113" s="2">
-        <v>0</v>
-      </c>
       <c r="J113">
         <v>24</v>
       </c>
@@ -13665,13 +13329,13 @@
         <v>122</v>
       </c>
       <c r="D114">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G114" s="1">
         <v>0</v>
@@ -13679,11 +13343,8 @@
       <c r="H114" s="1">
         <v>100</v>
       </c>
-      <c r="I114" s="2">
-        <v>0</v>
-      </c>
       <c r="J114">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K114" s="1">
         <v>100</v>
@@ -13700,13 +13361,13 @@
         <v>123</v>
       </c>
       <c r="D115">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G115" s="1">
         <v>0</v>
@@ -13714,11 +13375,8 @@
       <c r="H115" s="1">
         <v>100</v>
       </c>
-      <c r="I115" s="2">
-        <v>0</v>
-      </c>
       <c r="J115">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K115" s="1">
         <v>100</v>
@@ -13749,9 +13407,6 @@
       <c r="H116" s="1">
         <v>100</v>
       </c>
-      <c r="I116" s="2">
-        <v>0</v>
-      </c>
       <c r="J116">
         <v>39</v>
       </c>
@@ -13784,9 +13439,6 @@
       <c r="H117" s="1">
         <v>100</v>
       </c>
-      <c r="I117" s="2">
-        <v>0</v>
-      </c>
       <c r="J117">
         <v>30</v>
       </c>
@@ -13802,13 +13454,13 @@
         <v>100</v>
       </c>
       <c r="D118">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G118" s="1">
         <v>0</v>
@@ -13816,11 +13468,8 @@
       <c r="H118" s="1">
         <v>100</v>
       </c>
-      <c r="I118" s="2">
-        <v>0</v>
-      </c>
       <c r="J118">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K118" s="1">
         <v>100</v>
@@ -13851,9 +13500,6 @@
       <c r="H119" s="1">
         <v>100</v>
       </c>
-      <c r="I119" s="2">
-        <v>0</v>
-      </c>
       <c r="J119">
         <v>27</v>
       </c>
@@ -13886,9 +13532,6 @@
       <c r="H120" s="1">
         <v>100</v>
       </c>
-      <c r="I120" s="2">
-        <v>0</v>
-      </c>
       <c r="J120">
         <v>24</v>
       </c>
@@ -13921,9 +13564,6 @@
       <c r="H121" s="1">
         <v>100</v>
       </c>
-      <c r="I121" s="2">
-        <v>0</v>
-      </c>
       <c r="J121">
         <v>30</v>
       </c>
@@ -13956,9 +13596,6 @@
       <c r="H122" s="1">
         <v>100</v>
       </c>
-      <c r="I122" s="2">
-        <v>0</v>
-      </c>
       <c r="J122">
         <v>27</v>
       </c>
@@ -13991,9 +13628,6 @@
       <c r="H123" s="1">
         <v>100</v>
       </c>
-      <c r="I123" s="2">
-        <v>0</v>
-      </c>
       <c r="J123">
         <v>35</v>
       </c>
@@ -14026,9 +13660,6 @@
       <c r="H124" s="1">
         <v>100</v>
       </c>
-      <c r="I124" s="2">
-        <v>0</v>
-      </c>
       <c r="J124">
         <v>33</v>
       </c>
@@ -14061,9 +13692,6 @@
       <c r="H125" s="1">
         <v>85.7</v>
       </c>
-      <c r="I125" s="2">
-        <v>0</v>
-      </c>
       <c r="J125">
         <v>14</v>
       </c>
@@ -14093,9 +13721,6 @@
       <c r="H126" s="1">
         <v>98.90000000000001</v>
       </c>
-      <c r="I126" s="2">
-        <v>0</v>
-      </c>
       <c r="J126">
         <v>190</v>
       </c>
@@ -14128,9 +13753,6 @@
       <c r="H127" s="1">
         <v>100</v>
       </c>
-      <c r="I127" s="2">
-        <v>0</v>
-      </c>
       <c r="J127">
         <v>24</v>
       </c>
@@ -14160,9 +13782,6 @@
       <c r="H128" s="1">
         <v>100</v>
       </c>
-      <c r="I128" s="2">
-        <v>0</v>
-      </c>
       <c r="J128">
         <v>24</v>
       </c>
@@ -14195,9 +13814,6 @@
       <c r="H129" s="1">
         <v>100</v>
       </c>
-      <c r="I129" s="2">
-        <v>0</v>
-      </c>
       <c r="J129">
         <v>36</v>
       </c>
@@ -14230,9 +13846,6 @@
       <c r="H130" s="1">
         <v>100</v>
       </c>
-      <c r="I130" s="2">
-        <v>0</v>
-      </c>
       <c r="J130">
         <v>23</v>
       </c>
@@ -14265,9 +13878,6 @@
       <c r="H131" s="1">
         <v>100</v>
       </c>
-      <c r="I131" s="2">
-        <v>0</v>
-      </c>
       <c r="J131">
         <v>37</v>
       </c>
@@ -14300,9 +13910,6 @@
       <c r="H132" s="1">
         <v>100</v>
       </c>
-      <c r="I132" s="2">
-        <v>0</v>
-      </c>
       <c r="J132">
         <v>26</v>
       </c>
@@ -14335,9 +13942,6 @@
       <c r="H133" s="1">
         <v>100</v>
       </c>
-      <c r="I133" s="2">
-        <v>0</v>
-      </c>
       <c r="J133">
         <v>30</v>
       </c>
@@ -14367,9 +13971,6 @@
       <c r="H134" s="1">
         <v>100</v>
       </c>
-      <c r="I134" s="2">
-        <v>0</v>
-      </c>
       <c r="J134">
         <v>152</v>
       </c>
@@ -14388,13 +13989,13 @@
         <v>113</v>
       </c>
       <c r="D135">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G135" s="1">
         <v>0</v>
@@ -14402,11 +14003,8 @@
       <c r="H135" s="1">
         <v>100</v>
       </c>
-      <c r="I135" s="2">
-        <v>0</v>
-      </c>
       <c r="J135">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K135" s="1">
         <v>100</v>
@@ -14437,9 +14035,6 @@
       <c r="H136" s="1">
         <v>100</v>
       </c>
-      <c r="I136" s="2">
-        <v>0</v>
-      </c>
       <c r="J136">
         <v>24</v>
       </c>
@@ -14472,9 +14067,6 @@
       <c r="H137" s="1">
         <v>100</v>
       </c>
-      <c r="I137" s="2">
-        <v>0</v>
-      </c>
       <c r="J137">
         <v>24</v>
       </c>
@@ -14507,9 +14099,6 @@
       <c r="H138" s="1">
         <v>100</v>
       </c>
-      <c r="I138" s="2">
-        <v>0</v>
-      </c>
       <c r="J138">
         <v>25</v>
       </c>
@@ -14542,9 +14131,6 @@
       <c r="H139" s="1">
         <v>100</v>
       </c>
-      <c r="I139" s="2">
-        <v>0</v>
-      </c>
       <c r="J139">
         <v>26</v>
       </c>
@@ -14560,13 +14146,13 @@
         <v>100</v>
       </c>
       <c r="D140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
       <c r="F140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G140" s="1">
         <v>0</v>
@@ -14574,11 +14160,8 @@
       <c r="H140" s="1">
         <v>100</v>
       </c>
-      <c r="I140" s="2">
-        <v>0</v>
-      </c>
       <c r="J140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K140" s="1">
         <v>100</v>
@@ -14609,9 +14192,6 @@
       <c r="H141" s="1">
         <v>76.7</v>
       </c>
-      <c r="I141" s="2">
-        <v>0</v>
-      </c>
       <c r="J141">
         <v>30</v>
       </c>
@@ -14644,9 +14224,6 @@
       <c r="H142" s="1">
         <v>94.7</v>
       </c>
-      <c r="I142" s="2">
-        <v>0</v>
-      </c>
       <c r="J142">
         <v>38</v>
       </c>
@@ -14679,9 +14256,6 @@
       <c r="H143" s="1">
         <v>93.90000000000001</v>
       </c>
-      <c r="I143" s="2">
-        <v>0</v>
-      </c>
       <c r="J143">
         <v>33</v>
       </c>
@@ -14714,9 +14288,6 @@
       <c r="H144" s="1">
         <v>74.09999999999999</v>
       </c>
-      <c r="I144" s="2">
-        <v>0</v>
-      </c>
       <c r="J144">
         <v>27</v>
       </c>
@@ -14746,9 +14317,6 @@
       <c r="H145" s="1">
         <v>85.90000000000001</v>
       </c>
-      <c r="I145" s="2">
-        <v>0</v>
-      </c>
       <c r="J145">
         <v>128</v>
       </c>
@@ -14781,9 +14349,6 @@
       <c r="H146" s="1">
         <v>100</v>
       </c>
-      <c r="I146" s="2">
-        <v>0</v>
-      </c>
       <c r="J146">
         <v>44</v>
       </c>
@@ -14816,9 +14381,6 @@
       <c r="H147" s="1">
         <v>96.3</v>
       </c>
-      <c r="I147" s="2">
-        <v>0</v>
-      </c>
       <c r="J147">
         <v>27</v>
       </c>
@@ -14851,9 +14413,6 @@
       <c r="H148" s="1">
         <v>93.90000000000001</v>
       </c>
-      <c r="I148" s="2">
-        <v>0</v>
-      </c>
       <c r="J148">
         <v>33</v>
       </c>
@@ -14883,9 +14442,6 @@
       <c r="H149" s="1">
         <v>97.09999999999999</v>
       </c>
-      <c r="I149" s="2">
-        <v>0</v>
-      </c>
       <c r="J149">
         <v>104</v>
       </c>
@@ -14918,9 +14474,6 @@
       <c r="H150" s="1">
         <v>100</v>
       </c>
-      <c r="I150" s="2">
-        <v>0</v>
-      </c>
       <c r="J150">
         <v>28</v>
       </c>
@@ -14950,9 +14503,6 @@
       <c r="H151" s="1">
         <v>100</v>
       </c>
-      <c r="I151" s="2">
-        <v>0</v>
-      </c>
       <c r="J151">
         <v>28</v>
       </c>
@@ -14985,9 +14535,6 @@
       <c r="H152" s="1">
         <v>100</v>
       </c>
-      <c r="I152" s="2">
-        <v>0</v>
-      </c>
       <c r="J152">
         <v>27</v>
       </c>
@@ -15020,9 +14567,6 @@
       <c r="H153" s="1">
         <v>100</v>
       </c>
-      <c r="I153" s="2">
-        <v>0</v>
-      </c>
       <c r="J153">
         <v>24</v>
       </c>
@@ -15041,13 +14585,13 @@
         <v>122</v>
       </c>
       <c r="D154">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G154" s="1">
         <v>0</v>
@@ -15055,11 +14599,8 @@
       <c r="H154" s="1">
         <v>100</v>
       </c>
-      <c r="I154" s="2">
-        <v>0</v>
-      </c>
       <c r="J154">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K154" s="1">
         <v>100</v>
@@ -15076,7 +14617,7 @@
         <v>123</v>
       </c>
       <c r="D155">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -15088,13 +14629,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="1">
-        <v>100</v>
-      </c>
-      <c r="I155" s="2">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="J155">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K155" s="1">
         <v>100</v>
@@ -15125,9 +14663,6 @@
       <c r="H156" s="1">
         <v>100</v>
       </c>
-      <c r="I156" s="2">
-        <v>0</v>
-      </c>
       <c r="J156">
         <v>39</v>
       </c>
@@ -15160,9 +14695,6 @@
       <c r="H157" s="1">
         <v>100</v>
       </c>
-      <c r="I157" s="2">
-        <v>0</v>
-      </c>
       <c r="J157">
         <v>30</v>
       </c>
@@ -15178,25 +14710,22 @@
         <v>100</v>
       </c>
       <c r="D158">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="F158">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G158" s="1">
         <v>0</v>
       </c>
       <c r="H158" s="1">
-        <v>100</v>
-      </c>
-      <c r="I158" s="2">
-        <v>0</v>
+        <v>99.5</v>
       </c>
       <c r="J158">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K158" s="1">
         <v>100</v>
@@ -15227,9 +14756,6 @@
       <c r="H159" s="1">
         <v>100</v>
       </c>
-      <c r="I159" s="2">
-        <v>0</v>
-      </c>
       <c r="J159">
         <v>37</v>
       </c>
@@ -15262,9 +14788,6 @@
       <c r="H160" s="1">
         <v>100</v>
       </c>
-      <c r="I160" s="2">
-        <v>0</v>
-      </c>
       <c r="J160">
         <v>24</v>
       </c>
@@ -15297,9 +14820,6 @@
       <c r="H161" s="1">
         <v>100</v>
       </c>
-      <c r="I161" s="2">
-        <v>0</v>
-      </c>
       <c r="J161">
         <v>26</v>
       </c>
@@ -15332,9 +14852,6 @@
       <c r="H162" s="1">
         <v>100</v>
       </c>
-      <c r="I162" s="2">
-        <v>0</v>
-      </c>
       <c r="J162">
         <v>30</v>
       </c>
@@ -15364,9 +14881,6 @@
       <c r="H163" s="1">
         <v>100</v>
       </c>
-      <c r="I163" s="2">
-        <v>0</v>
-      </c>
       <c r="J163">
         <v>117</v>
       </c>
@@ -15399,9 +14913,6 @@
       <c r="H164" s="1">
         <v>100</v>
       </c>
-      <c r="I164" s="2">
-        <v>0</v>
-      </c>
       <c r="J164">
         <v>27</v>
       </c>
@@ -15434,9 +14945,6 @@
       <c r="H165" s="1">
         <v>100</v>
       </c>
-      <c r="I165" s="2">
-        <v>0</v>
-      </c>
       <c r="J165">
         <v>24</v>
       </c>
@@ -15455,25 +14963,22 @@
         <v>122</v>
       </c>
       <c r="D166">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G166" s="1">
         <v>0</v>
       </c>
       <c r="H166" s="1">
-        <v>88.2</v>
-      </c>
-      <c r="I166" s="2">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="J166">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K166" s="1">
         <v>100</v>
@@ -15490,25 +14995,22 @@
         <v>123</v>
       </c>
       <c r="D167">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E167">
         <v>0</v>
       </c>
       <c r="F167">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G167" s="1">
         <v>0</v>
       </c>
       <c r="H167" s="1">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="I167" s="2">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J167">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K167" s="1">
         <v>100</v>
@@ -15539,9 +15041,6 @@
       <c r="H168" s="1">
         <v>100</v>
       </c>
-      <c r="I168" s="2">
-        <v>0</v>
-      </c>
       <c r="J168">
         <v>39</v>
       </c>
@@ -15574,9 +15073,6 @@
       <c r="H169" s="1">
         <v>100</v>
       </c>
-      <c r="I169" s="2">
-        <v>0</v>
-      </c>
       <c r="J169">
         <v>30</v>
       </c>
@@ -15609,9 +15105,6 @@
       <c r="H170" s="1">
         <v>100</v>
       </c>
-      <c r="I170" s="2">
-        <v>0</v>
-      </c>
       <c r="J170">
         <v>42</v>
       </c>
@@ -15644,9 +15137,6 @@
       <c r="H171" s="1">
         <v>100</v>
       </c>
-      <c r="I171" s="2">
-        <v>0</v>
-      </c>
       <c r="J171">
         <v>43</v>
       </c>
@@ -15662,25 +15152,22 @@
         <v>100</v>
       </c>
       <c r="D172">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E172">
         <v>0</v>
       </c>
       <c r="F172">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G172" s="1">
         <v>0</v>
       </c>
       <c r="H172" s="1">
-        <v>97.8</v>
-      </c>
-      <c r="I172" s="2">
-        <v>0</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J172">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K172" s="1">
         <v>100</v>
@@ -15711,9 +15198,6 @@
       <c r="H173" s="1">
         <v>100</v>
       </c>
-      <c r="I173" s="2">
-        <v>0</v>
-      </c>
       <c r="J173">
         <v>36</v>
       </c>
@@ -15732,13 +15216,13 @@
         <v>112</v>
       </c>
       <c r="D174">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G174" s="1">
         <v>0</v>
@@ -15746,11 +15230,8 @@
       <c r="H174" s="1">
         <v>100</v>
       </c>
-      <c r="I174" s="2">
-        <v>0</v>
-      </c>
       <c r="J174">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K174" s="1">
         <v>100</v>
@@ -15767,13 +15248,13 @@
         <v>113</v>
       </c>
       <c r="D175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
       <c r="F175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G175" s="1">
         <v>0</v>
@@ -15781,11 +15262,8 @@
       <c r="H175" s="1">
         <v>100</v>
       </c>
-      <c r="I175" s="2">
-        <v>0</v>
-      </c>
       <c r="J175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K175" s="1">
         <v>100</v>
@@ -15816,9 +15294,6 @@
       <c r="H176" s="1">
         <v>100</v>
       </c>
-      <c r="I176" s="2">
-        <v>0</v>
-      </c>
       <c r="J176">
         <v>37</v>
       </c>
@@ -15837,7 +15312,7 @@
         <v>115</v>
       </c>
       <c r="D177">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -15849,13 +15324,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="1">
-        <v>100</v>
-      </c>
-      <c r="I177" s="2">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="J177">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K177" s="1">
         <v>100</v>
@@ -15886,9 +15358,6 @@
       <c r="H178" s="1">
         <v>100</v>
       </c>
-      <c r="I178" s="2">
-        <v>0</v>
-      </c>
       <c r="J178">
         <v>38</v>
       </c>
@@ -15921,9 +15390,6 @@
       <c r="H179" s="1">
         <v>93.90000000000001</v>
       </c>
-      <c r="I179" s="2">
-        <v>0</v>
-      </c>
       <c r="J179">
         <v>33</v>
       </c>
@@ -15939,25 +15405,22 @@
         <v>100</v>
       </c>
       <c r="D180">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E180">
         <v>0</v>
       </c>
       <c r="F180">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G180" s="1">
         <v>0</v>
       </c>
       <c r="H180" s="1">
-        <v>99.2</v>
-      </c>
-      <c r="I180" s="2">
-        <v>0</v>
+        <v>98.8</v>
       </c>
       <c r="J180">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K180" s="1">
         <v>100</v>
@@ -15988,9 +15451,6 @@
       <c r="H181" s="1">
         <v>100</v>
       </c>
-      <c r="I181" s="2">
-        <v>0</v>
-      </c>
       <c r="J181">
         <v>28</v>
       </c>
@@ -16023,9 +15483,6 @@
       <c r="H182" s="1">
         <v>100</v>
       </c>
-      <c r="I182" s="2">
-        <v>0</v>
-      </c>
       <c r="J182">
         <v>33</v>
       </c>
@@ -16058,9 +15515,6 @@
       <c r="H183" s="1">
         <v>100</v>
       </c>
-      <c r="I183" s="2">
-        <v>0</v>
-      </c>
       <c r="J183">
         <v>33</v>
       </c>
@@ -16093,9 +15547,6 @@
       <c r="H184" s="1">
         <v>100</v>
       </c>
-      <c r="I184" s="2">
-        <v>0</v>
-      </c>
       <c r="J184">
         <v>26</v>
       </c>
@@ -16128,9 +15579,6 @@
       <c r="H185" s="1">
         <v>85.7</v>
       </c>
-      <c r="I185" s="2">
-        <v>0</v>
-      </c>
       <c r="J185">
         <v>14</v>
       </c>
@@ -16160,9 +15608,6 @@
       <c r="H186" s="1">
         <v>98.5</v>
       </c>
-      <c r="I186" s="2">
-        <v>0</v>
-      </c>
       <c r="J186">
         <v>134</v>
       </c>
@@ -16195,9 +15640,6 @@
       <c r="H187" s="1">
         <v>100</v>
       </c>
-      <c r="I187" s="2">
-        <v>0</v>
-      </c>
       <c r="J187">
         <v>30</v>
       </c>
@@ -16230,9 +15672,6 @@
       <c r="H188" s="1">
         <v>100</v>
       </c>
-      <c r="I188" s="2">
-        <v>0</v>
-      </c>
       <c r="J188">
         <v>42</v>
       </c>
@@ -16265,9 +15704,6 @@
       <c r="H189" s="1">
         <v>100</v>
       </c>
-      <c r="I189" s="2">
-        <v>0</v>
-      </c>
       <c r="J189">
         <v>42</v>
       </c>
@@ -16300,9 +15736,6 @@
       <c r="H190" s="1">
         <v>100</v>
       </c>
-      <c r="I190" s="2">
-        <v>0</v>
-      </c>
       <c r="J190">
         <v>32</v>
       </c>
@@ -16332,9 +15765,6 @@
       <c r="H191" s="1">
         <v>100</v>
       </c>
-      <c r="I191" s="2">
-        <v>0</v>
-      </c>
       <c r="J191">
         <v>146</v>
       </c>
@@ -16367,9 +15797,6 @@
       <c r="H192" s="1">
         <v>100</v>
       </c>
-      <c r="I192" s="2">
-        <v>0</v>
-      </c>
       <c r="J192">
         <v>42</v>
       </c>
@@ -16402,9 +15829,6 @@
       <c r="H193" s="1">
         <v>100</v>
       </c>
-      <c r="I193" s="2">
-        <v>0</v>
-      </c>
       <c r="J193">
         <v>33</v>
       </c>
@@ -16434,9 +15858,6 @@
       <c r="H194" s="1">
         <v>100</v>
       </c>
-      <c r="I194" s="2">
-        <v>0</v>
-      </c>
       <c r="J194">
         <v>75</v>
       </c>
@@ -16469,9 +15890,6 @@
       <c r="H195" s="1">
         <v>100</v>
       </c>
-      <c r="I195" s="2">
-        <v>0</v>
-      </c>
       <c r="J195">
         <v>36</v>
       </c>
@@ -16504,9 +15922,6 @@
       <c r="H196" s="1">
         <v>100</v>
       </c>
-      <c r="I196" s="2">
-        <v>0</v>
-      </c>
       <c r="J196">
         <v>30</v>
       </c>
@@ -16539,9 +15954,6 @@
       <c r="H197" s="1">
         <v>100</v>
       </c>
-      <c r="I197" s="2">
-        <v>0</v>
-      </c>
       <c r="J197">
         <v>30</v>
       </c>
@@ -16574,9 +15986,6 @@
       <c r="H198" s="1">
         <v>100</v>
       </c>
-      <c r="I198" s="2">
-        <v>0</v>
-      </c>
       <c r="J198">
         <v>25</v>
       </c>
@@ -16606,9 +16015,6 @@
       <c r="H199" s="1">
         <v>100</v>
       </c>
-      <c r="I199" s="2">
-        <v>0</v>
-      </c>
       <c r="J199">
         <v>121</v>
       </c>
@@ -16641,9 +16047,6 @@
       <c r="H200" s="1">
         <v>100</v>
       </c>
-      <c r="I200" s="2">
-        <v>0</v>
-      </c>
       <c r="J200">
         <v>36</v>
       </c>
@@ -16662,13 +16065,13 @@
         <v>112</v>
       </c>
       <c r="D201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E201">
         <v>0</v>
       </c>
       <c r="F201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G201" s="1">
         <v>0</v>
@@ -16676,11 +16079,8 @@
       <c r="H201" s="1">
         <v>100</v>
       </c>
-      <c r="I201" s="2">
-        <v>0</v>
-      </c>
       <c r="J201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K201" s="1">
         <v>100</v>
@@ -16697,13 +16097,13 @@
         <v>113</v>
       </c>
       <c r="D202">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E202">
         <v>0</v>
       </c>
       <c r="F202">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G202" s="1">
         <v>0</v>
@@ -16711,11 +16111,8 @@
       <c r="H202" s="1">
         <v>100</v>
       </c>
-      <c r="I202" s="2">
-        <v>0</v>
-      </c>
       <c r="J202">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K202" s="1">
         <v>100</v>
@@ -16732,7 +16129,7 @@
         <v>115</v>
       </c>
       <c r="D203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -16744,13 +16141,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="1">
-        <v>100</v>
-      </c>
-      <c r="I203" s="2">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="J203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K203" s="1">
         <v>100</v>
@@ -16764,25 +16158,22 @@
         <v>100</v>
       </c>
       <c r="D204">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E204">
         <v>0</v>
       </c>
       <c r="F204">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G204" s="1">
         <v>0</v>
       </c>
       <c r="H204" s="1">
-        <v>100</v>
-      </c>
-      <c r="I204" s="2">
-        <v>0</v>
+        <v>99.2</v>
       </c>
       <c r="J204">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K204" s="1">
         <v>100</v>
@@ -16799,7 +16190,7 @@
         <v>122</v>
       </c>
       <c r="D205">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -16811,13 +16202,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="1">
-        <v>100</v>
-      </c>
-      <c r="I205" s="2">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J205">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K205" s="1">
         <v>100</v>
@@ -16834,13 +16222,13 @@
         <v>123</v>
       </c>
       <c r="D206">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E206">
         <v>0</v>
       </c>
       <c r="F206">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G206" s="1">
         <v>0</v>
@@ -16848,11 +16236,8 @@
       <c r="H206" s="1">
         <v>100</v>
       </c>
-      <c r="I206" s="2">
-        <v>0</v>
-      </c>
       <c r="J206">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K206" s="1">
         <v>100</v>
@@ -16883,9 +16268,6 @@
       <c r="H207" s="1">
         <v>100</v>
       </c>
-      <c r="I207" s="2">
-        <v>0</v>
-      </c>
       <c r="J207">
         <v>39</v>
       </c>
@@ -16918,9 +16300,6 @@
       <c r="H208" s="1">
         <v>100</v>
       </c>
-      <c r="I208" s="2">
-        <v>0</v>
-      </c>
       <c r="J208">
         <v>30</v>
       </c>
@@ -16953,9 +16332,6 @@
       <c r="H209" s="1">
         <v>100</v>
       </c>
-      <c r="I209" s="2">
-        <v>0</v>
-      </c>
       <c r="J209">
         <v>25</v>
       </c>
@@ -16971,25 +16347,22 @@
         <v>100</v>
       </c>
       <c r="D210">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E210">
         <v>0</v>
       </c>
       <c r="F210">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G210" s="1">
         <v>0</v>
       </c>
       <c r="H210" s="1">
-        <v>100</v>
-      </c>
-      <c r="I210" s="2">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J210">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K210" s="1">
         <v>100</v>
@@ -17006,13 +16379,13 @@
         <v>123</v>
       </c>
       <c r="D211">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E211">
         <v>0</v>
       </c>
       <c r="F211">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G211" s="1">
         <v>0</v>
@@ -17020,11 +16393,8 @@
       <c r="H211" s="1">
         <v>100</v>
       </c>
-      <c r="I211" s="2">
-        <v>0</v>
-      </c>
       <c r="J211">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K211" s="1">
         <v>100</v>
@@ -17038,13 +16408,13 @@
         <v>100</v>
       </c>
       <c r="D212">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E212">
         <v>0</v>
       </c>
       <c r="F212">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G212" s="1">
         <v>0</v>
@@ -17052,11 +16422,8 @@
       <c r="H212" s="1">
         <v>100</v>
       </c>
-      <c r="I212" s="2">
-        <v>0</v>
-      </c>
       <c r="J212">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K212" s="1">
         <v>100</v>
@@ -17087,9 +16454,6 @@
       <c r="H213" s="1">
         <v>100</v>
       </c>
-      <c r="I213" s="2">
-        <v>0</v>
-      </c>
       <c r="J213">
         <v>36</v>
       </c>
@@ -17119,9 +16483,6 @@
       <c r="H214" s="1">
         <v>100</v>
       </c>
-      <c r="I214" s="2">
-        <v>0</v>
-      </c>
       <c r="J214">
         <v>36</v>
       </c>
@@ -17154,9 +16515,6 @@
       <c r="H215" s="1">
         <v>100</v>
       </c>
-      <c r="I215" s="2">
-        <v>0</v>
-      </c>
       <c r="J215">
         <v>26</v>
       </c>
@@ -17186,9 +16544,6 @@
       <c r="H216" s="1">
         <v>100</v>
       </c>
-      <c r="I216" s="2">
-        <v>0</v>
-      </c>
       <c r="J216">
         <v>26</v>
       </c>
@@ -17221,9 +16576,6 @@
       <c r="H217" s="1">
         <v>97.2</v>
       </c>
-      <c r="I217" s="2">
-        <v>0</v>
-      </c>
       <c r="J217">
         <v>36</v>
       </c>
@@ -17256,9 +16608,6 @@
       <c r="H218" s="1">
         <v>0</v>
       </c>
-      <c r="I218" s="2">
-        <v>0</v>
-      </c>
       <c r="J218">
         <v>37</v>
       </c>
@@ -17277,7 +16626,7 @@
         <v>115</v>
       </c>
       <c r="D219">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -17291,11 +16640,8 @@
       <c r="H219" s="1">
         <v>0</v>
       </c>
-      <c r="I219" s="2">
-        <v>0</v>
-      </c>
       <c r="J219">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K219" s="1">
         <v>100</v>
@@ -17326,9 +16672,6 @@
       <c r="H220" s="1">
         <v>100</v>
       </c>
-      <c r="I220" s="2">
-        <v>0</v>
-      </c>
       <c r="J220">
         <v>28</v>
       </c>
@@ -17361,9 +16704,6 @@
       <c r="H221" s="1">
         <v>100</v>
       </c>
-      <c r="I221" s="2">
-        <v>0</v>
-      </c>
       <c r="J221">
         <v>28</v>
       </c>
@@ -17396,9 +16736,6 @@
       <c r="H222" s="1">
         <v>100</v>
       </c>
-      <c r="I222" s="2">
-        <v>0</v>
-      </c>
       <c r="J222">
         <v>28</v>
       </c>
@@ -17414,7 +16751,7 @@
         <v>100</v>
       </c>
       <c r="D223">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -17426,13 +16763,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="1">
-        <v>68</v>
-      </c>
-      <c r="I223" s="2">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J223">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K223" s="1">
         <v>100</v>
@@ -17463,9 +16797,6 @@
       <c r="H224" s="1">
         <v>100</v>
       </c>
-      <c r="I224" s="2">
-        <v>0</v>
-      </c>
       <c r="J224">
         <v>25</v>
       </c>
@@ -17498,9 +16829,6 @@
       <c r="H225" s="1">
         <v>100</v>
       </c>
-      <c r="I225" s="2">
-        <v>0</v>
-      </c>
       <c r="J225">
         <v>17</v>
       </c>
@@ -17530,9 +16858,6 @@
       <c r="H226" s="1">
         <v>100</v>
       </c>
-      <c r="I226" s="2">
-        <v>0</v>
-      </c>
       <c r="J226">
         <v>42</v>
       </c>
@@ -17565,9 +16890,6 @@
       <c r="H227" s="1">
         <v>0</v>
       </c>
-      <c r="I227" s="2">
-        <v>0</v>
-      </c>
       <c r="J227">
         <v>30</v>
       </c>
@@ -17600,9 +16922,6 @@
       <c r="H228" s="1">
         <v>100</v>
       </c>
-      <c r="I228" s="2">
-        <v>0</v>
-      </c>
       <c r="J228">
         <v>30</v>
       </c>
@@ -17632,9 +16951,6 @@
       <c r="H229" s="1">
         <v>50</v>
       </c>
-      <c r="I229" s="2">
-        <v>0</v>
-      </c>
       <c r="J229">
         <v>60</v>
       </c>
@@ -17667,9 +16983,6 @@
       <c r="H230" s="1">
         <v>85.7</v>
       </c>
-      <c r="I230" s="2">
-        <v>0</v>
-      </c>
       <c r="J230">
         <v>14</v>
       </c>
@@ -17699,9 +17012,6 @@
       <c r="H231" s="1">
         <v>85.7</v>
       </c>
-      <c r="I231" s="2">
-        <v>0</v>
-      </c>
       <c r="J231">
         <v>14</v>
       </c>
@@ -17720,7 +17030,7 @@
         <v>113</v>
       </c>
       <c r="D232">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -17734,11 +17044,8 @@
       <c r="H232" s="1">
         <v>0</v>
       </c>
-      <c r="I232" s="2">
-        <v>0</v>
-      </c>
       <c r="J232">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K232" s="1">
         <v>100</v>
@@ -17769,9 +17076,6 @@
       <c r="H233" s="1">
         <v>0</v>
       </c>
-      <c r="I233" s="2">
-        <v>0</v>
-      </c>
       <c r="J233">
         <v>37</v>
       </c>
@@ -17790,7 +17094,7 @@
         <v>115</v>
       </c>
       <c r="D234">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -17804,11 +17108,8 @@
       <c r="H234" s="1">
         <v>0</v>
       </c>
-      <c r="I234" s="2">
-        <v>0</v>
-      </c>
       <c r="J234">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K234" s="1">
         <v>100</v>
@@ -17839,9 +17140,6 @@
       <c r="H235" s="1">
         <v>0</v>
       </c>
-      <c r="I235" s="2">
-        <v>0</v>
-      </c>
       <c r="J235">
         <v>26</v>
       </c>
@@ -17871,9 +17169,6 @@
       <c r="H236" s="1">
         <v>0</v>
       </c>
-      <c r="I236" s="2">
-        <v>0</v>
-      </c>
       <c r="J236">
         <v>121</v>
       </c>
@@ -17906,9 +17201,6 @@
       <c r="H237" s="1">
         <v>100</v>
       </c>
-      <c r="I237" s="2">
-        <v>0</v>
-      </c>
       <c r="J237">
         <v>27</v>
       </c>
@@ -17941,9 +17233,6 @@
       <c r="H238" s="1">
         <v>100</v>
       </c>
-      <c r="I238" s="2">
-        <v>0</v>
-      </c>
       <c r="J238">
         <v>24</v>
       </c>
@@ -17976,9 +17265,6 @@
       <c r="H239" s="1">
         <v>100</v>
       </c>
-      <c r="I239" s="2">
-        <v>0</v>
-      </c>
       <c r="J239">
         <v>39</v>
       </c>
@@ -18011,9 +17297,6 @@
       <c r="H240" s="1">
         <v>100</v>
       </c>
-      <c r="I240" s="2">
-        <v>0</v>
-      </c>
       <c r="J240">
         <v>30</v>
       </c>
@@ -18046,9 +17329,6 @@
       <c r="H241" s="1">
         <v>100</v>
       </c>
-      <c r="I241" s="2">
-        <v>0</v>
-      </c>
       <c r="J241">
         <v>25</v>
       </c>
@@ -18081,9 +17361,6 @@
       <c r="H242" s="1">
         <v>82.90000000000001</v>
       </c>
-      <c r="I242" s="2">
-        <v>0</v>
-      </c>
       <c r="J242">
         <v>35</v>
       </c>
@@ -18113,9 +17390,6 @@
       <c r="H243" s="1">
         <v>96.7</v>
       </c>
-      <c r="I243" s="2">
-        <v>0</v>
-      </c>
       <c r="J243">
         <v>180</v>
       </c>
@@ -18134,7 +17408,7 @@
         <v>112</v>
       </c>
       <c r="D244">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -18148,11 +17422,8 @@
       <c r="H244" s="1">
         <v>0</v>
       </c>
-      <c r="I244" s="2">
-        <v>0</v>
-      </c>
       <c r="J244">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K244" s="1">
         <v>100</v>
@@ -18169,13 +17440,13 @@
         <v>113</v>
       </c>
       <c r="D245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E245">
         <v>0</v>
       </c>
       <c r="F245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G245" s="1">
         <v>0</v>
@@ -18183,11 +17454,8 @@
       <c r="H245" s="1">
         <v>100</v>
       </c>
-      <c r="I245" s="2">
-        <v>0</v>
-      </c>
       <c r="J245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K245" s="1">
         <v>100</v>
@@ -18218,9 +17486,6 @@
       <c r="H246" s="1">
         <v>100</v>
       </c>
-      <c r="I246" s="2">
-        <v>0</v>
-      </c>
       <c r="J246">
         <v>37</v>
       </c>
@@ -18239,7 +17504,7 @@
         <v>115</v>
       </c>
       <c r="D247">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -18251,13 +17516,10 @@
         <v>0</v>
       </c>
       <c r="H247" s="1">
-        <v>100</v>
-      </c>
-      <c r="I247" s="2">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="J247">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K247" s="1">
         <v>100</v>
@@ -18288,9 +17550,6 @@
       <c r="H248" s="1">
         <v>100</v>
       </c>
-      <c r="I248" s="2">
-        <v>0</v>
-      </c>
       <c r="J248">
         <v>24</v>
       </c>
@@ -18323,9 +17582,6 @@
       <c r="H249" s="1">
         <v>100</v>
       </c>
-      <c r="I249" s="2">
-        <v>0</v>
-      </c>
       <c r="J249">
         <v>30</v>
       </c>
@@ -18341,25 +17597,22 @@
         <v>100</v>
       </c>
       <c r="D250">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E250">
         <v>0</v>
       </c>
       <c r="F250">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G250" s="1">
         <v>0</v>
       </c>
       <c r="H250" s="1">
-        <v>79.3</v>
-      </c>
-      <c r="I250" s="2">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="J250">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K250" s="1">
         <v>100</v>
@@ -18390,9 +17643,6 @@
       <c r="H251" s="1">
         <v>100</v>
       </c>
-      <c r="I251" s="2">
-        <v>0</v>
-      </c>
       <c r="J251">
         <v>36</v>
       </c>
@@ -18425,9 +17675,6 @@
       <c r="H252" s="1">
         <v>100</v>
       </c>
-      <c r="I252" s="2">
-        <v>0</v>
-      </c>
       <c r="J252">
         <v>25</v>
       </c>
@@ -18460,9 +17707,6 @@
       <c r="H253" s="1">
         <v>100</v>
       </c>
-      <c r="I253" s="2">
-        <v>0</v>
-      </c>
       <c r="J253">
         <v>25</v>
       </c>
@@ -18495,9 +17739,6 @@
       <c r="H254" s="1">
         <v>96.7</v>
       </c>
-      <c r="I254" s="2">
-        <v>0</v>
-      </c>
       <c r="J254">
         <v>30</v>
       </c>
@@ -18530,9 +17771,6 @@
       <c r="H255" s="1">
         <v>100</v>
       </c>
-      <c r="I255" s="2">
-        <v>0</v>
-      </c>
       <c r="J255">
         <v>28</v>
       </c>
@@ -18562,9 +17800,6 @@
       <c r="H256" s="1">
         <v>99.3</v>
       </c>
-      <c r="I256" s="2">
-        <v>0</v>
-      </c>
       <c r="J256">
         <v>144</v>
       </c>
@@ -18597,9 +17832,6 @@
       <c r="H257" s="1">
         <v>100</v>
       </c>
-      <c r="I257" s="2">
-        <v>0</v>
-      </c>
       <c r="J257">
         <v>24</v>
       </c>
@@ -18632,9 +17864,6 @@
       <c r="H258" s="1">
         <v>100</v>
       </c>
-      <c r="I258" s="2">
-        <v>0</v>
-      </c>
       <c r="J258">
         <v>38</v>
       </c>
@@ -18667,9 +17896,6 @@
       <c r="H259" s="1">
         <v>100</v>
       </c>
-      <c r="I259" s="2">
-        <v>0</v>
-      </c>
       <c r="J259">
         <v>38</v>
       </c>
@@ -18702,9 +17928,6 @@
       <c r="H260" s="1">
         <v>100</v>
       </c>
-      <c r="I260" s="2">
-        <v>0</v>
-      </c>
       <c r="J260">
         <v>35</v>
       </c>
@@ -18737,9 +17960,6 @@
       <c r="H261" s="1">
         <v>100</v>
       </c>
-      <c r="I261" s="2">
-        <v>0</v>
-      </c>
       <c r="J261">
         <v>35</v>
       </c>
@@ -18768,9 +17988,6 @@
       </c>
       <c r="H262" s="1">
         <v>100</v>
-      </c>
-      <c r="I262" s="2">
-        <v>0</v>
       </c>
       <c r="J262">
         <v>170</v>
@@ -19909,25 +19126,25 @@
         <v>112</v>
       </c>
       <c r="D33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>23</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" s="1">
-        <v>59</v>
+        <v>60.5</v>
       </c>
       <c r="H33" s="1">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="I33" s="2">
         <v>6.3</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="1">
         <v>100</v>
@@ -19944,25 +19161,25 @@
         <v>113</v>
       </c>
       <c r="D34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>14</v>
       </c>
       <c r="G34" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I34" s="2">
         <v>6.7</v>
       </c>
       <c r="J34">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K34" s="1">
         <v>100</v>
@@ -20014,7 +19231,7 @@
         <v>115</v>
       </c>
       <c r="D36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -20023,16 +19240,16 @@
         <v>6</v>
       </c>
       <c r="G36" s="1">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="H36" s="1">
-        <v>33.3</v>
+        <v>31.6</v>
       </c>
       <c r="I36" s="2">
         <v>6.6</v>
       </c>
       <c r="J36">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K36" s="1">
         <v>100</v>
@@ -20046,25 +19263,25 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E37">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F37">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37" s="1">
-        <v>55.9</v>
+        <v>55.6</v>
       </c>
       <c r="H37" s="1">
-        <v>44.1</v>
+        <v>43.8</v>
       </c>
       <c r="I37" s="2">
         <v>6.3</v>
       </c>
       <c r="J37">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K37" s="1">
         <v>100</v>
@@ -20597,25 +19814,25 @@
         <v>122</v>
       </c>
       <c r="D53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E53">
         <v>14</v>
       </c>
       <c r="F53">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G53" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="H53" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="I53" s="2">
         <v>6.1</v>
       </c>
       <c r="J53">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K53" s="1">
         <v>100</v>
@@ -20632,25 +19849,25 @@
         <v>122</v>
       </c>
       <c r="D54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
       <c r="G54" s="1">
-        <v>88.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H54" s="1">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="I54" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J54">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K54" s="1">
         <v>100</v>
@@ -20667,25 +19884,25 @@
         <v>123</v>
       </c>
       <c r="D55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E55">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F55">
         <v>21</v>
       </c>
       <c r="G55" s="1">
-        <v>46.2</v>
+        <v>47.5</v>
       </c>
       <c r="H55" s="1">
-        <v>53.8</v>
+        <v>52.5</v>
       </c>
       <c r="I55" s="2">
         <v>6</v>
       </c>
       <c r="J55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K55" s="1">
         <v>100</v>
@@ -20769,25 +19986,25 @@
         <v>100</v>
       </c>
       <c r="D58">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E58">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F58">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G58" s="1">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="H58" s="1">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="I58" s="2">
         <v>6.2</v>
       </c>
       <c r="J58">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K58" s="1">
         <v>100</v>
@@ -20941,25 +20158,25 @@
         <v>122</v>
       </c>
       <c r="D63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E63">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F63">
         <v>3</v>
       </c>
       <c r="G63" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H63" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I63" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J63">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K63" s="1">
         <v>100</v>
@@ -20976,25 +20193,25 @@
         <v>123</v>
       </c>
       <c r="D64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E64">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F64">
         <v>3</v>
       </c>
       <c r="G64" s="1">
-        <v>92.3</v>
+        <v>92.5</v>
       </c>
       <c r="H64" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I64" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K64" s="1">
         <v>100</v>
@@ -21046,25 +20263,25 @@
         <v>112</v>
       </c>
       <c r="D66">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E66">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F66">
         <v>12</v>
       </c>
       <c r="G66" s="1">
-        <v>69.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H66" s="1">
-        <v>30.8</v>
+        <v>31.6</v>
       </c>
       <c r="I66" s="2">
         <v>6.3</v>
       </c>
       <c r="J66">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K66" s="1">
         <v>100</v>
@@ -21183,10 +20400,10 @@
         <v>100</v>
       </c>
       <c r="D70">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E70">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F70">
         <v>29</v>
@@ -21201,7 +20418,7 @@
         <v>7.8</v>
       </c>
       <c r="J70">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K70" s="1">
         <v>100</v>
@@ -21565,25 +20782,25 @@
         <v>112</v>
       </c>
       <c r="D81">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E81">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F81">
         <v>11</v>
       </c>
       <c r="G81" s="1">
-        <v>71.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="H81" s="1">
-        <v>28.2</v>
+        <v>28.9</v>
       </c>
       <c r="I81" s="2">
         <v>6</v>
       </c>
       <c r="J81">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K81" s="1">
         <v>100</v>
@@ -21600,25 +20817,25 @@
         <v>113</v>
       </c>
       <c r="D82">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F82">
         <v>7</v>
       </c>
       <c r="G82" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H82" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I82" s="2">
         <v>6.5</v>
       </c>
       <c r="J82">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K82" s="1">
         <v>100</v>
@@ -21670,7 +20887,7 @@
         <v>115</v>
       </c>
       <c r="D84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E84">
         <v>9</v>
@@ -21679,16 +20896,16 @@
         <v>9</v>
       </c>
       <c r="G84" s="1">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="H84" s="1">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="I84" s="2">
         <v>5.7</v>
       </c>
       <c r="J84">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K84" s="1">
         <v>100</v>
@@ -21702,25 +20919,25 @@
         <v>100</v>
       </c>
       <c r="D85">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E85">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F85">
         <v>48</v>
       </c>
       <c r="G85" s="1">
-        <v>71.8</v>
+        <v>71</v>
       </c>
       <c r="H85" s="1">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="I85" s="2">
         <v>6.1</v>
       </c>
       <c r="J85">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K85" s="1">
         <v>100</v>
@@ -22028,9 +21245,6 @@
       <c r="H94" s="1">
         <v>0</v>
       </c>
-      <c r="I94" s="2">
-        <v>0</v>
-      </c>
       <c r="J94">
         <v>23</v>
       </c>
@@ -22063,9 +21277,6 @@
       <c r="H95" s="1">
         <v>0</v>
       </c>
-      <c r="I95" s="2">
-        <v>0</v>
-      </c>
       <c r="J95">
         <v>37</v>
       </c>
@@ -22098,9 +21309,6 @@
       <c r="H96" s="1">
         <v>0</v>
       </c>
-      <c r="I96" s="2">
-        <v>0</v>
-      </c>
       <c r="J96">
         <v>26</v>
       </c>
@@ -22133,9 +21341,6 @@
       <c r="H97" s="1">
         <v>0</v>
       </c>
-      <c r="I97" s="2">
-        <v>0</v>
-      </c>
       <c r="J97">
         <v>28</v>
       </c>
@@ -22168,9 +21373,6 @@
       <c r="H98" s="1">
         <v>0</v>
       </c>
-      <c r="I98" s="2">
-        <v>0</v>
-      </c>
       <c r="J98">
         <v>16</v>
       </c>
@@ -22236,7 +21438,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="2">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J100">
         <v>156</v>
@@ -22270,9 +21472,6 @@
       <c r="H101" s="1">
         <v>0</v>
       </c>
-      <c r="I101" s="2">
-        <v>0</v>
-      </c>
       <c r="J101">
         <v>30</v>
       </c>
@@ -22305,9 +21504,6 @@
       <c r="H102" s="1">
         <v>0</v>
       </c>
-      <c r="I102" s="2">
-        <v>0</v>
-      </c>
       <c r="J102">
         <v>38</v>
       </c>
@@ -22340,9 +21536,6 @@
       <c r="H103" s="1">
         <v>0</v>
       </c>
-      <c r="I103" s="2">
-        <v>0</v>
-      </c>
       <c r="J103">
         <v>25</v>
       </c>
@@ -22375,9 +21568,6 @@
       <c r="H104" s="1">
         <v>0</v>
       </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
       <c r="J104">
         <v>33</v>
       </c>
@@ -22410,9 +21600,6 @@
       <c r="H105" s="1">
         <v>0</v>
       </c>
-      <c r="I105" s="2">
-        <v>0</v>
-      </c>
       <c r="J105">
         <v>35</v>
       </c>
@@ -22445,9 +21632,6 @@
       <c r="H106" s="1">
         <v>0</v>
       </c>
-      <c r="I106" s="2">
-        <v>0</v>
-      </c>
       <c r="J106">
         <v>28</v>
       </c>
@@ -22477,9 +21661,6 @@
       <c r="H107" s="1">
         <v>0</v>
       </c>
-      <c r="I107" s="2">
-        <v>0</v>
-      </c>
       <c r="J107">
         <v>189</v>
       </c>
@@ -22498,25 +21679,25 @@
         <v>112</v>
       </c>
       <c r="D108">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E108">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F108">
         <v>18</v>
       </c>
       <c r="G108" s="1">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="H108" s="1">
-        <v>46.2</v>
+        <v>47.4</v>
       </c>
       <c r="I108" s="2">
         <v>6.4</v>
       </c>
       <c r="J108">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K108" s="1">
         <v>100</v>
@@ -22600,25 +21781,25 @@
         <v>100</v>
       </c>
       <c r="D111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E111">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F111">
         <v>25</v>
       </c>
       <c r="G111" s="1">
-        <v>76.2</v>
+        <v>76</v>
       </c>
       <c r="H111" s="1">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="I111" s="2">
         <v>7.8</v>
       </c>
       <c r="J111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K111" s="1">
         <v>100</v>
@@ -22705,25 +21886,25 @@
         <v>122</v>
       </c>
       <c r="D114">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E114">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F114">
         <v>9</v>
       </c>
       <c r="G114" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H114" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I114" s="2">
         <v>6.3</v>
       </c>
       <c r="J114">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K114" s="1">
         <v>100</v>
@@ -22740,25 +21921,25 @@
         <v>123</v>
       </c>
       <c r="D115">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E115">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F115">
         <v>9</v>
       </c>
       <c r="G115" s="1">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="H115" s="1">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="I115" s="2">
         <v>6.4</v>
       </c>
       <c r="J115">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K115" s="1">
         <v>100</v>
@@ -22842,25 +22023,25 @@
         <v>100</v>
       </c>
       <c r="D118">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E118">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F118">
         <v>66</v>
       </c>
       <c r="G118" s="1">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="H118" s="1">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="I118" s="2">
         <v>6.2</v>
       </c>
       <c r="J118">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K118" s="1">
         <v>100</v>
@@ -23428,25 +22609,25 @@
         <v>113</v>
       </c>
       <c r="D135">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E135">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F135">
         <v>14</v>
       </c>
       <c r="G135" s="1">
-        <v>65</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H135" s="1">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="I135" s="2">
         <v>6</v>
       </c>
       <c r="J135">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K135" s="1">
         <v>100</v>
@@ -23600,25 +22781,25 @@
         <v>100</v>
       </c>
       <c r="D140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E140">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F140">
         <v>35</v>
       </c>
       <c r="G140" s="1">
-        <v>74.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H140" s="1">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="I140" s="2">
         <v>7.1</v>
       </c>
       <c r="J140">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K140" s="1">
         <v>100</v>
@@ -24081,25 +23262,25 @@
         <v>122</v>
       </c>
       <c r="D154">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E154">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F154">
         <v>3</v>
       </c>
       <c r="G154" s="1">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I154" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J154">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K154" s="1">
         <v>100</v>
@@ -24116,7 +23297,7 @@
         <v>123</v>
       </c>
       <c r="D155">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E155">
         <v>36</v>
@@ -24125,16 +23306,16 @@
         <v>3</v>
       </c>
       <c r="G155" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H155" s="1">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I155" s="2">
         <v>9.5</v>
       </c>
       <c r="J155">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K155" s="1">
         <v>100</v>
@@ -24218,25 +23399,25 @@
         <v>100</v>
       </c>
       <c r="D158">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E158">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F158">
         <v>18</v>
       </c>
       <c r="G158" s="1">
-        <v>90.7</v>
+        <v>90.3</v>
       </c>
       <c r="H158" s="1">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I158" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J158">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K158" s="1">
         <v>100</v>
@@ -24495,25 +23676,25 @@
         <v>122</v>
       </c>
       <c r="D166">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E166">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F166">
         <v>9</v>
       </c>
       <c r="G166" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H166" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I166" s="2">
         <v>7.4</v>
       </c>
       <c r="J166">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K166" s="1">
         <v>100</v>
@@ -24530,25 +23711,25 @@
         <v>123</v>
       </c>
       <c r="D167">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E167">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F167">
         <v>7</v>
       </c>
       <c r="G167" s="1">
-        <v>82.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H167" s="1">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="I167" s="2">
         <v>7.2</v>
       </c>
       <c r="J167">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K167" s="1">
         <v>100</v>
@@ -24702,25 +23883,25 @@
         <v>100</v>
       </c>
       <c r="D172">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E172">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F172">
         <v>88</v>
       </c>
       <c r="G172" s="1">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H172" s="1">
-        <v>31.7</v>
+        <v>31.4</v>
       </c>
       <c r="I172" s="2">
         <v>7</v>
       </c>
       <c r="J172">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K172" s="1">
         <v>100</v>
@@ -24772,25 +23953,25 @@
         <v>112</v>
       </c>
       <c r="D174">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E174">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F174">
         <v>9</v>
       </c>
       <c r="G174" s="1">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H174" s="1">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="I174" s="2">
         <v>6.9</v>
       </c>
       <c r="J174">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K174" s="1">
         <v>100</v>
@@ -24807,25 +23988,25 @@
         <v>113</v>
       </c>
       <c r="D175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E175">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F175">
         <v>7</v>
       </c>
       <c r="G175" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H175" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I175" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J175">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K175" s="1">
         <v>100</v>
@@ -24877,7 +24058,7 @@
         <v>115</v>
       </c>
       <c r="D177">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E177">
         <v>13</v>
@@ -24886,16 +24067,16 @@
         <v>5</v>
       </c>
       <c r="G177" s="1">
-        <v>72.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H177" s="1">
-        <v>27.8</v>
+        <v>26.3</v>
       </c>
       <c r="I177" s="2">
         <v>7.2</v>
       </c>
       <c r="J177">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K177" s="1">
         <v>100</v>
@@ -24979,25 +24160,25 @@
         <v>100</v>
       </c>
       <c r="D180">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E180">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F180">
         <v>28</v>
       </c>
       <c r="G180" s="1">
-        <v>87.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H180" s="1">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="I180" s="2">
         <v>7.5</v>
       </c>
       <c r="J180">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K180" s="1">
         <v>100</v>
@@ -25702,25 +24883,25 @@
         <v>112</v>
       </c>
       <c r="D201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E201">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F201">
         <v>10</v>
       </c>
       <c r="G201" s="1">
-        <v>74.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="H201" s="1">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="I201" s="2">
         <v>5.7</v>
       </c>
       <c r="J201">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K201" s="1">
         <v>100</v>
@@ -25737,25 +24918,25 @@
         <v>113</v>
       </c>
       <c r="D202">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E202">
         <v>19</v>
       </c>
       <c r="F202">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G202" s="1">
-        <v>47.5</v>
+        <v>48.7</v>
       </c>
       <c r="H202" s="1">
-        <v>52.5</v>
+        <v>51.3</v>
       </c>
       <c r="I202" s="2">
         <v>5.5</v>
       </c>
       <c r="J202">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K202" s="1">
         <v>100</v>
@@ -25772,7 +24953,7 @@
         <v>115</v>
       </c>
       <c r="D203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E203">
         <v>14</v>
@@ -25781,16 +24962,16 @@
         <v>4</v>
       </c>
       <c r="G203" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H203" s="1">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="I203" s="2">
         <v>6.4</v>
       </c>
       <c r="J203">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K203" s="1">
         <v>100</v>
@@ -25804,25 +24985,25 @@
         <v>100</v>
       </c>
       <c r="D204">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E204">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F204">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G204" s="1">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="H204" s="1">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="I204" s="2">
         <v>5.9</v>
       </c>
       <c r="J204">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K204" s="1">
         <v>100</v>
@@ -25839,7 +25020,7 @@
         <v>122</v>
       </c>
       <c r="D205">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E205">
         <v>31</v>
@@ -25848,16 +25029,16 @@
         <v>3</v>
       </c>
       <c r="G205" s="1">
-        <v>91.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H205" s="1">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I205" s="2">
         <v>8.4</v>
       </c>
       <c r="J205">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K205" s="1">
         <v>100</v>
@@ -25874,25 +25055,25 @@
         <v>123</v>
       </c>
       <c r="D206">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E206">
         <v>39</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H206" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I206" s="2">
         <v>8.6</v>
       </c>
       <c r="J206">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K206" s="1">
         <v>100</v>
@@ -26011,25 +25192,25 @@
         <v>100</v>
       </c>
       <c r="D210">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E210">
         <v>156</v>
       </c>
       <c r="F210">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G210" s="1">
-        <v>93.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H210" s="1">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I210" s="2">
         <v>8.1</v>
       </c>
       <c r="J210">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K210" s="1">
         <v>100</v>
@@ -26046,25 +25227,25 @@
         <v>123</v>
       </c>
       <c r="D211">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E211">
         <v>36</v>
       </c>
       <c r="F211">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G211" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H211" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I211" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J211">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K211" s="1">
         <v>100</v>
@@ -26078,25 +25259,25 @@
         <v>100</v>
       </c>
       <c r="D212">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E212">
         <v>36</v>
       </c>
       <c r="F212">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G212" s="1">
-        <v>92.3</v>
+        <v>90</v>
       </c>
       <c r="H212" s="1">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I212" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J212">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K212" s="1">
         <v>100</v>
@@ -26296,9 +25477,6 @@
       <c r="H218" s="1">
         <v>0</v>
       </c>
-      <c r="I218" s="2">
-        <v>0</v>
-      </c>
       <c r="J218">
         <v>37</v>
       </c>
@@ -26317,7 +25495,7 @@
         <v>115</v>
       </c>
       <c r="D219">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -26331,11 +25509,8 @@
       <c r="H219" s="1">
         <v>0</v>
       </c>
-      <c r="I219" s="2">
-        <v>0</v>
-      </c>
       <c r="J219">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K219" s="1">
         <v>100</v>
@@ -26454,7 +25629,7 @@
         <v>100</v>
       </c>
       <c r="D223">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E223">
         <v>84</v>
@@ -26463,16 +25638,16 @@
         <v>35</v>
       </c>
       <c r="G223" s="1">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="H223" s="1">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="I223" s="2">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="J223">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K223" s="1">
         <v>100</v>
@@ -26605,9 +25780,6 @@
       <c r="H227" s="1">
         <v>0</v>
       </c>
-      <c r="I227" s="2">
-        <v>0</v>
-      </c>
       <c r="J227">
         <v>30</v>
       </c>
@@ -26673,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="I229" s="2">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="J229">
         <v>60</v>
@@ -26760,7 +25932,7 @@
         <v>113</v>
       </c>
       <c r="D232">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -26774,11 +25946,8 @@
       <c r="H232" s="1">
         <v>0</v>
       </c>
-      <c r="I232" s="2">
-        <v>0</v>
-      </c>
       <c r="J232">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K232" s="1">
         <v>100</v>
@@ -26809,9 +25978,6 @@
       <c r="H233" s="1">
         <v>0</v>
       </c>
-      <c r="I233" s="2">
-        <v>0</v>
-      </c>
       <c r="J233">
         <v>37</v>
       </c>
@@ -26830,7 +25996,7 @@
         <v>115</v>
       </c>
       <c r="D234">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -26844,11 +26010,8 @@
       <c r="H234" s="1">
         <v>0</v>
       </c>
-      <c r="I234" s="2">
-        <v>0</v>
-      </c>
       <c r="J234">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K234" s="1">
         <v>100</v>
@@ -26879,9 +26042,6 @@
       <c r="H235" s="1">
         <v>0</v>
       </c>
-      <c r="I235" s="2">
-        <v>0</v>
-      </c>
       <c r="J235">
         <v>26</v>
       </c>
@@ -26911,9 +26071,6 @@
       <c r="H236" s="1">
         <v>0</v>
       </c>
-      <c r="I236" s="2">
-        <v>0</v>
-      </c>
       <c r="J236">
         <v>121</v>
       </c>
@@ -27174,7 +26331,7 @@
         <v>112</v>
       </c>
       <c r="D244">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -27188,11 +26345,8 @@
       <c r="H244" s="1">
         <v>0</v>
       </c>
-      <c r="I244" s="2">
-        <v>0</v>
-      </c>
       <c r="J244">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K244" s="1">
         <v>100</v>
@@ -27209,25 +26363,25 @@
         <v>113</v>
       </c>
       <c r="D245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E245">
         <v>21</v>
       </c>
       <c r="F245">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G245" s="1">
-        <v>52.5</v>
+        <v>53.8</v>
       </c>
       <c r="H245" s="1">
-        <v>47.5</v>
+        <v>46.2</v>
       </c>
       <c r="I245" s="2">
         <v>5.9</v>
       </c>
       <c r="J245">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K245" s="1">
         <v>100</v>
@@ -27279,7 +26433,7 @@
         <v>115</v>
       </c>
       <c r="D247">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E247">
         <v>14</v>
@@ -27288,16 +26442,16 @@
         <v>4</v>
       </c>
       <c r="G247" s="1">
-        <v>77.8</v>
+        <v>73.7</v>
       </c>
       <c r="H247" s="1">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="I247" s="2">
         <v>7.1</v>
       </c>
       <c r="J247">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K247" s="1">
         <v>100</v>
@@ -27381,25 +26535,25 @@
         <v>100</v>
       </c>
       <c r="D250">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E250">
         <v>95</v>
       </c>
       <c r="F250">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G250" s="1">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="H250" s="1">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="I250" s="2">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J250">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K250" s="1">
         <v>100</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -965,7 +965,7 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -974,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -983,10 +983,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -997,7 +997,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>92</v>
@@ -1006,19 +1006,19 @@
         <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>90.2</v>
+        <v>92</v>
       </c>
       <c r="H7" s="1">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2">
         <v>8.1</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1618,7 +1618,7 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         <v>9.1</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1650,7 +1650,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>9.1</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1790,7 +1790,7 @@
         <v>110</v>
       </c>
       <c r="D30">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E30">
         <v>31</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -1808,10 +1808,10 @@
         <v>9.4</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1822,7 +1822,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E31">
         <v>126</v>
@@ -1831,19 +1831,19 @@
         <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I31" s="2">
         <v>9</v>
       </c>
       <c r="J31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2443,7 +2443,7 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E49">
         <v>6</v>
@@ -2452,19 +2452,19 @@
         <v>6</v>
       </c>
       <c r="G49" s="1">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H49" s="1">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I49" s="2">
         <v>6.3</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2475,7 +2475,7 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50">
         <v>72</v>
@@ -2484,19 +2484,19 @@
         <v>52</v>
       </c>
       <c r="G50" s="1">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="H50" s="1">
-        <v>41.3</v>
+        <v>41.9</v>
       </c>
       <c r="I50" s="2">
         <v>6.4</v>
       </c>
       <c r="J50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -3341,7 +3341,7 @@
         <v>110</v>
       </c>
       <c r="D75">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E75">
         <v>31</v>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -3359,10 +3359,10 @@
         <v>9.6</v>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3478,7 +3478,7 @@
         <v>100</v>
       </c>
       <c r="D79">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E79">
         <v>230</v>
@@ -3487,19 +3487,19 @@
         <v>9</v>
       </c>
       <c r="G79" s="1">
-        <v>95.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="H79" s="1">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I79" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -4320,7 +4320,7 @@
         <v>110</v>
       </c>
       <c r="D104">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -4413,7 +4413,7 @@
         <v>100</v>
       </c>
       <c r="D107">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K107" s="1">
         <v>100</v>
@@ -5034,7 +5034,7 @@
         <v>99</v>
       </c>
       <c r="D125">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E125">
         <v>8</v>
@@ -5043,19 +5043,19 @@
         <v>4</v>
       </c>
       <c r="G125" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="H125" s="1">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="I125" s="2">
         <v>7.3</v>
       </c>
       <c r="J125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5066,7 +5066,7 @@
         <v>100</v>
       </c>
       <c r="D126">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E126">
         <v>161</v>
@@ -5075,19 +5075,19 @@
         <v>27</v>
       </c>
       <c r="G126" s="1">
-        <v>84.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H126" s="1">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="I126" s="2">
         <v>8.1</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5652,7 +5652,7 @@
         <v>110</v>
       </c>
       <c r="D143">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E143">
         <v>28</v>
@@ -5661,19 +5661,19 @@
         <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>84.8</v>
+        <v>90.3</v>
       </c>
       <c r="H143" s="1">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I143" s="2">
         <v>7.4</v>
       </c>
       <c r="J143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -5719,7 +5719,7 @@
         <v>100</v>
       </c>
       <c r="D145">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E145">
         <v>107</v>
@@ -5728,19 +5728,19 @@
         <v>3</v>
       </c>
       <c r="G145" s="1">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H145" s="1">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I145" s="2">
         <v>7.4</v>
       </c>
       <c r="J145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K145" s="1">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -5824,7 +5824,7 @@
         <v>110</v>
       </c>
       <c r="D148">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E148">
         <v>31</v>
@@ -5833,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
@@ -5842,10 +5842,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5856,7 +5856,7 @@
         <v>100</v>
       </c>
       <c r="D149">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E149">
         <v>98</v>
@@ -5865,7 +5865,7 @@
         <v>3</v>
       </c>
       <c r="G149" s="1">
-        <v>94.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H149" s="1">
         <v>2.9</v>
@@ -5874,10 +5874,10 @@
         <v>8.4</v>
       </c>
       <c r="J149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K149" s="1">
-        <v>2.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6894,7 +6894,7 @@
         <v>110</v>
       </c>
       <c r="D179">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E179">
         <v>31</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -6912,10 +6912,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -6926,7 +6926,7 @@
         <v>100</v>
       </c>
       <c r="D180">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E180">
         <v>209</v>
@@ -6935,19 +6935,19 @@
         <v>28</v>
       </c>
       <c r="G180" s="1">
-        <v>87.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H180" s="1">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="I180" s="2">
         <v>7.5</v>
       </c>
       <c r="J180">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K180" s="1">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7101,7 +7101,7 @@
         <v>99</v>
       </c>
       <c r="D185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E185">
         <v>12</v>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -7119,10 +7119,10 @@
         <v>7.6</v>
       </c>
       <c r="J185">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7133,7 +7133,7 @@
         <v>100</v>
       </c>
       <c r="D186">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E186">
         <v>132</v>
@@ -7142,7 +7142,7 @@
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -7151,10 +7151,10 @@
         <v>7.3</v>
       </c>
       <c r="J186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -8631,7 +8631,7 @@
         <v>99</v>
       </c>
       <c r="D230">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E230">
         <v>2</v>
@@ -8640,19 +8640,19 @@
         <v>10</v>
       </c>
       <c r="G230" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H230" s="1">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I230" s="2">
         <v>4.8</v>
       </c>
       <c r="J230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K230" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -8663,7 +8663,7 @@
         <v>100</v>
       </c>
       <c r="D231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -8672,19 +8672,19 @@
         <v>10</v>
       </c>
       <c r="G231" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H231" s="1">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I231" s="2">
         <v>4.8</v>
       </c>
       <c r="J231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -9930,7 +9930,7 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -9942,10 +9942,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -9959,7 +9959,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -9971,10 +9971,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -10526,7 +10526,7 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -10538,10 +10538,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -10555,7 +10555,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -10567,10 +10567,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -10683,7 +10683,7 @@
         <v>110</v>
       </c>
       <c r="D30">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -10695,10 +10695,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K30" s="1">
         <v>100</v>
@@ -10712,7 +10712,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -10724,10 +10724,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -11279,7 +11279,7 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J49">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -11308,7 +11308,7 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -11320,10 +11320,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J50">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -12099,7 +12099,7 @@
         <v>110</v>
       </c>
       <c r="D75">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -12111,10 +12111,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J75">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -12224,7 +12224,7 @@
         <v>100</v>
       </c>
       <c r="D79">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -12236,10 +12236,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="J79">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -13015,7 +13015,7 @@
         <v>110</v>
       </c>
       <c r="D104">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -13108,7 +13108,7 @@
         <v>100</v>
       </c>
       <c r="D107">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -13123,7 +13123,7 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K107" s="1">
         <v>100</v>
@@ -13678,7 +13678,7 @@
         <v>99</v>
       </c>
       <c r="D125">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -13690,10 +13690,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J125">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K125" s="1">
         <v>100</v>
@@ -13707,7 +13707,7 @@
         <v>100</v>
       </c>
       <c r="D126">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -13719,10 +13719,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J126">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K126" s="1">
         <v>100</v>
@@ -14242,7 +14242,7 @@
         <v>110</v>
       </c>
       <c r="D143">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -14254,10 +14254,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J143">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K143" s="1">
         <v>100</v>
@@ -14303,7 +14303,7 @@
         <v>100</v>
       </c>
       <c r="D145">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -14315,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="1">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="J145">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K145" s="1">
         <v>100</v>
@@ -14399,7 +14399,7 @@
         <v>110</v>
       </c>
       <c r="D148">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -14411,10 +14411,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J148">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K148" s="1">
         <v>100</v>
@@ -14428,7 +14428,7 @@
         <v>100</v>
       </c>
       <c r="D149">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -14440,10 +14440,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="1">
-        <v>97.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="J149">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K149" s="1">
         <v>100</v>
@@ -15376,7 +15376,7 @@
         <v>110</v>
       </c>
       <c r="D179">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -15388,10 +15388,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="J179">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K179" s="1">
         <v>100</v>
@@ -15405,7 +15405,7 @@
         <v>100</v>
       </c>
       <c r="D180">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -15417,10 +15417,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="1">
-        <v>98.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J180">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K180" s="1">
         <v>100</v>
@@ -15565,7 +15565,7 @@
         <v>99</v>
       </c>
       <c r="D185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -15577,10 +15577,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K185" s="1">
         <v>100</v>
@@ -15594,7 +15594,7 @@
         <v>100</v>
       </c>
       <c r="D186">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -15606,10 +15606,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="1">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="J186">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K186" s="1">
         <v>100</v>
@@ -16969,7 +16969,7 @@
         <v>99</v>
       </c>
       <c r="D230">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -16981,10 +16981,10 @@
         <v>0</v>
       </c>
       <c r="H230" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J230">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K230" s="1">
         <v>100</v>
@@ -16998,7 +16998,7 @@
         <v>100</v>
       </c>
       <c r="D231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -17010,10 +17010,10 @@
         <v>0</v>
       </c>
       <c r="H231" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="J231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>
@@ -18199,7 +18199,7 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -18208,7 +18208,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -18217,7 +18217,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -18231,7 +18231,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>92</v>
@@ -18240,16 +18240,16 @@
         <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>90.2</v>
+        <v>92</v>
       </c>
       <c r="H7" s="1">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I7" s="2">
         <v>8.1</v>
       </c>
       <c r="J7">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -18852,7 +18852,7 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>12</v>
@@ -18861,7 +18861,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -18870,7 +18870,7 @@
         <v>9.1</v>
       </c>
       <c r="J25">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -18884,7 +18884,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -18893,7 +18893,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -18902,7 +18902,7 @@
         <v>9.1</v>
       </c>
       <c r="J26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -19024,7 +19024,7 @@
         <v>110</v>
       </c>
       <c r="D30">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E30">
         <v>31</v>
@@ -19033,7 +19033,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -19042,7 +19042,7 @@
         <v>9.4</v>
       </c>
       <c r="J30">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K30" s="1">
         <v>100</v>
@@ -19056,7 +19056,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E31">
         <v>126</v>
@@ -19065,16 +19065,16 @@
         <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H31" s="1">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I31" s="2">
         <v>9</v>
       </c>
       <c r="J31">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K31" s="1">
         <v>100</v>
@@ -19677,7 +19677,7 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E49">
         <v>6</v>
@@ -19686,16 +19686,16 @@
         <v>6</v>
       </c>
       <c r="G49" s="1">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="H49" s="1">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I49" s="2">
         <v>6.3</v>
       </c>
       <c r="J49">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -19709,7 +19709,7 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50">
         <v>72</v>
@@ -19718,16 +19718,16 @@
         <v>52</v>
       </c>
       <c r="G50" s="1">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="H50" s="1">
-        <v>41.3</v>
+        <v>41.9</v>
       </c>
       <c r="I50" s="2">
         <v>6.4</v>
       </c>
       <c r="J50">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -20575,7 +20575,7 @@
         <v>110</v>
       </c>
       <c r="D75">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E75">
         <v>31</v>
@@ -20584,7 +20584,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -20593,7 +20593,7 @@
         <v>9.6</v>
       </c>
       <c r="J75">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K75" s="1">
         <v>100</v>
@@ -20712,7 +20712,7 @@
         <v>100</v>
       </c>
       <c r="D79">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E79">
         <v>230</v>
@@ -20721,16 +20721,16 @@
         <v>9</v>
       </c>
       <c r="G79" s="1">
-        <v>95.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="H79" s="1">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I79" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J79">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="K79" s="1">
         <v>100</v>
@@ -21554,7 +21554,7 @@
         <v>110</v>
       </c>
       <c r="D104">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -21569,7 +21569,7 @@
         <v>0</v>
       </c>
       <c r="J104">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K104" s="1">
         <v>100</v>
@@ -21647,7 +21647,7 @@
         <v>100</v>
       </c>
       <c r="D107">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -21662,7 +21662,7 @@
         <v>0</v>
       </c>
       <c r="J107">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K107" s="1">
         <v>100</v>
@@ -22268,7 +22268,7 @@
         <v>99</v>
       </c>
       <c r="D125">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E125">
         <v>8</v>
@@ -22277,16 +22277,16 @@
         <v>4</v>
       </c>
       <c r="G125" s="1">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="H125" s="1">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="I125" s="2">
         <v>7.3</v>
       </c>
       <c r="J125">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K125" s="1">
         <v>100</v>
@@ -22300,7 +22300,7 @@
         <v>100</v>
       </c>
       <c r="D126">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E126">
         <v>161</v>
@@ -22309,16 +22309,16 @@
         <v>27</v>
       </c>
       <c r="G126" s="1">
-        <v>84.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H126" s="1">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="I126" s="2">
         <v>8.1</v>
       </c>
       <c r="J126">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K126" s="1">
         <v>100</v>
@@ -22886,7 +22886,7 @@
         <v>110</v>
       </c>
       <c r="D143">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E143">
         <v>28</v>
@@ -22895,16 +22895,16 @@
         <v>3</v>
       </c>
       <c r="G143" s="1">
-        <v>84.8</v>
+        <v>90.3</v>
       </c>
       <c r="H143" s="1">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I143" s="2">
         <v>7.4</v>
       </c>
       <c r="J143">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K143" s="1">
         <v>100</v>
@@ -22953,7 +22953,7 @@
         <v>100</v>
       </c>
       <c r="D145">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E145">
         <v>107</v>
@@ -22962,16 +22962,16 @@
         <v>18</v>
       </c>
       <c r="G145" s="1">
-        <v>83.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H145" s="1">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="I145" s="2">
         <v>7.1</v>
       </c>
       <c r="J145">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K145" s="1">
         <v>100</v>
@@ -23058,7 +23058,7 @@
         <v>110</v>
       </c>
       <c r="D148">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E148">
         <v>31</v>
@@ -23067,7 +23067,7 @@
         <v>0</v>
       </c>
       <c r="G148" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
@@ -23076,7 +23076,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J148">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K148" s="1">
         <v>100</v>
@@ -23090,7 +23090,7 @@
         <v>100</v>
       </c>
       <c r="D149">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E149">
         <v>98</v>
@@ -23099,7 +23099,7 @@
         <v>3</v>
       </c>
       <c r="G149" s="1">
-        <v>94.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H149" s="1">
         <v>2.9</v>
@@ -23108,7 +23108,7 @@
         <v>8.4</v>
       </c>
       <c r="J149">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K149" s="1">
         <v>100</v>
@@ -24128,7 +24128,7 @@
         <v>110</v>
       </c>
       <c r="D179">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E179">
         <v>31</v>
@@ -24137,7 +24137,7 @@
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>93.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -24146,7 +24146,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J179">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K179" s="1">
         <v>100</v>
@@ -24160,7 +24160,7 @@
         <v>100</v>
       </c>
       <c r="D180">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E180">
         <v>209</v>
@@ -24169,16 +24169,16 @@
         <v>28</v>
       </c>
       <c r="G180" s="1">
-        <v>87.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H180" s="1">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="I180" s="2">
         <v>7.5</v>
       </c>
       <c r="J180">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K180" s="1">
         <v>100</v>
@@ -24335,7 +24335,7 @@
         <v>99</v>
       </c>
       <c r="D185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E185">
         <v>12</v>
@@ -24344,7 +24344,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -24353,7 +24353,7 @@
         <v>7.6</v>
       </c>
       <c r="J185">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K185" s="1">
         <v>100</v>
@@ -24367,7 +24367,7 @@
         <v>100</v>
       </c>
       <c r="D186">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E186">
         <v>132</v>
@@ -24376,7 +24376,7 @@
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -24385,7 +24385,7 @@
         <v>7.3</v>
       </c>
       <c r="J186">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K186" s="1">
         <v>100</v>
@@ -25865,7 +25865,7 @@
         <v>99</v>
       </c>
       <c r="D230">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E230">
         <v>2</v>
@@ -25874,16 +25874,16 @@
         <v>10</v>
       </c>
       <c r="G230" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H230" s="1">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I230" s="2">
         <v>5.3</v>
       </c>
       <c r="J230">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K230" s="1">
         <v>100</v>
@@ -25897,7 +25897,7 @@
         <v>100</v>
       </c>
       <c r="D231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E231">
         <v>2</v>
@@ -25906,16 +25906,16 @@
         <v>10</v>
       </c>
       <c r="G231" s="1">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H231" s="1">
-        <v>71.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I231" s="2">
         <v>5.3</v>
       </c>
       <c r="J231">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -5003,13 +5003,13 @@
         <v>36</v>
       </c>
       <c r="E123">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F123">
         <v>2</v>
       </c>
       <c r="G123" s="1">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H123" s="1">
         <v>5.6</v>
@@ -5018,10 +5018,10 @@
         <v>8.6</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5105,13 +5105,13 @@
         <v>189</v>
       </c>
       <c r="E126">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F126">
         <v>27</v>
       </c>
       <c r="G126" s="1">
-        <v>85.2</v>
+        <v>85.7</v>
       </c>
       <c r="H126" s="1">
         <v>14.3</v>
@@ -5120,10 +5120,10 @@
         <v>8.1</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -7761,22 +7761,22 @@
         <v>14</v>
       </c>
       <c r="F203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G203" s="1">
         <v>73.7</v>
       </c>
       <c r="H203" s="1">
-        <v>21.1</v>
+        <v>26.3</v>
       </c>
       <c r="I203" s="2">
         <v>6.4</v>
       </c>
       <c r="J203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -7793,22 +7793,22 @@
         <v>84</v>
       </c>
       <c r="F204">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G204" s="1">
         <v>63.2</v>
       </c>
       <c r="H204" s="1">
-        <v>36.1</v>
+        <v>36.8</v>
       </c>
       <c r="I204" s="2">
         <v>5.9</v>
       </c>
       <c r="J204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -9268,22 +9268,22 @@
         <v>14</v>
       </c>
       <c r="F247">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G247" s="1">
         <v>73.7</v>
       </c>
       <c r="H247" s="1">
-        <v>21.1</v>
+        <v>26.3</v>
       </c>
       <c r="I247" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9370,22 +9370,22 @@
         <v>118</v>
       </c>
       <c r="F250">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G250" s="1">
         <v>62.8</v>
       </c>
       <c r="H250" s="1">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="I250" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -10387,22 +10387,25 @@
         <v>38</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>18.4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -10419,22 +10422,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>18.4</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.1</v>
       </c>
       <c r="J18">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -10448,25 +10454,25 @@
         <v>160</v>
       </c>
       <c r="E19">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="F19">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="G19" s="1">
-        <v>49.4</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H19" s="1">
-        <v>50.6</v>
+        <v>11.9</v>
       </c>
       <c r="I19" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>47.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -10929,22 +10935,25 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>43.6</v>
+      </c>
+      <c r="I33" s="2">
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -10961,22 +10970,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F34">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>61.5</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>38.5</v>
+      </c>
+      <c r="I34" s="2">
+        <v>6.3</v>
       </c>
       <c r="J34">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -10993,22 +11005,25 @@
         <v>37</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>59.5</v>
+      </c>
+      <c r="I35" s="2">
+        <v>6.2</v>
       </c>
       <c r="J35">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -11057,25 +11072,25 @@
         <v>170</v>
       </c>
       <c r="E37">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="F37">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="G37" s="1">
-        <v>14.7</v>
+        <v>50.6</v>
       </c>
       <c r="H37" s="1">
-        <v>85.3</v>
+        <v>49.4</v>
       </c>
       <c r="I37" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>67.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -13261,22 +13276,25 @@
         <v>30</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F101">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G101" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H101" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I101" s="2">
+        <v>6.3</v>
       </c>
       <c r="J101">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -13293,22 +13311,25 @@
         <v>38</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F102">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G102" s="1">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="H102" s="1">
-        <v>100</v>
+        <v>5.3</v>
+      </c>
+      <c r="I102" s="2">
+        <v>8.1</v>
       </c>
       <c r="J102">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -13325,22 +13346,25 @@
         <v>25</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F103">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H103" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I103" s="2">
+        <v>7.3</v>
       </c>
       <c r="J103">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -13357,22 +13381,25 @@
         <v>31</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F104">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="G104" s="1">
-        <v>0</v>
+        <v>90.3</v>
       </c>
       <c r="H104" s="1">
-        <v>100</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I104" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J104">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -13389,22 +13416,25 @@
         <v>36</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F105">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H105" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I105" s="2">
+        <v>7.6</v>
       </c>
       <c r="J105">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -13421,22 +13451,25 @@
         <v>28</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F106">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H106" s="1">
-        <v>100</v>
+        <v>10.7</v>
+      </c>
+      <c r="I106" s="2">
+        <v>6.5</v>
       </c>
       <c r="J106">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -13450,22 +13483,25 @@
         <v>188</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F107">
-        <v>188</v>
+        <v>32</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H107" s="1">
-        <v>100</v>
+        <v>17</v>
+      </c>
+      <c r="I107" s="2">
+        <v>7.3</v>
       </c>
       <c r="J107">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -13482,22 +13518,25 @@
         <v>39</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F108">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G108" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H108" s="1">
-        <v>100</v>
+        <v>43.6</v>
+      </c>
+      <c r="I108" s="2">
+        <v>6.5</v>
       </c>
       <c r="J108">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -13514,22 +13553,25 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F109">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H109" s="1">
-        <v>100</v>
+        <v>13.9</v>
+      </c>
+      <c r="I109" s="2">
+        <v>6.9</v>
       </c>
       <c r="J109">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -13546,22 +13588,25 @@
         <v>30</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F110">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G110" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H110" s="1">
-        <v>100</v>
+        <v>6.7</v>
+      </c>
+      <c r="I110" s="2">
+        <v>6.8</v>
       </c>
       <c r="J110">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -13575,22 +13620,25 @@
         <v>105</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F111">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H111" s="1">
-        <v>100</v>
+        <v>22.9</v>
+      </c>
+      <c r="I111" s="2">
+        <v>6.7</v>
       </c>
       <c r="J111">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -13849,22 +13897,25 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F119">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G119" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H119" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I119" s="2">
+        <v>7.8</v>
       </c>
       <c r="J119">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -13881,22 +13932,25 @@
         <v>24</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F120">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G120" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H120" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I120" s="2">
+        <v>7.7</v>
       </c>
       <c r="J120">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -13913,22 +13967,25 @@
         <v>30</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F121">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="H121" s="1">
-        <v>100</v>
+        <v>3.3</v>
+      </c>
+      <c r="I121" s="2">
+        <v>7.6</v>
       </c>
       <c r="J121">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -13945,22 +14002,25 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F122">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G122" s="1">
-        <v>0</v>
+        <v>77.8</v>
       </c>
       <c r="H122" s="1">
-        <v>100</v>
+        <v>22.2</v>
+      </c>
+      <c r="I122" s="2">
+        <v>7.6</v>
       </c>
       <c r="J122">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -13977,22 +14037,25 @@
         <v>36</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F123">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G123" s="1">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="H123" s="1">
-        <v>97.2</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I123" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J123">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -14009,22 +14072,25 @@
         <v>33</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F124">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>84.8</v>
       </c>
       <c r="H124" s="1">
-        <v>100</v>
+        <v>15.2</v>
+      </c>
+      <c r="I124" s="2">
+        <v>8.1</v>
       </c>
       <c r="J124">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -14041,22 +14107,25 @@
         <v>12</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F125">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H125" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I125" s="2">
+        <v>8.1</v>
       </c>
       <c r="J125">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -14070,22 +14139,25 @@
         <v>189</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="F126">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="G126" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H126" s="1">
-        <v>99.5</v>
+        <v>13.2</v>
+      </c>
+      <c r="I126" s="2">
+        <v>8</v>
       </c>
       <c r="J126">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -14647,22 +14719,25 @@
         <v>31</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F143">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G143" s="1">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="H143" s="1">
-        <v>100</v>
+        <v>6.5</v>
+      </c>
+      <c r="I143" s="2">
+        <v>7.9</v>
       </c>
       <c r="J143">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -14711,25 +14786,25 @@
         <v>126</v>
       </c>
       <c r="E145">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="F145">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="G145" s="1">
-        <v>63.5</v>
+        <v>86.5</v>
       </c>
       <c r="H145" s="1">
-        <v>36.5</v>
+        <v>13.5</v>
       </c>
       <c r="I145" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J145">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>24.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -14883,22 +14958,25 @@
         <v>28</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F150">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G150" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H150" s="1">
-        <v>100</v>
+        <v>17.9</v>
+      </c>
+      <c r="I150" s="2">
+        <v>6.4</v>
       </c>
       <c r="J150">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -14912,22 +14990,25 @@
         <v>28</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F151">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H151" s="1">
-        <v>100</v>
+        <v>17.9</v>
+      </c>
+      <c r="I151" s="2">
+        <v>6.4</v>
       </c>
       <c r="J151">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -14944,22 +15025,25 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F152">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="H152" s="1">
-        <v>100</v>
+        <v>14.8</v>
+      </c>
+      <c r="I152" s="2">
+        <v>7.4</v>
       </c>
       <c r="J152">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -14976,22 +15060,25 @@
         <v>24</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F153">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H153" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I153" s="2">
+        <v>6.5</v>
       </c>
       <c r="J153">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -15008,22 +15095,25 @@
         <v>34</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F154">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G154" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H154" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I154" s="2">
+        <v>7.7</v>
       </c>
       <c r="J154">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -15040,22 +15130,25 @@
         <v>40</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F155">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H155" s="1">
-        <v>97.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="I155" s="2">
+        <v>7.8</v>
       </c>
       <c r="J155">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -15072,22 +15165,25 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F156">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H156" s="1">
-        <v>100</v>
+        <v>5.1</v>
+      </c>
+      <c r="I156" s="2">
+        <v>9</v>
       </c>
       <c r="J156">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -15104,22 +15200,25 @@
         <v>30</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F157">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G157" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H157" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I157" s="2">
+        <v>8</v>
       </c>
       <c r="J157">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -15133,22 +15232,25 @@
         <v>194</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="F158">
-        <v>193</v>
+        <v>15</v>
       </c>
       <c r="G158" s="1">
-        <v>0</v>
+        <v>91.8</v>
       </c>
       <c r="H158" s="1">
-        <v>99.5</v>
+        <v>7.7</v>
+      </c>
+      <c r="I158" s="2">
+        <v>7.7</v>
       </c>
       <c r="J158">
-        <v>194</v>
+        <v>1</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -15719,22 +15821,25 @@
         <v>39</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F175">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G175" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H175" s="1">
-        <v>100</v>
+        <v>25.6</v>
+      </c>
+      <c r="I175" s="2">
+        <v>6.4</v>
       </c>
       <c r="J175">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -15888,25 +15993,25 @@
         <v>239</v>
       </c>
       <c r="E180">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="F180">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="G180" s="1">
-        <v>73.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="H180" s="1">
-        <v>26.4</v>
+        <v>14.2</v>
       </c>
       <c r="I180" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J180">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>16.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -15923,22 +16028,25 @@
         <v>28</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F181">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H181" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I181" s="2">
+        <v>6.9</v>
       </c>
       <c r="J181">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -15955,22 +16063,25 @@
         <v>33</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F182">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G182" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H182" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I182" s="2">
+        <v>7.5</v>
       </c>
       <c r="J182">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -15987,22 +16098,25 @@
         <v>33</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F183">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G183" s="1">
-        <v>0</v>
+        <v>75.8</v>
       </c>
       <c r="H183" s="1">
-        <v>100</v>
+        <v>24.2</v>
+      </c>
+      <c r="I183" s="2">
+        <v>6.1</v>
       </c>
       <c r="J183">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -16054,22 +16168,25 @@
         <v>12</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F185">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G185" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H185" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I185" s="2">
+        <v>6</v>
       </c>
       <c r="J185">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -16083,25 +16200,25 @@
         <v>132</v>
       </c>
       <c r="E186">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="F186">
-        <v>116</v>
+        <v>22</v>
       </c>
       <c r="G186" s="1">
-        <v>12.1</v>
+        <v>83.3</v>
       </c>
       <c r="H186" s="1">
-        <v>87.90000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="I186" s="2">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J186">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="K186" s="1">
-        <v>80.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -16182,22 +16299,25 @@
         <v>42</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F189">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G189" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H189" s="1">
-        <v>100</v>
+        <v>2.4</v>
+      </c>
+      <c r="I189" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J189">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -16243,22 +16363,25 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F191">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="G191" s="1">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="H191" s="1">
-        <v>100</v>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="I191" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J191">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -16549,22 +16672,25 @@
         <v>36</v>
       </c>
       <c r="E200">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F200">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G200" s="1">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="H200" s="1">
-        <v>100</v>
+        <v>52.8</v>
+      </c>
+      <c r="I200" s="2">
+        <v>5.3</v>
       </c>
       <c r="J200">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K200" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -16581,22 +16707,25 @@
         <v>39</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F201">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G201" s="1">
-        <v>0</v>
+        <v>51.3</v>
       </c>
       <c r="H201" s="1">
-        <v>100</v>
+        <v>48.7</v>
+      </c>
+      <c r="I201" s="2">
+        <v>5.6</v>
       </c>
       <c r="J201">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K201" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -16613,22 +16742,25 @@
         <v>39</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F202">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G202" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="H202" s="1">
-        <v>100</v>
+        <v>66.7</v>
+      </c>
+      <c r="I202" s="2">
+        <v>5.4</v>
       </c>
       <c r="J202">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K202" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -16645,22 +16777,25 @@
         <v>19</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F203">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G203" s="1">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="H203" s="1">
-        <v>94.7</v>
+        <v>52.6</v>
+      </c>
+      <c r="I203" s="2">
+        <v>5.4</v>
       </c>
       <c r="J203">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -16674,22 +16809,25 @@
         <v>133</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F204">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="G204" s="1">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="H204" s="1">
-        <v>99.2</v>
+        <v>55.6</v>
+      </c>
+      <c r="I204" s="2">
+        <v>5.4</v>
       </c>
       <c r="J204">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -17129,10 +17267,10 @@
         <v>5.7</v>
       </c>
       <c r="J217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K217" s="1">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -17336,10 +17474,10 @@
         <v>6.4</v>
       </c>
       <c r="J223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -17790,22 +17928,25 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F237">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G237" s="1">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="H237" s="1">
-        <v>100</v>
+        <v>33.3</v>
+      </c>
+      <c r="I237" s="2">
+        <v>7.1</v>
       </c>
       <c r="J237">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K237" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -17822,22 +17963,25 @@
         <v>24</v>
       </c>
       <c r="E238">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F238">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G238" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H238" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I238" s="2">
+        <v>7.4</v>
       </c>
       <c r="J238">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K238" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -17918,22 +18062,25 @@
         <v>25</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F241">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G241" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H241" s="1">
-        <v>100</v>
+        <v>16</v>
+      </c>
+      <c r="I241" s="2">
+        <v>7.9</v>
       </c>
       <c r="J241">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K241" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -17982,25 +18129,25 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F243">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="G243" s="1">
-        <v>16.6</v>
+        <v>48.1</v>
       </c>
       <c r="H243" s="1">
-        <v>83.40000000000001</v>
+        <v>51.9</v>
       </c>
       <c r="I243" s="2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J243">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="K243" s="1">
-        <v>80.09999999999999</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -18017,22 +18164,25 @@
         <v>39</v>
       </c>
       <c r="E244">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F244">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="G244" s="1">
-        <v>0</v>
+        <v>56.4</v>
       </c>
       <c r="H244" s="1">
-        <v>97.40000000000001</v>
+        <v>43.6</v>
+      </c>
+      <c r="I244" s="2">
+        <v>5.8</v>
       </c>
       <c r="J244">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K244" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -18049,22 +18199,25 @@
         <v>39</v>
       </c>
       <c r="E245">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F245">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G245" s="1">
-        <v>0</v>
+        <v>35.9</v>
       </c>
       <c r="H245" s="1">
-        <v>100</v>
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I245" s="2">
+        <v>5.4</v>
       </c>
       <c r="J245">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K245" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -18081,22 +18234,25 @@
         <v>37</v>
       </c>
       <c r="E246">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F246">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G246" s="1">
-        <v>0</v>
+        <v>40.5</v>
       </c>
       <c r="H246" s="1">
-        <v>100</v>
+        <v>59.5</v>
+      </c>
+      <c r="I246" s="2">
+        <v>5.6</v>
       </c>
       <c r="J246">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K246" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -18113,22 +18269,25 @@
         <v>19</v>
       </c>
       <c r="E247">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F247">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G247" s="1">
-        <v>0</v>
+        <v>47.4</v>
       </c>
       <c r="H247" s="1">
-        <v>94.7</v>
+        <v>52.6</v>
+      </c>
+      <c r="I247" s="2">
+        <v>6.1</v>
       </c>
       <c r="J247">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K247" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -18145,22 +18304,25 @@
         <v>24</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F248">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G248" s="1">
-        <v>0</v>
+        <v>70.8</v>
       </c>
       <c r="H248" s="1">
-        <v>100</v>
+        <v>29.2</v>
+      </c>
+      <c r="I248" s="2">
+        <v>6</v>
       </c>
       <c r="J248">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K248" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -18177,22 +18339,25 @@
         <v>30</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F249">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G249" s="1">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="H249" s="1">
-        <v>100</v>
+        <v>6.7</v>
+      </c>
+      <c r="I249" s="2">
+        <v>6.9</v>
       </c>
       <c r="J249">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K249" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -18206,22 +18371,25 @@
         <v>188</v>
       </c>
       <c r="E250">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F250">
-        <v>186</v>
+        <v>83</v>
       </c>
       <c r="G250" s="1">
-        <v>0</v>
+        <v>55.9</v>
       </c>
       <c r="H250" s="1">
-        <v>98.90000000000001</v>
+        <v>44.1</v>
+      </c>
+      <c r="I250" s="2">
+        <v>6</v>
       </c>
       <c r="J250">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K250" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -19223,19 +19391,19 @@
         <v>38</v>
       </c>
       <c r="E17">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1">
-        <v>78.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H17" s="1">
-        <v>21.1</v>
+        <v>18.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
         <v>38</v>
@@ -19258,19 +19426,19 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>92.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="H18" s="1">
-        <v>7.9</v>
+        <v>15.8</v>
       </c>
       <c r="I18" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>38</v>
@@ -19290,16 +19458,16 @@
         <v>160</v>
       </c>
       <c r="E19">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G19" s="1">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="H19" s="1">
-        <v>10</v>
+        <v>11.2</v>
       </c>
       <c r="I19" s="2">
         <v>7.9</v>
@@ -19771,19 +19939,19 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" s="1">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="H33" s="1">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="I33" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J33">
         <v>39</v>
@@ -19806,19 +19974,19 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F34">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G34" s="1">
-        <v>64.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="H34" s="1">
-        <v>35.9</v>
+        <v>38.5</v>
       </c>
       <c r="I34" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J34">
         <v>39</v>
@@ -19841,16 +20009,16 @@
         <v>37</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F35">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G35" s="1">
-        <v>54.1</v>
+        <v>40.5</v>
       </c>
       <c r="H35" s="1">
-        <v>45.9</v>
+        <v>59.5</v>
       </c>
       <c r="I35" s="2">
         <v>5.9</v>
@@ -19908,16 +20076,16 @@
         <v>170</v>
       </c>
       <c r="E37">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F37">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G37" s="1">
-        <v>54.7</v>
+        <v>50.6</v>
       </c>
       <c r="H37" s="1">
-        <v>45.3</v>
+        <v>49.4</v>
       </c>
       <c r="I37" s="2">
         <v>6.4</v>
@@ -22118,16 +22286,16 @@
         <v>30</v>
       </c>
       <c r="E101">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F101">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G101" s="1">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="H101" s="1">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="I101" s="2">
         <v>6.5</v>
@@ -22165,7 +22333,7 @@
         <v>5.3</v>
       </c>
       <c r="I102" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J102">
         <v>38</v>
@@ -22188,19 +22356,19 @@
         <v>25</v>
       </c>
       <c r="E103">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G103" s="1">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H103" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I103" s="2">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="J103">
         <v>25</v>
@@ -22223,19 +22391,19 @@
         <v>31</v>
       </c>
       <c r="E104">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F104">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G104" s="1">
-        <v>83.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="H104" s="1">
-        <v>16.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I104" s="2">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="J104">
         <v>31</v>
@@ -22258,19 +22426,19 @@
         <v>36</v>
       </c>
       <c r="E105">
+        <v>27</v>
+      </c>
+      <c r="F105">
+        <v>9</v>
+      </c>
+      <c r="G105" s="1">
+        <v>75</v>
+      </c>
+      <c r="H105" s="1">
         <v>25</v>
       </c>
-      <c r="F105">
-        <v>11</v>
-      </c>
-      <c r="G105" s="1">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="H105" s="1">
-        <v>30.6</v>
-      </c>
       <c r="I105" s="2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="J105">
         <v>36</v>
@@ -22305,7 +22473,7 @@
         <v>10.7</v>
       </c>
       <c r="I106" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J106">
         <v>28</v>
@@ -22325,19 +22493,19 @@
         <v>188</v>
       </c>
       <c r="E107">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F107">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G107" s="1">
-        <v>81.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="H107" s="1">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="I107" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J107">
         <v>188</v>
@@ -22360,16 +22528,16 @@
         <v>39</v>
       </c>
       <c r="E108">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F108">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G108" s="1">
-        <v>53.8</v>
+        <v>56.4</v>
       </c>
       <c r="H108" s="1">
-        <v>46.2</v>
+        <v>43.6</v>
       </c>
       <c r="I108" s="2">
         <v>6.4</v>
@@ -22395,19 +22563,19 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F109">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G109" s="1">
-        <v>88.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H109" s="1">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="I109" s="2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J109">
         <v>36</v>
@@ -22442,7 +22610,7 @@
         <v>6.7</v>
       </c>
       <c r="I110" s="2">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J110">
         <v>30</v>
@@ -22474,7 +22642,7 @@
         <v>22.9</v>
       </c>
       <c r="I111" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J111">
         <v>105</v>
@@ -22739,19 +22907,19 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" s="1">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H119" s="1">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="I119" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J119">
         <v>27</v>
@@ -22774,19 +22942,19 @@
         <v>24</v>
       </c>
       <c r="E120">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F120">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G120" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H120" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I120" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J120">
         <v>24</v>
@@ -22821,7 +22989,7 @@
         <v>3.3</v>
       </c>
       <c r="I121" s="2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J121">
         <v>30</v>
@@ -22844,19 +23012,19 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G122" s="1">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="H122" s="1">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="I122" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J122">
         <v>27</v>
@@ -22882,16 +23050,16 @@
         <v>33</v>
       </c>
       <c r="F123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G123" s="1">
         <v>91.7</v>
       </c>
       <c r="H123" s="1">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I123" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J123">
         <v>36</v>
@@ -22914,19 +23082,19 @@
         <v>33</v>
       </c>
       <c r="E124">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F124">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G124" s="1">
-        <v>72.7</v>
+        <v>84.8</v>
       </c>
       <c r="H124" s="1">
-        <v>27.3</v>
+        <v>15.2</v>
       </c>
       <c r="I124" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J124">
         <v>33</v>
@@ -22949,19 +23117,19 @@
         <v>12</v>
       </c>
       <c r="E125">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H125" s="1">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I125" s="2">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="J125">
         <v>12</v>
@@ -22981,19 +23149,19 @@
         <v>189</v>
       </c>
       <c r="E126">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F126">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G126" s="1">
-        <v>85.2</v>
+        <v>86.8</v>
       </c>
       <c r="H126" s="1">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="I126" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J126">
         <v>189</v>
@@ -23567,19 +23735,19 @@
         <v>31</v>
       </c>
       <c r="E143">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G143" s="1">
-        <v>90.3</v>
+        <v>93.5</v>
       </c>
       <c r="H143" s="1">
-        <v>9.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="I143" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J143">
         <v>31</v>
@@ -23634,19 +23802,19 @@
         <v>126</v>
       </c>
       <c r="E145">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F145">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G145" s="1">
-        <v>85.7</v>
+        <v>86.5</v>
       </c>
       <c r="H145" s="1">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="I145" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J145">
         <v>126</v>
@@ -23818,7 +23986,7 @@
         <v>17.9</v>
       </c>
       <c r="I150" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J150">
         <v>28</v>
@@ -23850,7 +24018,7 @@
         <v>17.9</v>
       </c>
       <c r="I151" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J151">
         <v>28</v>
@@ -23873,19 +24041,19 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F152">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G152" s="1">
-        <v>77.8</v>
+        <v>85.2</v>
       </c>
       <c r="H152" s="1">
-        <v>22.2</v>
+        <v>14.8</v>
       </c>
       <c r="I152" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J152">
         <v>27</v>
@@ -23908,19 +24076,19 @@
         <v>24</v>
       </c>
       <c r="E153">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G153" s="1">
-        <v>91.7</v>
+        <v>87.5</v>
       </c>
       <c r="H153" s="1">
-        <v>8.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="I153" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="J153">
         <v>24</v>
@@ -23955,7 +24123,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I154" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J154">
         <v>34</v>
@@ -23990,7 +24158,7 @@
         <v>7.5</v>
       </c>
       <c r="I155" s="2">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="J155">
         <v>40</v>
@@ -24013,19 +24181,19 @@
         <v>39</v>
       </c>
       <c r="E156">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
-        <v>92.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H156" s="1">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="I156" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J156">
         <v>39</v>
@@ -24048,19 +24216,19 @@
         <v>30</v>
       </c>
       <c r="E157">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H157" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I157" s="2">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="J157">
         <v>30</v>
@@ -24080,19 +24248,19 @@
         <v>194</v>
       </c>
       <c r="E158">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F158">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G158" s="1">
-        <v>90.2</v>
+        <v>91.8</v>
       </c>
       <c r="H158" s="1">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I158" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J158">
         <v>194</v>
@@ -24669,16 +24837,16 @@
         <v>39</v>
       </c>
       <c r="E175">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F175">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G175" s="1">
-        <v>82.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H175" s="1">
-        <v>17.9</v>
+        <v>25.6</v>
       </c>
       <c r="I175" s="2">
         <v>6.7</v>
@@ -24841,16 +25009,16 @@
         <v>239</v>
       </c>
       <c r="E180">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F180">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G180" s="1">
-        <v>87</v>
+        <v>85.8</v>
       </c>
       <c r="H180" s="1">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="I180" s="2">
         <v>7.6</v>
@@ -24888,7 +25056,7 @@
         <v>0</v>
       </c>
       <c r="I181" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J181">
         <v>28</v>
@@ -24923,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="I182" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J182">
         <v>33</v>
@@ -24946,19 +25114,19 @@
         <v>33</v>
       </c>
       <c r="E183">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G183" s="1">
-        <v>100</v>
+        <v>84.8</v>
       </c>
       <c r="H183" s="1">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="I183" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J183">
         <v>33</v>
@@ -25016,19 +25184,19 @@
         <v>12</v>
       </c>
       <c r="E185">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G185" s="1">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="H185" s="1">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I185" s="2">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J185">
         <v>12</v>
@@ -25048,19 +25216,19 @@
         <v>132</v>
       </c>
       <c r="E186">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F186">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G186" s="1">
-        <v>92.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H186" s="1">
-        <v>7.6</v>
+        <v>14.4</v>
       </c>
       <c r="I186" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J186">
         <v>132</v>
@@ -25153,19 +25321,19 @@
         <v>42</v>
       </c>
       <c r="E189">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F189">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G189" s="1">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H189" s="1">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="I189" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J189">
         <v>42</v>
@@ -25220,16 +25388,16 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F191">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G191" s="1">
-        <v>86.3</v>
+        <v>87.7</v>
       </c>
       <c r="H191" s="1">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="I191" s="2">
         <v>8.199999999999999</v>
@@ -25529,19 +25697,19 @@
         <v>36</v>
       </c>
       <c r="E200">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F200">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G200" s="1">
-        <v>61.1</v>
+        <v>47.2</v>
       </c>
       <c r="H200" s="1">
-        <v>38.9</v>
+        <v>52.8</v>
       </c>
       <c r="I200" s="2">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="J200">
         <v>36</v>
@@ -25564,19 +25732,19 @@
         <v>39</v>
       </c>
       <c r="E201">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F201">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G201" s="1">
-        <v>74.40000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="H201" s="1">
-        <v>25.6</v>
+        <v>48.7</v>
       </c>
       <c r="I201" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J201">
         <v>39</v>
@@ -25599,19 +25767,19 @@
         <v>39</v>
       </c>
       <c r="E202">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F202">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G202" s="1">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="H202" s="1">
-        <v>51.3</v>
+        <v>66.7</v>
       </c>
       <c r="I202" s="2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J202">
         <v>39</v>
@@ -25634,19 +25802,19 @@
         <v>19</v>
       </c>
       <c r="E203">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F203">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G203" s="1">
-        <v>73.7</v>
+        <v>47.4</v>
       </c>
       <c r="H203" s="1">
-        <v>21.1</v>
+        <v>52.6</v>
       </c>
       <c r="I203" s="2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J203">
         <v>19</v>
@@ -25666,19 +25834,19 @@
         <v>133</v>
       </c>
       <c r="E204">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="F204">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="G204" s="1">
-        <v>63.2</v>
+        <v>44.4</v>
       </c>
       <c r="H204" s="1">
-        <v>36.1</v>
+        <v>55.6</v>
       </c>
       <c r="I204" s="2">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J204">
         <v>133</v>
@@ -26794,19 +26962,19 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F237">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G237" s="1">
-        <v>81.5</v>
+        <v>66.7</v>
       </c>
       <c r="H237" s="1">
-        <v>18.5</v>
+        <v>33.3</v>
       </c>
       <c r="I237" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J237">
         <v>27</v>
@@ -26829,19 +26997,19 @@
         <v>24</v>
       </c>
       <c r="E238">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F238">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G238" s="1">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H238" s="1">
-        <v>16.7</v>
+        <v>25</v>
       </c>
       <c r="I238" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J238">
         <v>24</v>
@@ -26934,19 +27102,19 @@
         <v>25</v>
       </c>
       <c r="E241">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F241">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G241" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H241" s="1">
+        <v>16</v>
+      </c>
+      <c r="I241" s="2">
         <v>8</v>
-      </c>
-      <c r="I241" s="2">
-        <v>7.8</v>
       </c>
       <c r="J241">
         <v>25</v>
@@ -27001,16 +27169,16 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F243">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G243" s="1">
-        <v>86.7</v>
+        <v>82.3</v>
       </c>
       <c r="H243" s="1">
-        <v>13.3</v>
+        <v>17.7</v>
       </c>
       <c r="I243" s="2">
         <v>7.7</v>
@@ -27036,19 +27204,19 @@
         <v>39</v>
       </c>
       <c r="E244">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F244">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G244" s="1">
-        <v>59</v>
+        <v>56.4</v>
       </c>
       <c r="H244" s="1">
-        <v>41</v>
+        <v>43.6</v>
       </c>
       <c r="I244" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J244">
         <v>39</v>
@@ -27071,19 +27239,19 @@
         <v>39</v>
       </c>
       <c r="E245">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F245">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G245" s="1">
-        <v>53.8</v>
+        <v>35.9</v>
       </c>
       <c r="H245" s="1">
-        <v>46.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I245" s="2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J245">
         <v>39</v>
@@ -27106,19 +27274,19 @@
         <v>37</v>
       </c>
       <c r="E246">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F246">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G246" s="1">
-        <v>35.1</v>
+        <v>40.5</v>
       </c>
       <c r="H246" s="1">
-        <v>64.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I246" s="2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J246">
         <v>37</v>
@@ -27141,19 +27309,19 @@
         <v>19</v>
       </c>
       <c r="E247">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F247">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G247" s="1">
-        <v>73.7</v>
+        <v>47.4</v>
       </c>
       <c r="H247" s="1">
-        <v>21.1</v>
+        <v>52.6</v>
       </c>
       <c r="I247" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J247">
         <v>19</v>
@@ -27176,19 +27344,19 @@
         <v>24</v>
       </c>
       <c r="E248">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F248">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G248" s="1">
-        <v>79.2</v>
+        <v>70.8</v>
       </c>
       <c r="H248" s="1">
-        <v>20.8</v>
+        <v>29.2</v>
       </c>
       <c r="I248" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J248">
         <v>24</v>
@@ -27223,7 +27391,7 @@
         <v>6.7</v>
       </c>
       <c r="I249" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J249">
         <v>30</v>
@@ -27243,19 +27411,19 @@
         <v>188</v>
       </c>
       <c r="E250">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F250">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="G250" s="1">
-        <v>62.8</v>
+        <v>55.9</v>
       </c>
       <c r="H250" s="1">
-        <v>36.7</v>
+        <v>44.1</v>
       </c>
       <c r="I250" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J250">
         <v>188</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -10399,13 +10399,13 @@
         <v>18.4</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -10422,25 +10422,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="1">
-        <v>81.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="H18" s="1">
-        <v>18.4</v>
+        <v>15.8</v>
       </c>
       <c r="I18" s="2">
         <v>7.1</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -10454,25 +10454,25 @@
         <v>160</v>
       </c>
       <c r="E19">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G19" s="1">
-        <v>88.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="H19" s="1">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -11658,22 +11658,25 @@
         <v>34</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F54">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>91.2</v>
       </c>
       <c r="H54" s="1">
-        <v>100</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I54" s="2">
+        <v>8.5</v>
       </c>
       <c r="J54">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -11792,25 +11795,25 @@
         <v>228</v>
       </c>
       <c r="E58">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F58">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G58" s="1">
-        <v>40.8</v>
+        <v>54.4</v>
       </c>
       <c r="H58" s="1">
-        <v>59.2</v>
+        <v>45.6</v>
       </c>
       <c r="I58" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J58">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>14.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -16098,25 +16101,25 @@
         <v>33</v>
       </c>
       <c r="E183">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F183">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G183" s="1">
-        <v>75.8</v>
+        <v>81.8</v>
       </c>
       <c r="H183" s="1">
-        <v>24.2</v>
+        <v>18.2</v>
       </c>
       <c r="I183" s="2">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J183">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -16200,25 +16203,25 @@
         <v>132</v>
       </c>
       <c r="E186">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F186">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G186" s="1">
-        <v>83.3</v>
+        <v>84.8</v>
       </c>
       <c r="H186" s="1">
-        <v>16.7</v>
+        <v>15.2</v>
       </c>
       <c r="I186" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J186">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>2.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -16235,22 +16238,25 @@
         <v>30</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F187">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G187" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H187" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I187" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J187">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -16267,22 +16273,25 @@
         <v>42</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F188">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G188" s="1">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H188" s="1">
-        <v>100</v>
+        <v>2.4</v>
+      </c>
+      <c r="I188" s="2">
+        <v>9.4</v>
       </c>
       <c r="J188">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -16334,22 +16343,25 @@
         <v>32</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F190">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G190" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H190" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I190" s="2">
+        <v>7.7</v>
       </c>
       <c r="J190">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -16363,25 +16375,25 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="F191">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="G191" s="1">
-        <v>28.1</v>
+        <v>89</v>
       </c>
       <c r="H191" s="1">
-        <v>71.90000000000001</v>
+        <v>11</v>
       </c>
       <c r="I191" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J191">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>71.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -17494,22 +17506,25 @@
         <v>25</v>
       </c>
       <c r="E224">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F224">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G224" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H224" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I224" s="2">
+        <v>7.9</v>
       </c>
       <c r="J224">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K224" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -17526,22 +17541,25 @@
         <v>17</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F225">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G225" s="1">
-        <v>0</v>
+        <v>88.2</v>
       </c>
       <c r="H225" s="1">
-        <v>100</v>
+        <v>11.8</v>
+      </c>
+      <c r="I225" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J225">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K225" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -17555,22 +17573,25 @@
         <v>42</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F226">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="G226" s="1">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="H226" s="1">
-        <v>100</v>
+        <v>4.8</v>
+      </c>
+      <c r="I226" s="2">
+        <v>8</v>
       </c>
       <c r="J226">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K226" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -17998,22 +18019,25 @@
         <v>39</v>
       </c>
       <c r="E239">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F239">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="G239" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H239" s="1">
-        <v>100</v>
+        <v>5.1</v>
+      </c>
+      <c r="I239" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J239">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K239" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -18030,22 +18054,25 @@
         <v>30</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F240">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G240" s="1">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="H240" s="1">
-        <v>100</v>
+        <v>13.3</v>
+      </c>
+      <c r="I240" s="2">
+        <v>7.7</v>
       </c>
       <c r="J240">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K240" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -18129,25 +18156,25 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="F243">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="G243" s="1">
-        <v>48.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H243" s="1">
-        <v>51.9</v>
+        <v>17.1</v>
       </c>
       <c r="I243" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J243">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K243" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -20662,19 +20689,19 @@
         <v>34</v>
       </c>
       <c r="E54">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G54" s="1">
-        <v>88.2</v>
+        <v>91.2</v>
       </c>
       <c r="H54" s="1">
-        <v>11.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I54" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J54">
         <v>34</v>
@@ -20799,19 +20826,19 @@
         <v>228</v>
       </c>
       <c r="E58">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F58">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G58" s="1">
-        <v>53.9</v>
+        <v>54.4</v>
       </c>
       <c r="H58" s="1">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="I58" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J58">
         <v>228</v>
@@ -25114,19 +25141,19 @@
         <v>33</v>
       </c>
       <c r="E183">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G183" s="1">
-        <v>84.8</v>
+        <v>81.8</v>
       </c>
       <c r="H183" s="1">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="I183" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J183">
         <v>33</v>
@@ -25216,19 +25243,19 @@
         <v>132</v>
       </c>
       <c r="E186">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F186">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G186" s="1">
-        <v>85.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H186" s="1">
-        <v>14.4</v>
+        <v>15.2</v>
       </c>
       <c r="I186" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J186">
         <v>132</v>
@@ -25263,7 +25290,7 @@
         <v>20</v>
       </c>
       <c r="I187" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J187">
         <v>30</v>
@@ -25298,7 +25325,7 @@
         <v>2.4</v>
       </c>
       <c r="I188" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J188">
         <v>42</v>
@@ -25356,19 +25383,19 @@
         <v>32</v>
       </c>
       <c r="E190">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F190">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G190" s="1">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="H190" s="1">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="I190" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J190">
         <v>32</v>
@@ -25388,19 +25415,19 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F191">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G191" s="1">
-        <v>87.7</v>
+        <v>89</v>
       </c>
       <c r="H191" s="1">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="I191" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J191">
         <v>146</v>
@@ -26519,16 +26546,16 @@
         <v>25</v>
       </c>
       <c r="E224">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G224" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H224" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I224" s="2">
         <v>8.6</v>
@@ -26566,7 +26593,7 @@
         <v>11.8</v>
       </c>
       <c r="I225" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J225">
         <v>17</v>
@@ -26586,19 +26613,19 @@
         <v>42</v>
       </c>
       <c r="E226">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G226" s="1">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="H226" s="1">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="I226" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J226">
         <v>42</v>
@@ -27067,19 +27094,19 @@
         <v>30</v>
       </c>
       <c r="E240">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F240">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G240" s="1">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="H240" s="1">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="I240" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J240">
         <v>30</v>
@@ -27169,16 +27196,16 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F243">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G243" s="1">
-        <v>82.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H243" s="1">
-        <v>17.7</v>
+        <v>17.1</v>
       </c>
       <c r="I243" s="2">
         <v>7.7</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -13072,25 +13072,25 @@
         <v>36</v>
       </c>
       <c r="E95">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F95">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G95" s="1">
-        <v>33.3</v>
+        <v>72.2</v>
       </c>
       <c r="H95" s="1">
-        <v>66.7</v>
+        <v>27.8</v>
       </c>
       <c r="I95" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J95">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -13189,13 +13189,13 @@
         <v>31.2</v>
       </c>
       <c r="I98" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -13244,25 +13244,25 @@
         <v>155</v>
       </c>
       <c r="E100">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F100">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G100" s="1">
-        <v>73.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H100" s="1">
-        <v>26.5</v>
+        <v>17.4</v>
       </c>
       <c r="I100" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -14177,22 +14177,25 @@
         <v>24</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F127">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G127" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H127" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I127" s="2">
+        <v>7.1</v>
       </c>
       <c r="J127">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K127" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -14206,22 +14209,25 @@
         <v>24</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F128">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G128" s="1">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="H128" s="1">
-        <v>100</v>
+        <v>16.7</v>
+      </c>
+      <c r="I128" s="2">
+        <v>7.1</v>
       </c>
       <c r="J128">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K128" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -22106,19 +22112,19 @@
         <v>36</v>
       </c>
       <c r="E95">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F95">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G95" s="1">
-        <v>86.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="H95" s="1">
-        <v>13.9</v>
+        <v>27.8</v>
       </c>
       <c r="I95" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J95">
         <v>36</v>
@@ -22211,16 +22217,16 @@
         <v>16</v>
       </c>
       <c r="E98">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G98" s="1">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="H98" s="1">
-        <v>25</v>
+        <v>31.2</v>
       </c>
       <c r="I98" s="2">
         <v>7.3</v>
@@ -22278,16 +22284,16 @@
         <v>155</v>
       </c>
       <c r="E100">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F100">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G100" s="1">
-        <v>86.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H100" s="1">
-        <v>13.5</v>
+        <v>17.4</v>
       </c>
       <c r="I100" s="2">
         <v>7.5</v>
@@ -23211,19 +23217,19 @@
         <v>24</v>
       </c>
       <c r="E127">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F127">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G127" s="1">
-        <v>87.5</v>
+        <v>83.3</v>
       </c>
       <c r="H127" s="1">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I127" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J127">
         <v>24</v>
@@ -23243,19 +23249,19 @@
         <v>24</v>
       </c>
       <c r="E128">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F128">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G128" s="1">
-        <v>87.5</v>
+        <v>83.3</v>
       </c>
       <c r="H128" s="1">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="I128" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J128">
         <v>24</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -965,22 +965,22 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -997,19 +997,19 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7">
         <v>92</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>92</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I7" s="2">
         <v>8.1</v>
@@ -1618,10 +1618,10 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49">
         <v>6</v>
@@ -2452,19 +2452,19 @@
         <v>6</v>
       </c>
       <c r="G49" s="1">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="H49" s="1">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="I49" s="2">
         <v>6.3</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2475,7 +2475,7 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E50">
         <v>72</v>
@@ -2484,19 +2484,19 @@
         <v>52</v>
       </c>
       <c r="G50" s="1">
-        <v>58.1</v>
+        <v>57.6</v>
       </c>
       <c r="H50" s="1">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="I50" s="2">
         <v>6.4</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -5070,22 +5070,22 @@
         <v>99</v>
       </c>
       <c r="D125">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E125">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F125">
         <v>4</v>
       </c>
       <c r="G125" s="1">
-        <v>66.7</v>
+        <v>69.2</v>
       </c>
       <c r="H125" s="1">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="I125" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -5102,19 +5102,19 @@
         <v>100</v>
       </c>
       <c r="D126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E126">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F126">
         <v>27</v>
       </c>
       <c r="G126" s="1">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="H126" s="1">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="I126" s="2">
         <v>8.1</v>
@@ -5621,13 +5621,13 @@
         <v>30</v>
       </c>
       <c r="E141">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
@@ -5656,19 +5656,19 @@
         <v>38</v>
       </c>
       <c r="E142">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F142">
         <v>0</v>
       </c>
       <c r="G142" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H142" s="1">
         <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -5726,19 +5726,19 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G144" s="1">
-        <v>74.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H144" s="1">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I144" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -5758,19 +5758,19 @@
         <v>126</v>
       </c>
       <c r="E145">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G145" s="1">
-        <v>85.7</v>
+        <v>96</v>
       </c>
       <c r="H145" s="1">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="I145" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -6105,22 +6105,22 @@
         <v>36</v>
       </c>
       <c r="F155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G155" s="1">
         <v>90</v>
       </c>
       <c r="H155" s="1">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I155" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6207,22 +6207,22 @@
         <v>175</v>
       </c>
       <c r="F158">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G158" s="1">
         <v>90.2</v>
       </c>
       <c r="H158" s="1">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I158" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -7137,7 +7137,7 @@
         <v>99</v>
       </c>
       <c r="D185">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E185">
         <v>12</v>
@@ -7146,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -7155,10 +7155,10 @@
         <v>7.6</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7169,7 +7169,7 @@
         <v>100</v>
       </c>
       <c r="D186">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E186">
         <v>132</v>
@@ -7178,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -7187,10 +7187,10 @@
         <v>7.3</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K186" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -8676,22 +8676,22 @@
         <v>99</v>
       </c>
       <c r="D230">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F230">
         <v>10</v>
       </c>
       <c r="G230" s="1">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="H230" s="1">
-        <v>83.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I230" s="2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -8708,22 +8708,22 @@
         <v>100</v>
       </c>
       <c r="D231">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F231">
         <v>10</v>
       </c>
       <c r="G231" s="1">
-        <v>16.7</v>
+        <v>23.1</v>
       </c>
       <c r="H231" s="1">
-        <v>83.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I231" s="2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -9093,19 +9093,19 @@
         <v>36</v>
       </c>
       <c r="E242">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F242">
         <v>0</v>
       </c>
       <c r="G242" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H242" s="1">
         <v>0</v>
       </c>
       <c r="I242" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J242">
         <v>0</v>
@@ -9125,19 +9125,19 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F243">
         <v>18</v>
       </c>
       <c r="G243" s="1">
-        <v>86.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H243" s="1">
         <v>9.9</v>
       </c>
       <c r="I243" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J243">
         <v>0</v>
@@ -10005,22 +10005,22 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -10037,19 +10037,19 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7">
         <v>92</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>92</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I7" s="2">
         <v>7.7</v>
@@ -10536,7 +10536,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -10658,10 +10658,10 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -10673,7 +10673,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -10690,10 +10690,10 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -10705,7 +10705,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -11483,7 +11483,7 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49">
         <v>9</v>
@@ -11492,19 +11492,19 @@
         <v>3</v>
       </c>
       <c r="G49" s="1">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="H49" s="1">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="I49" s="2">
         <v>7.4</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -11515,7 +11515,7 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E50">
         <v>76</v>
@@ -11524,19 +11524,19 @@
         <v>48</v>
       </c>
       <c r="G50" s="1">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
       <c r="H50" s="1">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="I50" s="2">
         <v>7.1</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -12279,22 +12279,25 @@
         <v>30</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F72">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="H72" s="1">
-        <v>100</v>
+        <v>23.3</v>
+      </c>
+      <c r="I72" s="2">
+        <v>5.8</v>
       </c>
       <c r="J72">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -12518,25 +12521,25 @@
         <v>241</v>
       </c>
       <c r="E79">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="F79">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="G79" s="1">
-        <v>80.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H79" s="1">
-        <v>19.1</v>
+        <v>9.5</v>
       </c>
       <c r="I79" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J79">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K79" s="1">
-        <v>12.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -14107,22 +14110,22 @@
         <v>99</v>
       </c>
       <c r="D125">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E125">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F125">
         <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H125" s="1">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="I125" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -14139,10 +14142,10 @@
         <v>100</v>
       </c>
       <c r="D126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E126">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F126">
         <v>25</v>
@@ -14154,7 +14157,7 @@
         <v>13.2</v>
       </c>
       <c r="I126" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -14658,16 +14661,16 @@
         <v>30</v>
       </c>
       <c r="E141">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F141">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I141" s="2">
         <v>6.7</v>
@@ -14693,16 +14696,16 @@
         <v>38</v>
       </c>
       <c r="E142">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G142" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H142" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2">
         <v>8.300000000000001</v>
@@ -14763,16 +14766,16 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F144">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G144" s="1">
-        <v>74.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H144" s="1">
-        <v>25.9</v>
+        <v>7.4</v>
       </c>
       <c r="I144" s="2">
         <v>6.6</v>
@@ -14795,16 +14798,16 @@
         <v>126</v>
       </c>
       <c r="E145">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F145">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G145" s="1">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="H145" s="1">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I145" s="2">
         <v>7.4</v>
@@ -15142,22 +15145,22 @@
         <v>36</v>
       </c>
       <c r="F155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G155" s="1">
         <v>90</v>
       </c>
       <c r="H155" s="1">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I155" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -15244,22 +15247,22 @@
         <v>178</v>
       </c>
       <c r="F158">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G158" s="1">
         <v>91.8</v>
       </c>
       <c r="H158" s="1">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I158" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -16174,7 +16177,7 @@
         <v>99</v>
       </c>
       <c r="D185">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E185">
         <v>8</v>
@@ -16183,19 +16186,19 @@
         <v>4</v>
       </c>
       <c r="G185" s="1">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="H185" s="1">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="I185" s="2">
         <v>6</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -16206,7 +16209,7 @@
         <v>100</v>
       </c>
       <c r="D186">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E186">
         <v>112</v>
@@ -16215,19 +16218,19 @@
         <v>20</v>
       </c>
       <c r="G186" s="1">
-        <v>84.8</v>
+        <v>84.2</v>
       </c>
       <c r="H186" s="1">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="I186" s="2">
         <v>6.3</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K186" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -16256,7 +16259,7 @@
         <v>20</v>
       </c>
       <c r="I187" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -16349,19 +16352,19 @@
         <v>32</v>
       </c>
       <c r="E190">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G190" s="1">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="H190" s="1">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="I190" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -16381,19 +16384,19 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F191">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G191" s="1">
-        <v>89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H191" s="1">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="I191" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -17713,22 +17716,22 @@
         <v>99</v>
       </c>
       <c r="D230">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E230">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F230">
         <v>2</v>
       </c>
       <c r="G230" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H230" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I230" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -17745,22 +17748,22 @@
         <v>100</v>
       </c>
       <c r="D231">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E231">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F231">
         <v>2</v>
       </c>
       <c r="G231" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H231" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I231" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -18130,16 +18133,16 @@
         <v>36</v>
       </c>
       <c r="E242">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F242">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G242" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H242" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I242" s="2">
         <v>7</v>
@@ -18162,16 +18165,16 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F243">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G243" s="1">
-        <v>82.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H243" s="1">
-        <v>17.1</v>
+        <v>13.8</v>
       </c>
       <c r="I243" s="2">
         <v>7.6</v>
@@ -19042,25 +19045,25 @@
         <v>99</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>12</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" s="1">
         <v>100</v>
@@ -19074,25 +19077,25 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7">
         <v>92</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>92</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I7" s="2">
         <v>8.1</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K7" s="1">
         <v>100</v>
@@ -19573,7 +19576,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
         <v>36</v>
@@ -19695,10 +19698,10 @@
         <v>99</v>
       </c>
       <c r="D25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -19710,10 +19713,10 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J25">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" s="1">
         <v>100</v>
@@ -19727,10 +19730,10 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -19742,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="1">
         <v>100</v>
@@ -20520,7 +20523,7 @@
         <v>99</v>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E49">
         <v>9</v>
@@ -20529,16 +20532,16 @@
         <v>3</v>
       </c>
       <c r="G49" s="1">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="H49" s="1">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="I49" s="2">
         <v>7</v>
       </c>
       <c r="J49">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K49" s="1">
         <v>100</v>
@@ -20552,7 +20555,7 @@
         <v>100</v>
       </c>
       <c r="D50">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E50">
         <v>76</v>
@@ -20561,16 +20564,16 @@
         <v>48</v>
       </c>
       <c r="G50" s="1">
-        <v>61.3</v>
+        <v>60.8</v>
       </c>
       <c r="H50" s="1">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="I50" s="2">
         <v>6.8</v>
       </c>
       <c r="J50">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K50" s="1">
         <v>100</v>
@@ -21316,19 +21319,19 @@
         <v>30</v>
       </c>
       <c r="E72">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G72" s="1">
-        <v>93.3</v>
+        <v>83.3</v>
       </c>
       <c r="H72" s="1">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="I72" s="2">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J72">
         <v>30</v>
@@ -21558,19 +21561,19 @@
         <v>241</v>
       </c>
       <c r="E79">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F79">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G79" s="1">
-        <v>92.5</v>
+        <v>91.3</v>
       </c>
       <c r="H79" s="1">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I79" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J79">
         <v>241</v>
@@ -23147,25 +23150,25 @@
         <v>99</v>
       </c>
       <c r="D125">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E125">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F125">
         <v>3</v>
       </c>
       <c r="G125" s="1">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H125" s="1">
-        <v>25</v>
+        <v>23.1</v>
       </c>
       <c r="I125" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J125">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K125" s="1">
         <v>100</v>
@@ -23179,10 +23182,10 @@
         <v>100</v>
       </c>
       <c r="D126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E126">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F126">
         <v>25</v>
@@ -23194,10 +23197,10 @@
         <v>13.2</v>
       </c>
       <c r="I126" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J126">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K126" s="1">
         <v>100</v>
@@ -23698,19 +23701,19 @@
         <v>30</v>
       </c>
       <c r="E141">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F141">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H141" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J141">
         <v>30</v>
@@ -23733,19 +23736,19 @@
         <v>38</v>
       </c>
       <c r="E142">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G142" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H142" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J142">
         <v>38</v>
@@ -23803,19 +23806,19 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" s="1">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="H144" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="I144" s="2">
         <v>7</v>
-      </c>
-      <c r="G144" s="1">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="H144" s="1">
-        <v>25.9</v>
-      </c>
-      <c r="I144" s="2">
-        <v>6.7</v>
       </c>
       <c r="J144">
         <v>27</v>
@@ -23835,19 +23838,19 @@
         <v>126</v>
       </c>
       <c r="E145">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F145">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G145" s="1">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="H145" s="1">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I145" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J145">
         <v>126</v>
@@ -24182,16 +24185,16 @@
         <v>36</v>
       </c>
       <c r="F155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G155" s="1">
         <v>90</v>
       </c>
       <c r="H155" s="1">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I155" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J155">
         <v>40</v>
@@ -24284,13 +24287,13 @@
         <v>178</v>
       </c>
       <c r="F158">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G158" s="1">
         <v>91.8</v>
       </c>
       <c r="H158" s="1">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I158" s="2">
         <v>8.6</v>
@@ -25214,7 +25217,7 @@
         <v>99</v>
       </c>
       <c r="D185">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E185">
         <v>8</v>
@@ -25223,16 +25226,16 @@
         <v>4</v>
       </c>
       <c r="G185" s="1">
-        <v>66.7</v>
+        <v>61.5</v>
       </c>
       <c r="H185" s="1">
-        <v>33.3</v>
+        <v>30.8</v>
       </c>
       <c r="I185" s="2">
         <v>6.9</v>
       </c>
       <c r="J185">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K185" s="1">
         <v>100</v>
@@ -25246,7 +25249,7 @@
         <v>100</v>
       </c>
       <c r="D186">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E186">
         <v>112</v>
@@ -25255,16 +25258,16 @@
         <v>20</v>
       </c>
       <c r="G186" s="1">
-        <v>84.8</v>
+        <v>84.2</v>
       </c>
       <c r="H186" s="1">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="I186" s="2">
         <v>6.9</v>
       </c>
       <c r="J186">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K186" s="1">
         <v>100</v>
@@ -25296,7 +25299,7 @@
         <v>20</v>
       </c>
       <c r="I187" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J187">
         <v>30</v>
@@ -25389,19 +25392,19 @@
         <v>32</v>
       </c>
       <c r="E190">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G190" s="1">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="H190" s="1">
-        <v>25</v>
+        <v>18.8</v>
       </c>
       <c r="I190" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J190">
         <v>32</v>
@@ -25421,19 +25424,19 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F191">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G191" s="1">
-        <v>89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H191" s="1">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="I191" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J191">
         <v>146</v>
@@ -26753,25 +26756,25 @@
         <v>99</v>
       </c>
       <c r="D230">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E230">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F230">
         <v>2</v>
       </c>
       <c r="G230" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H230" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I230" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J230">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K230" s="1">
         <v>100</v>
@@ -26785,25 +26788,25 @@
         <v>100</v>
       </c>
       <c r="D231">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E231">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F231">
         <v>2</v>
       </c>
       <c r="G231" s="1">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H231" s="1">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
       <c r="I231" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J231">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K231" s="1">
         <v>100</v>
@@ -27170,19 +27173,19 @@
         <v>36</v>
       </c>
       <c r="E242">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F242">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G242" s="1">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H242" s="1">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="I242" s="2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="J242">
         <v>36</v>
@@ -27202,19 +27205,19 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F243">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G243" s="1">
-        <v>82.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="H243" s="1">
-        <v>17.1</v>
+        <v>13.8</v>
       </c>
       <c r="I243" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J243">
         <v>181</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -2449,22 +2449,22 @@
         <v>6</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G49" s="1">
         <v>46.2</v>
       </c>
       <c r="H49" s="1">
-        <v>46.2</v>
+        <v>53.8</v>
       </c>
       <c r="I49" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2481,22 +2481,22 @@
         <v>72</v>
       </c>
       <c r="F50">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="1">
         <v>57.6</v>
       </c>
       <c r="H50" s="1">
-        <v>41.6</v>
+        <v>42.4</v>
       </c>
       <c r="I50" s="2">
         <v>6.4</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -6586,19 +6586,19 @@
         <v>30</v>
       </c>
       <c r="E169">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F169">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G169" s="1">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="H169" s="1">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I169" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -6688,19 +6688,19 @@
         <v>279</v>
       </c>
       <c r="E172">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F172">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G172" s="1">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="H172" s="1">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="I172" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -11489,22 +11489,22 @@
         <v>9</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G49" s="1">
         <v>69.2</v>
       </c>
       <c r="H49" s="1">
-        <v>23.1</v>
+        <v>30.8</v>
       </c>
       <c r="I49" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -11521,22 +11521,22 @@
         <v>76</v>
       </c>
       <c r="F50">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G50" s="1">
         <v>60.8</v>
       </c>
       <c r="H50" s="1">
-        <v>38.4</v>
+        <v>39.2</v>
       </c>
       <c r="I50" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -12279,25 +12279,25 @@
         <v>30</v>
       </c>
       <c r="E72">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F72">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G72" s="1">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="H72" s="1">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="I72" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -12521,25 +12521,25 @@
         <v>241</v>
       </c>
       <c r="E79">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F79">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G79" s="1">
-        <v>90.5</v>
+        <v>91.3</v>
       </c>
       <c r="H79" s="1">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I79" s="2">
         <v>7.8</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K79" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -12973,19 +12973,19 @@
         <v>24</v>
       </c>
       <c r="E92">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F92">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G92" s="1">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="H92" s="1">
-        <v>50</v>
+        <v>45.8</v>
       </c>
       <c r="I92" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -13005,16 +13005,16 @@
         <v>245</v>
       </c>
       <c r="E93">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F93">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G93" s="1">
-        <v>88.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="H93" s="1">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="I93" s="2">
         <v>7.9</v>
@@ -16145,19 +16145,19 @@
         <v>26</v>
       </c>
       <c r="E184">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F184">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G184" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="H184" s="1">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
       <c r="I184" s="2">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -16212,19 +16212,19 @@
         <v>133</v>
       </c>
       <c r="E186">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F186">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G186" s="1">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="H186" s="1">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="I186" s="2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="J186">
         <v>1</v>
@@ -18920,13 +18920,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -18955,13 +18955,13 @@
         <v>12</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -18993,10 +18993,10 @@
         <v>7.6</v>
       </c>
       <c r="J4">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -19025,13 +19025,13 @@
         <v>17.6</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -19048,25 +19048,25 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>7.7</v>
       </c>
-      <c r="I6" s="2">
-        <v>7.9</v>
-      </c>
       <c r="J6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -19080,25 +19080,25 @@
         <v>101</v>
       </c>
       <c r="E7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>91.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -19115,25 +19115,25 @@
         <v>29</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -19150,25 +19150,25 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>85.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>14.3</v>
+        <v>2.4</v>
       </c>
       <c r="I9" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -19185,25 +19185,25 @@
         <v>36</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>86.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -19220,25 +19220,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11" s="1">
-        <v>69.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>30.2</v>
+        <v>20.9</v>
       </c>
       <c r="I11" s="2">
         <v>7.2</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -19255,25 +19255,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -19290,25 +19290,25 @@
         <v>38</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>92.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="J13">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -19322,25 +19322,25 @@
         <v>220</v>
       </c>
       <c r="E14">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F14">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="H14" s="1">
-        <v>13.6</v>
+        <v>6.8</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -19357,25 +19357,25 @@
         <v>42</v>
       </c>
       <c r="E15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -19392,25 +19392,25 @@
         <v>42</v>
       </c>
       <c r="E16">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="I16" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -19427,25 +19427,25 @@
         <v>38</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>81.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="H17" s="1">
-        <v>18.4</v>
+        <v>5.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -19462,25 +19462,25 @@
         <v>38</v>
       </c>
       <c r="E18">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
-        <v>84.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>15.8</v>
+        <v>7.9</v>
       </c>
       <c r="I18" s="2">
         <v>7.8</v>
       </c>
       <c r="J18">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -19494,25 +19494,25 @@
         <v>160</v>
       </c>
       <c r="E19">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F19">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1">
-        <v>88.8</v>
+        <v>96.2</v>
       </c>
       <c r="H19" s="1">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -19541,13 +19541,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -19564,25 +19564,25 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>75</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="I21" s="2">
         <v>7.1</v>
       </c>
       <c r="J21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -19599,25 +19599,25 @@
         <v>27</v>
       </c>
       <c r="E22">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>88.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="H22" s="1">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="I22" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J22">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -19634,25 +19634,25 @@
         <v>26</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>84.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H23" s="1">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -19666,25 +19666,25 @@
         <v>133</v>
       </c>
       <c r="E24">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1">
-        <v>88</v>
+        <v>94.7</v>
       </c>
       <c r="H24" s="1">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="I24" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -19716,10 +19716,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J25">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -19748,10 +19748,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J26">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -19780,13 +19780,13 @@
         <v>3.3</v>
       </c>
       <c r="I27" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -19803,25 +19803,25 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>90.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H28" s="1">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="I28" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J28">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -19850,13 +19850,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J29">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -19885,13 +19885,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J30">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -19905,25 +19905,25 @@
         <v>131</v>
       </c>
       <c r="E31">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1">
-        <v>96.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="H31" s="1">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="I31" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J31">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -19940,25 +19940,25 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F32">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1">
-        <v>36.1</v>
+        <v>72.2</v>
       </c>
       <c r="H32" s="1">
-        <v>63.9</v>
+        <v>27.8</v>
       </c>
       <c r="I32" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J32">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -19975,25 +19975,25 @@
         <v>39</v>
       </c>
       <c r="E33">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F33">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1">
-        <v>56.4</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>43.6</v>
+        <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -20010,25 +20010,25 @@
         <v>39</v>
       </c>
       <c r="E34">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G34" s="1">
-        <v>61.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>38.5</v>
+        <v>23.1</v>
       </c>
       <c r="I34" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J34">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -20045,25 +20045,25 @@
         <v>37</v>
       </c>
       <c r="E35">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G35" s="1">
-        <v>40.5</v>
+        <v>48.6</v>
       </c>
       <c r="H35" s="1">
-        <v>59.5</v>
+        <v>51.4</v>
       </c>
       <c r="I35" s="2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -20080,25 +20080,25 @@
         <v>19</v>
       </c>
       <c r="E36">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G36" s="1">
-        <v>63.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H36" s="1">
-        <v>36.8</v>
+        <v>21.1</v>
       </c>
       <c r="I36" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -20112,25 +20112,25 @@
         <v>170</v>
       </c>
       <c r="E37">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F37">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="G37" s="1">
-        <v>50.6</v>
+        <v>71.8</v>
       </c>
       <c r="H37" s="1">
-        <v>49.4</v>
+        <v>28.2</v>
       </c>
       <c r="I37" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -20147,25 +20147,25 @@
         <v>32</v>
       </c>
       <c r="E38">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I38" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J38">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -20182,25 +20182,25 @@
         <v>30</v>
       </c>
       <c r="E39">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H39" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -20229,13 +20229,13 @@
         <v>3.6</v>
       </c>
       <c r="I40" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J40">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -20249,25 +20249,25 @@
         <v>90</v>
       </c>
       <c r="E41">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41" s="1">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="H41" s="1">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I41" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J41">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -20284,25 +20284,25 @@
         <v>36</v>
       </c>
       <c r="E42">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1">
-        <v>91.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H42" s="1">
-        <v>8.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I42" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -20319,25 +20319,25 @@
         <v>25</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H43" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I43" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J43">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -20351,25 +20351,25 @@
         <v>61</v>
       </c>
       <c r="E44">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G44" s="1">
-        <v>90.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H44" s="1">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="I44" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J44">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -20386,25 +20386,25 @@
         <v>37</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F45">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G45" s="1">
-        <v>40.5</v>
+        <v>51.4</v>
       </c>
       <c r="H45" s="1">
-        <v>59.5</v>
+        <v>48.6</v>
       </c>
       <c r="I45" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J45">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -20421,25 +20421,25 @@
         <v>33</v>
       </c>
       <c r="E46">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G46" s="1">
-        <v>51.5</v>
+        <v>84.8</v>
       </c>
       <c r="H46" s="1">
-        <v>48.5</v>
+        <v>15.2</v>
       </c>
       <c r="I46" s="2">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="J46">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -20456,25 +20456,25 @@
         <v>16</v>
       </c>
       <c r="E47">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47" s="1">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H47" s="1">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I47" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J47">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K47" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -20491,25 +20491,25 @@
         <v>26</v>
       </c>
       <c r="E48">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G48" s="1">
-        <v>88.5</v>
+        <v>96.2</v>
       </c>
       <c r="H48" s="1">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="I48" s="2">
         <v>7.5</v>
       </c>
       <c r="J48">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -20526,25 +20526,25 @@
         <v>13</v>
       </c>
       <c r="E49">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="1">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H49" s="1">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="I49" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J49">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -20558,25 +20558,25 @@
         <v>125</v>
       </c>
       <c r="E50">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F50">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G50" s="1">
-        <v>60.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H50" s="1">
-        <v>38.4</v>
+        <v>22.4</v>
       </c>
       <c r="I50" s="2">
         <v>6.8</v>
       </c>
       <c r="J50">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -20593,25 +20593,25 @@
         <v>27</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F51">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G51" s="1">
-        <v>37</v>
+        <v>48.1</v>
       </c>
       <c r="H51" s="1">
-        <v>63</v>
+        <v>51.9</v>
       </c>
       <c r="I51" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J51">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -20643,10 +20643,10 @@
         <v>6</v>
       </c>
       <c r="J52">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -20663,25 +20663,25 @@
         <v>34</v>
       </c>
       <c r="E53">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F53">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G53" s="1">
-        <v>61.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H53" s="1">
-        <v>38.2</v>
+        <v>32.4</v>
       </c>
       <c r="I53" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J53">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -20710,13 +20710,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I54" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J54">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -20733,25 +20733,25 @@
         <v>40</v>
       </c>
       <c r="E55">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F55">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1">
-        <v>57.5</v>
+        <v>75</v>
       </c>
       <c r="H55" s="1">
-        <v>42.5</v>
+        <v>25</v>
       </c>
       <c r="I55" s="2">
         <v>6.5</v>
       </c>
       <c r="J55">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K55" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -20768,25 +20768,25 @@
         <v>39</v>
       </c>
       <c r="E56">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F56">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G56" s="1">
-        <v>46.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H56" s="1">
-        <v>53.8</v>
+        <v>25.6</v>
       </c>
       <c r="I56" s="2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J56">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K56" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -20803,25 +20803,25 @@
         <v>30</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F57">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G57" s="1">
-        <v>36.7</v>
+        <v>66.7</v>
       </c>
       <c r="H57" s="1">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="I57" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J57">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -20835,25 +20835,25 @@
         <v>228</v>
       </c>
       <c r="E58">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="F58">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="G58" s="1">
-        <v>54.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H58" s="1">
-        <v>45.6</v>
+        <v>31.6</v>
       </c>
       <c r="I58" s="2">
         <v>6.5</v>
       </c>
       <c r="J58">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -20870,25 +20870,25 @@
         <v>41</v>
       </c>
       <c r="E59">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F59">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G59" s="1">
-        <v>80.5</v>
+        <v>90.2</v>
       </c>
       <c r="H59" s="1">
-        <v>19.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I59" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J59">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -20905,25 +20905,25 @@
         <v>33</v>
       </c>
       <c r="E60">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H60" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I60" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J60">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -20937,25 +20937,25 @@
         <v>74</v>
       </c>
       <c r="E61">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F61">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G61" s="1">
-        <v>87.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H61" s="1">
-        <v>12.2</v>
+        <v>5.4</v>
       </c>
       <c r="I61" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J61">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -20972,25 +20972,25 @@
         <v>27</v>
       </c>
       <c r="E62">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G62" s="1">
-        <v>74.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="H62" s="1">
-        <v>25.9</v>
+        <v>18.5</v>
       </c>
       <c r="I62" s="2">
         <v>7.4</v>
       </c>
       <c r="J62">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -21007,25 +21007,25 @@
         <v>34</v>
       </c>
       <c r="E63">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G63" s="1">
-        <v>94.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="H63" s="1">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I63" s="2">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J63">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -21042,25 +21042,25 @@
         <v>40</v>
       </c>
       <c r="E64">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G64" s="1">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="H64" s="1">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="I64" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J64">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K64" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -21077,25 +21077,25 @@
         <v>39</v>
       </c>
       <c r="E65">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65" s="1">
-        <v>97.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H65" s="1">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="I65" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J65">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K65" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -21112,25 +21112,25 @@
         <v>39</v>
       </c>
       <c r="E66">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G66" s="1">
-        <v>87.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H66" s="1">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="I66" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J66">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K66" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -21159,13 +21159,13 @@
         <v>3.1</v>
       </c>
       <c r="I67" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J67">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -21182,25 +21182,25 @@
         <v>30</v>
       </c>
       <c r="E68">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H68" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I68" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J68">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -21229,13 +21229,13 @@
         <v>10.7</v>
       </c>
       <c r="I69" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J69">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -21249,25 +21249,25 @@
         <v>269</v>
       </c>
       <c r="E70">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F70">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G70" s="1">
-        <v>91.8</v>
+        <v>92.2</v>
       </c>
       <c r="H70" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="I70" s="2">
         <v>8.199999999999999</v>
       </c>
-      <c r="I70" s="2">
-        <v>8.4</v>
-      </c>
       <c r="J70">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -21284,25 +21284,25 @@
         <v>38</v>
       </c>
       <c r="E71">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" s="1">
-        <v>97.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H71" s="1">
-        <v>2.6</v>
+        <v>7.9</v>
       </c>
       <c r="I71" s="2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J71">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -21319,25 +21319,25 @@
         <v>30</v>
       </c>
       <c r="E72">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F72">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G72" s="1">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="H72" s="1">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="I72" s="2">
         <v>7.3</v>
       </c>
       <c r="J72">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -21366,13 +21366,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J73">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K73" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -21389,25 +21389,25 @@
         <v>25</v>
       </c>
       <c r="E74">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74" s="1">
+        <v>92</v>
+      </c>
+      <c r="H74" s="1">
+        <v>8</v>
+      </c>
+      <c r="I74" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J74">
         <v>1</v>
       </c>
-      <c r="G74" s="1">
-        <v>96</v>
-      </c>
-      <c r="H74" s="1">
+      <c r="K74" s="1">
         <v>4</v>
-      </c>
-      <c r="I74" s="2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J74">
-        <v>25</v>
-      </c>
-      <c r="K74" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -21436,13 +21436,13 @@
         <v>0</v>
       </c>
       <c r="I75" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J75">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K75" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -21459,25 +21459,25 @@
         <v>27</v>
       </c>
       <c r="E76">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F76">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G76" s="1">
-        <v>74.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H76" s="1">
-        <v>25.9</v>
+        <v>3.7</v>
       </c>
       <c r="I76" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J76">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K76" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -21509,10 +21509,10 @@
         <v>9.1</v>
       </c>
       <c r="J77">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K77" s="1">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -21529,25 +21529,25 @@
         <v>16</v>
       </c>
       <c r="E78">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F78">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G78" s="1">
-        <v>56.2</v>
+        <v>81.2</v>
       </c>
       <c r="H78" s="1">
-        <v>43.8</v>
+        <v>18.8</v>
       </c>
       <c r="I78" s="2">
         <v>7.1</v>
       </c>
       <c r="J78">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K78" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -21561,25 +21561,25 @@
         <v>241</v>
       </c>
       <c r="E79">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="F79">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G79" s="1">
-        <v>91.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="H79" s="1">
-        <v>8.699999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="I79" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J79">
-        <v>241</v>
+        <v>4</v>
       </c>
       <c r="K79" s="1">
-        <v>100</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -21596,25 +21596,25 @@
         <v>36</v>
       </c>
       <c r="E80">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F80">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G80" s="1">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="H80" s="1">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="I80" s="2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J80">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K80" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -21631,25 +21631,25 @@
         <v>39</v>
       </c>
       <c r="E81">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F81">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G81" s="1">
-        <v>48.7</v>
+        <v>61.5</v>
       </c>
       <c r="H81" s="1">
-        <v>51.3</v>
+        <v>38.5</v>
       </c>
       <c r="I81" s="2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J81">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K81" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -21666,25 +21666,25 @@
         <v>39</v>
       </c>
       <c r="E82">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F82">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G82" s="1">
-        <v>56.4</v>
+        <v>61.5</v>
       </c>
       <c r="H82" s="1">
-        <v>43.6</v>
+        <v>38.5</v>
       </c>
       <c r="I82" s="2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J82">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K82" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -21701,25 +21701,25 @@
         <v>37</v>
       </c>
       <c r="E83">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F83">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G83" s="1">
-        <v>48.6</v>
+        <v>54.1</v>
       </c>
       <c r="H83" s="1">
-        <v>51.4</v>
+        <v>45.9</v>
       </c>
       <c r="I83" s="2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J83">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -21736,25 +21736,25 @@
         <v>19</v>
       </c>
       <c r="E84">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F84">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G84" s="1">
-        <v>42.1</v>
+        <v>73.7</v>
       </c>
       <c r="H84" s="1">
-        <v>57.9</v>
+        <v>26.3</v>
       </c>
       <c r="I84" s="2">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="J84">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -21768,25 +21768,25 @@
         <v>170</v>
       </c>
       <c r="E85">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="F85">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G85" s="1">
-        <v>48.2</v>
+        <v>58.8</v>
       </c>
       <c r="H85" s="1">
-        <v>51.8</v>
+        <v>41.2</v>
       </c>
       <c r="I85" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J85">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="K85" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -21815,13 +21815,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="2">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="J86">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K86" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -21838,25 +21838,25 @@
         <v>42</v>
       </c>
       <c r="E87">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F87">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G87" s="1">
-        <v>90.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H87" s="1">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="I87" s="2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="J87">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -21873,25 +21873,25 @@
         <v>36</v>
       </c>
       <c r="E88">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G88" s="1">
-        <v>94.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H88" s="1">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I88" s="2">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J88">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -21920,13 +21920,13 @@
         <v>18.2</v>
       </c>
       <c r="I89" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J89">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -21955,13 +21955,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J90">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K90" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -21990,13 +21990,13 @@
         <v>5.3</v>
       </c>
       <c r="I91" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J91">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -22013,25 +22013,25 @@
         <v>24</v>
       </c>
       <c r="E92">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F92">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I92" s="2">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="J92">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -22045,25 +22045,25 @@
         <v>245</v>
       </c>
       <c r="E93">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F93">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G93" s="1">
-        <v>88.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="H93" s="1">
-        <v>11.4</v>
+        <v>6.5</v>
       </c>
       <c r="I93" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J93">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -22080,25 +22080,25 @@
         <v>23</v>
       </c>
       <c r="E94">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="H94" s="1">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I94" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J94">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -22115,25 +22115,25 @@
         <v>36</v>
       </c>
       <c r="E95">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F95">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G95" s="1">
-        <v>72.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H95" s="1">
-        <v>27.8</v>
+        <v>13.9</v>
       </c>
       <c r="I95" s="2">
         <v>7</v>
       </c>
       <c r="J95">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K95" s="1">
-        <v>100</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -22150,25 +22150,25 @@
         <v>26</v>
       </c>
       <c r="E96">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F96">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G96" s="1">
-        <v>76.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H96" s="1">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="I96" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="J96">
+        <v>2</v>
+      </c>
+      <c r="K96" s="1">
         <v>7.7</v>
-      </c>
-      <c r="J96">
-        <v>26</v>
-      </c>
-      <c r="K96" s="1">
-        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -22185,25 +22185,25 @@
         <v>28</v>
       </c>
       <c r="E97">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G97" s="1">
-        <v>89.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H97" s="1">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="I97" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J97">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -22220,25 +22220,25 @@
         <v>16</v>
       </c>
       <c r="E98">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G98" s="1">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="H98" s="1">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="I98" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J98">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K98" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -22270,10 +22270,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J99">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -22287,25 +22287,25 @@
         <v>155</v>
       </c>
       <c r="E100">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="F100">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G100" s="1">
-        <v>82.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="H100" s="1">
-        <v>17.4</v>
+        <v>7.7</v>
       </c>
       <c r="I100" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J100">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="K100" s="1">
-        <v>100</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -22322,25 +22322,25 @@
         <v>30</v>
       </c>
       <c r="E101">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F101">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G101" s="1">
-        <v>66.7</v>
+        <v>96.7</v>
       </c>
       <c r="H101" s="1">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="I101" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J101">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K101" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -22357,25 +22357,25 @@
         <v>38</v>
       </c>
       <c r="E102">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="H102" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I102" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J102">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K102" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -22392,25 +22392,25 @@
         <v>25</v>
       </c>
       <c r="E103">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F103">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G103" s="1">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H103" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I103" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J103">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K103" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -22427,25 +22427,25 @@
         <v>31</v>
       </c>
       <c r="E104">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" s="1">
-        <v>90.3</v>
+        <v>96.8</v>
       </c>
       <c r="H104" s="1">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="I104" s="2">
         <v>7.7</v>
       </c>
       <c r="J104">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -22462,25 +22462,25 @@
         <v>36</v>
       </c>
       <c r="E105">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F105">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G105" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H105" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I105" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J105">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K105" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -22529,25 +22529,25 @@
         <v>188</v>
       </c>
       <c r="E107">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="F107">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G107" s="1">
-        <v>83</v>
+        <v>96.8</v>
       </c>
       <c r="H107" s="1">
-        <v>17</v>
+        <v>3.2</v>
       </c>
       <c r="I107" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J107">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="K107" s="1">
-        <v>100</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -22564,25 +22564,25 @@
         <v>39</v>
       </c>
       <c r="E108">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F108">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G108" s="1">
-        <v>56.4</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H108" s="1">
-        <v>43.6</v>
+        <v>17.9</v>
       </c>
       <c r="I108" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J108">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K108" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -22599,25 +22599,25 @@
         <v>36</v>
       </c>
       <c r="E109">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F109">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G109" s="1">
-        <v>86.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H109" s="1">
-        <v>13.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I109" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J109">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K109" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -22634,25 +22634,25 @@
         <v>30</v>
       </c>
       <c r="E110">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H110" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I110" s="2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J110">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K110" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -22666,25 +22666,25 @@
         <v>105</v>
       </c>
       <c r="E111">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="F111">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G111" s="1">
-        <v>77.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="H111" s="1">
-        <v>22.9</v>
+        <v>9.5</v>
       </c>
       <c r="I111" s="2">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J111">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K111" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -22701,25 +22701,25 @@
         <v>27</v>
       </c>
       <c r="E112">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F112">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G112" s="1">
-        <v>55.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H112" s="1">
-        <v>44.4</v>
+        <v>29.6</v>
       </c>
       <c r="I112" s="2">
         <v>6.3</v>
       </c>
       <c r="J112">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K112" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -22736,25 +22736,25 @@
         <v>24</v>
       </c>
       <c r="E113">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F113">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G113" s="1">
-        <v>58.3</v>
+        <v>70.8</v>
       </c>
       <c r="H113" s="1">
-        <v>41.7</v>
+        <v>29.2</v>
       </c>
       <c r="I113" s="2">
         <v>6.3</v>
       </c>
       <c r="J113">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K113" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -22771,25 +22771,25 @@
         <v>34</v>
       </c>
       <c r="E114">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F114">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G114" s="1">
-        <v>79.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H114" s="1">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="I114" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J114">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K114" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -22806,25 +22806,25 @@
         <v>40</v>
       </c>
       <c r="E115">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F115">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G115" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H115" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I115" s="2">
         <v>6.7</v>
       </c>
       <c r="J115">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K115" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -22841,25 +22841,25 @@
         <v>39</v>
       </c>
       <c r="E116">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F116">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G116" s="1">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H116" s="1">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="I116" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J116">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K116" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -22876,25 +22876,25 @@
         <v>30</v>
       </c>
       <c r="E117">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F117">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G117" s="1">
-        <v>63.3</v>
+        <v>90</v>
       </c>
       <c r="H117" s="1">
-        <v>36.7</v>
+        <v>10</v>
       </c>
       <c r="I117" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J117">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K117" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -22908,25 +22908,25 @@
         <v>194</v>
       </c>
       <c r="E118">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="F118">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G118" s="1">
-        <v>71.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H118" s="1">
-        <v>28.4</v>
+        <v>17.5</v>
       </c>
       <c r="I118" s="2">
         <v>6.7</v>
       </c>
       <c r="J118">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="K118" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -22943,25 +22943,25 @@
         <v>27</v>
       </c>
       <c r="E119">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G119" s="1">
-        <v>96.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H119" s="1">
-        <v>3.7</v>
+        <v>11.1</v>
       </c>
       <c r="I119" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J119">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K119" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -22978,25 +22978,25 @@
         <v>24</v>
       </c>
       <c r="E120">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F120">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G120" s="1">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="H120" s="1">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="I120" s="2">
         <v>7.6</v>
       </c>
       <c r="J120">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K120" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -23013,25 +23013,25 @@
         <v>30</v>
       </c>
       <c r="E121">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H121" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I121" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J121">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K121" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -23048,25 +23048,25 @@
         <v>27</v>
       </c>
       <c r="E122">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F122">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>77.8</v>
+        <v>96.3</v>
       </c>
       <c r="H122" s="1">
-        <v>22.2</v>
+        <v>3.7</v>
       </c>
       <c r="I122" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J122">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K122" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -23083,25 +23083,25 @@
         <v>36</v>
       </c>
       <c r="E123">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F123">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G123" s="1">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="H123" s="1">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I123" s="2">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J123">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K123" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -23118,25 +23118,25 @@
         <v>33</v>
       </c>
       <c r="E124">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F124">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G124" s="1">
-        <v>84.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H124" s="1">
-        <v>15.2</v>
+        <v>12.1</v>
       </c>
       <c r="I124" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J124">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K124" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -23153,25 +23153,25 @@
         <v>13</v>
       </c>
       <c r="E125">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G125" s="1">
-        <v>76.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H125" s="1">
-        <v>23.1</v>
+        <v>7.7</v>
       </c>
       <c r="I125" s="2">
         <v>7.8</v>
       </c>
       <c r="J125">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K125" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -23185,25 +23185,25 @@
         <v>190</v>
       </c>
       <c r="E126">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F126">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G126" s="1">
-        <v>86.8</v>
+        <v>93.7</v>
       </c>
       <c r="H126" s="1">
-        <v>13.2</v>
+        <v>6.3</v>
       </c>
       <c r="I126" s="2">
         <v>8.1</v>
       </c>
       <c r="J126">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="K126" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -23302,10 +23302,10 @@
         <v>9</v>
       </c>
       <c r="J129">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K129" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -23322,25 +23322,25 @@
         <v>23</v>
       </c>
       <c r="E130">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" s="1">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="H130" s="1">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I130" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J130">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K130" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -23357,25 +23357,25 @@
         <v>36</v>
       </c>
       <c r="E131">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F131">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G131" s="1">
-        <v>88.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="H131" s="1">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I131" s="2">
         <v>7.8</v>
       </c>
       <c r="J131">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -23392,25 +23392,25 @@
         <v>26</v>
       </c>
       <c r="E132">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G132" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H132" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I132" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J132">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -23439,13 +23439,13 @@
         <v>0</v>
       </c>
       <c r="I133" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J133">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K133" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -23459,25 +23459,25 @@
         <v>151</v>
       </c>
       <c r="E134">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F134">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G134" s="1">
-        <v>94.7</v>
+        <v>96.7</v>
       </c>
       <c r="H134" s="1">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="I134" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J134">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K134" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -23494,25 +23494,25 @@
         <v>39</v>
       </c>
       <c r="E135">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F135">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G135" s="1">
-        <v>61.5</v>
+        <v>79.5</v>
       </c>
       <c r="H135" s="1">
-        <v>38.5</v>
+        <v>20.5</v>
       </c>
       <c r="I135" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J135">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="K135" s="1">
-        <v>100</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -23541,13 +23541,13 @@
         <v>20.8</v>
       </c>
       <c r="I136" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J136">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K136" s="1">
-        <v>100</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -23576,13 +23576,13 @@
         <v>25</v>
       </c>
       <c r="I137" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J137">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K137" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -23611,13 +23611,13 @@
         <v>16</v>
       </c>
       <c r="I138" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J138">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K138" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -23634,25 +23634,25 @@
         <v>26</v>
       </c>
       <c r="E139">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F139">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G139" s="1">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="H139" s="1">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="I139" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J139">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -23666,25 +23666,25 @@
         <v>138</v>
       </c>
       <c r="E140">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F140">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G140" s="1">
-        <v>76.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H140" s="1">
-        <v>23.9</v>
+        <v>18.1</v>
       </c>
       <c r="I140" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J140">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="K140" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -23713,13 +23713,13 @@
         <v>0</v>
       </c>
       <c r="I141" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J141">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K141" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -23748,13 +23748,13 @@
         <v>0</v>
       </c>
       <c r="I142" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J142">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K142" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -23771,25 +23771,25 @@
         <v>31</v>
       </c>
       <c r="E143">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="H143" s="1">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="I143" s="2">
         <v>7.9</v>
       </c>
       <c r="J143">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K143" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -23806,25 +23806,25 @@
         <v>27</v>
       </c>
       <c r="E144">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F144">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G144" s="1">
-        <v>92.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="H144" s="1">
-        <v>7.4</v>
+        <v>14.8</v>
       </c>
       <c r="I144" s="2">
         <v>7</v>
       </c>
       <c r="J144">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -23853,10 +23853,10 @@
         <v>7.6</v>
       </c>
       <c r="J145">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K145" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -23885,13 +23885,13 @@
         <v>2.3</v>
       </c>
       <c r="I146" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J146">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K146" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -23908,25 +23908,25 @@
         <v>27</v>
       </c>
       <c r="E147">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F147">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G147" s="1">
-        <v>85.2</v>
+        <v>96.3</v>
       </c>
       <c r="H147" s="1">
-        <v>14.8</v>
+        <v>3.7</v>
       </c>
       <c r="I147" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J147">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K147" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -23955,13 +23955,13 @@
         <v>0</v>
       </c>
       <c r="I148" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J148">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K148" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -23975,25 +23975,25 @@
         <v>102</v>
       </c>
       <c r="E149">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F149">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G149" s="1">
-        <v>95.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="H149" s="1">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="I149" s="2">
         <v>8.6</v>
       </c>
       <c r="J149">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -24010,25 +24010,25 @@
         <v>28</v>
       </c>
       <c r="E150">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F150">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G150" s="1">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H150" s="1">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="I150" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J150">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K150" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -24042,25 +24042,25 @@
         <v>28</v>
       </c>
       <c r="E151">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F151">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G151" s="1">
-        <v>82.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="H151" s="1">
-        <v>17.9</v>
+        <v>14.3</v>
       </c>
       <c r="I151" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J151">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="K151" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -24077,25 +24077,25 @@
         <v>27</v>
       </c>
       <c r="E152">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F152">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G152" s="1">
-        <v>85.2</v>
+        <v>77.8</v>
       </c>
       <c r="H152" s="1">
-        <v>14.8</v>
+        <v>22.2</v>
       </c>
       <c r="I152" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J152">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K152" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -24112,25 +24112,25 @@
         <v>24</v>
       </c>
       <c r="E153">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G153" s="1">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="H153" s="1">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I153" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J153">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K153" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -24159,13 +24159,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I154" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J154">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K154" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -24182,25 +24182,25 @@
         <v>40</v>
       </c>
       <c r="E155">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G155" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H155" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I155" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J155">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K155" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -24229,13 +24229,13 @@
         <v>5.1</v>
       </c>
       <c r="I156" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J156">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K156" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -24252,25 +24252,25 @@
         <v>30</v>
       </c>
       <c r="E157">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H157" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I157" s="2">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="J157">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K157" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -24296,13 +24296,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I158" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J158">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="K158" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -24319,25 +24319,25 @@
         <v>36</v>
       </c>
       <c r="E159">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F159">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G159" s="1">
-        <v>75</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H159" s="1">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="I159" s="2">
         <v>6.9</v>
       </c>
       <c r="J159">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K159" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -24354,25 +24354,25 @@
         <v>24</v>
       </c>
       <c r="E160">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G160" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H160" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I160" s="2">
         <v>7.8</v>
       </c>
       <c r="J160">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K160" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -24389,25 +24389,25 @@
         <v>26</v>
       </c>
       <c r="E161">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G161" s="1">
-        <v>84.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="H161" s="1">
-        <v>15.4</v>
+        <v>11.5</v>
       </c>
       <c r="I161" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J161">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K161" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -24436,13 +24436,13 @@
         <v>0</v>
       </c>
       <c r="I162" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J162">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K162" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -24456,25 +24456,25 @@
         <v>116</v>
       </c>
       <c r="E163">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F163">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G163" s="1">
-        <v>85.3</v>
+        <v>88.8</v>
       </c>
       <c r="H163" s="1">
-        <v>14.7</v>
+        <v>11.2</v>
       </c>
       <c r="I163" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J163">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="K163" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -24491,25 +24491,25 @@
         <v>27</v>
       </c>
       <c r="E164">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F164">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G164" s="1">
-        <v>66.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H164" s="1">
-        <v>33.3</v>
+        <v>25.9</v>
       </c>
       <c r="I164" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J164">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K164" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -24526,25 +24526,25 @@
         <v>24</v>
       </c>
       <c r="E165">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F165">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G165" s="1">
-        <v>45.8</v>
+        <v>66.7</v>
       </c>
       <c r="H165" s="1">
-        <v>54.2</v>
+        <v>33.3</v>
       </c>
       <c r="I165" s="2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J165">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K165" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -24561,25 +24561,25 @@
         <v>34</v>
       </c>
       <c r="E166">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F166">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G166" s="1">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H166" s="1">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="I166" s="2">
         <v>7.6</v>
       </c>
       <c r="J166">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K166" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -24596,25 +24596,25 @@
         <v>40</v>
       </c>
       <c r="E167">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F167">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G167" s="1">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="H167" s="1">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="I167" s="2">
         <v>7.8</v>
       </c>
       <c r="J167">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K167" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -24631,25 +24631,25 @@
         <v>39</v>
       </c>
       <c r="E168">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F168">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G168" s="1">
-        <v>79.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H168" s="1">
-        <v>20.5</v>
+        <v>17.9</v>
       </c>
       <c r="I168" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J168">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K168" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -24666,25 +24666,25 @@
         <v>30</v>
       </c>
       <c r="E169">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F169">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G169" s="1">
-        <v>73.3</v>
+        <v>70</v>
       </c>
       <c r="H169" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="I169" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J169">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -24701,25 +24701,25 @@
         <v>42</v>
       </c>
       <c r="E170">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F170">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H170" s="1">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I170" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J170">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -24736,25 +24736,25 @@
         <v>43</v>
       </c>
       <c r="E171">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F171">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G171" s="1">
-        <v>81.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H171" s="1">
-        <v>18.6</v>
+        <v>20.9</v>
       </c>
       <c r="I171" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J171">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -24768,25 +24768,25 @@
         <v>279</v>
       </c>
       <c r="E172">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F172">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G172" s="1">
-        <v>77.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H172" s="1">
-        <v>22.2</v>
+        <v>17.9</v>
       </c>
       <c r="I172" s="2">
         <v>7.4</v>
       </c>
       <c r="J172">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -24803,25 +24803,25 @@
         <v>36</v>
       </c>
       <c r="E173">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F173">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G173" s="1">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="H173" s="1">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="I173" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J173">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K173" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -24850,13 +24850,13 @@
         <v>5.1</v>
       </c>
       <c r="I174" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J174">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -24873,25 +24873,25 @@
         <v>39</v>
       </c>
       <c r="E175">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F175">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G175" s="1">
-        <v>74.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H175" s="1">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
       <c r="I175" s="2">
         <v>6.7</v>
       </c>
       <c r="J175">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K175" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -24908,25 +24908,25 @@
         <v>37</v>
       </c>
       <c r="E176">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F176">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G176" s="1">
-        <v>75.7</v>
+        <v>73</v>
       </c>
       <c r="H176" s="1">
-        <v>24.3</v>
+        <v>27</v>
       </c>
       <c r="I176" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J176">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K176" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -24958,10 +24958,10 @@
         <v>7.3</v>
       </c>
       <c r="J177">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K177" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -24993,10 +24993,10 @@
         <v>9.4</v>
       </c>
       <c r="J178">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K178" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -25028,10 +25028,10 @@
         <v>9.4</v>
       </c>
       <c r="J179">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K179" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -25045,25 +25045,25 @@
         <v>239</v>
       </c>
       <c r="E180">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F180">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G180" s="1">
-        <v>85.8</v>
+        <v>88.3</v>
       </c>
       <c r="H180" s="1">
-        <v>14.2</v>
+        <v>11.7</v>
       </c>
       <c r="I180" s="2">
         <v>7.6</v>
       </c>
       <c r="J180">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="K180" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -25127,13 +25127,13 @@
         <v>0</v>
       </c>
       <c r="I182" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J182">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="K182" s="1">
-        <v>100</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -25185,19 +25185,19 @@
         <v>26</v>
       </c>
       <c r="E184">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F184">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G184" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="H184" s="1">
-        <v>38.5</v>
+        <v>30.8</v>
       </c>
       <c r="I184" s="2">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J184">
         <v>26</v>
@@ -25252,25 +25252,25 @@
         <v>133</v>
       </c>
       <c r="E186">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F186">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G186" s="1">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="H186" s="1">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="I186" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J186">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="K186" s="1">
-        <v>100</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -25287,25 +25287,25 @@
         <v>30</v>
       </c>
       <c r="E187">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F187">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G187" s="1">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="H187" s="1">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="I187" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J187">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -25322,25 +25322,25 @@
         <v>42</v>
       </c>
       <c r="E188">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" s="1">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H188" s="1">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I188" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J188">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K188" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -25357,25 +25357,25 @@
         <v>42</v>
       </c>
       <c r="E189">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G189" s="1">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="H189" s="1">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="I189" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J189">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -25392,25 +25392,25 @@
         <v>32</v>
       </c>
       <c r="E190">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F190">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G190" s="1">
-        <v>81.2</v>
+        <v>87.5</v>
       </c>
       <c r="H190" s="1">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="I190" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J190">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K190" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -25424,25 +25424,25 @@
         <v>146</v>
       </c>
       <c r="E191">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F191">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G191" s="1">
-        <v>90.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="H191" s="1">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="I191" s="2">
         <v>8.6</v>
       </c>
       <c r="J191">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="K191" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -25459,25 +25459,25 @@
         <v>41</v>
       </c>
       <c r="E192">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F192">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G192" s="1">
-        <v>82.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="H192" s="1">
-        <v>17.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I192" s="2">
         <v>7.2</v>
       </c>
       <c r="J192">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K192" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -25506,13 +25506,13 @@
         <v>0</v>
       </c>
       <c r="I193" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J193">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -25526,25 +25526,25 @@
         <v>74</v>
       </c>
       <c r="E194">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F194">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G194" s="1">
-        <v>90.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H194" s="1">
-        <v>9.5</v>
+        <v>5.4</v>
       </c>
       <c r="I194" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J194">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="K194" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -25561,25 +25561,25 @@
         <v>36</v>
       </c>
       <c r="E195">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F195">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G195" s="1">
-        <v>86.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H195" s="1">
-        <v>13.9</v>
+        <v>5.6</v>
       </c>
       <c r="I195" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J195">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K195" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -25596,25 +25596,25 @@
         <v>30</v>
       </c>
       <c r="E196">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G196" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H196" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I196" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J196">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K196" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -25631,25 +25631,25 @@
         <v>30</v>
       </c>
       <c r="E197">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F197">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G197" s="1">
-        <v>83.3</v>
+        <v>96.7</v>
       </c>
       <c r="H197" s="1">
-        <v>16.7</v>
+        <v>3.3</v>
       </c>
       <c r="I197" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J197">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K197" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -25666,25 +25666,25 @@
         <v>25</v>
       </c>
       <c r="E198">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G198" s="1">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H198" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I198" s="2">
         <v>8</v>
       </c>
       <c r="J198">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K198" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -25698,25 +25698,25 @@
         <v>121</v>
       </c>
       <c r="E199">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F199">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G199" s="1">
-        <v>87.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="H199" s="1">
-        <v>12.4</v>
+        <v>3.3</v>
       </c>
       <c r="I199" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J199">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="K199" s="1">
-        <v>100</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -25905,25 +25905,25 @@
         <v>34</v>
       </c>
       <c r="E205">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F205">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G205" s="1">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H205" s="1">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="I205" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J205">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K205" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -25940,25 +25940,25 @@
         <v>40</v>
       </c>
       <c r="E206">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H206" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I206" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J206">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -25987,13 +25987,13 @@
         <v>5.1</v>
       </c>
       <c r="I207" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J207">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K207" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -26010,25 +26010,25 @@
         <v>30</v>
       </c>
       <c r="E208">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208" s="1">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H208" s="1">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I208" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J208">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K208" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -26045,25 +26045,25 @@
         <v>25</v>
       </c>
       <c r="E209">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209" s="1">
+        <v>96</v>
+      </c>
+      <c r="H209" s="1">
         <v>4</v>
-      </c>
-      <c r="G209" s="1">
-        <v>84</v>
-      </c>
-      <c r="H209" s="1">
-        <v>16</v>
       </c>
       <c r="I209" s="2">
         <v>8</v>
       </c>
       <c r="J209">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -26077,25 +26077,25 @@
         <v>168</v>
       </c>
       <c r="E210">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F210">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G210" s="1">
-        <v>94</v>
+        <v>95.8</v>
       </c>
       <c r="H210" s="1">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="I210" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J210">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K210" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -26112,25 +26112,25 @@
         <v>40</v>
       </c>
       <c r="E211">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F211">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G211" s="1">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="H211" s="1">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I211" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J211">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K211" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -26144,25 +26144,25 @@
         <v>40</v>
       </c>
       <c r="E212">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F212">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G212" s="1">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="H212" s="1">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I212" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J212">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K212" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -26246,25 +26246,25 @@
         <v>26</v>
       </c>
       <c r="E215">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G215" s="1">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H215" s="1">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I215" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J215">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K215" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -26278,25 +26278,25 @@
         <v>26</v>
       </c>
       <c r="E216">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" s="1">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="H216" s="1">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I216" s="2">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="J216">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K216" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -26555,25 +26555,25 @@
         <v>25</v>
       </c>
       <c r="E224">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F224">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G224" s="1">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="H224" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I224" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J224">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K224" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -26605,10 +26605,10 @@
         <v>8.4</v>
       </c>
       <c r="J225">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K225" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -26622,25 +26622,25 @@
         <v>42</v>
       </c>
       <c r="E226">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F226">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G226" s="1">
-        <v>95.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H226" s="1">
-        <v>4.8</v>
+        <v>11.9</v>
       </c>
       <c r="I226" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J226">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K226" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -26669,13 +26669,13 @@
         <v>0</v>
       </c>
       <c r="I227" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J227">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K227" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -26692,25 +26692,25 @@
         <v>30</v>
       </c>
       <c r="E228">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" s="1">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H228" s="1">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I228" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J228">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K228" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -26724,25 +26724,25 @@
         <v>60</v>
       </c>
       <c r="E229">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G229" s="1">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="H229" s="1">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I229" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J229">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K229" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -26771,13 +26771,13 @@
         <v>15.4</v>
       </c>
       <c r="I230" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J230">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K230" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -26803,13 +26803,13 @@
         <v>15.4</v>
       </c>
       <c r="I231" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J231">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K231" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -26826,25 +26826,25 @@
         <v>39</v>
       </c>
       <c r="E232">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F232">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G232" s="1">
-        <v>79.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H232" s="1">
-        <v>20.5</v>
+        <v>17.9</v>
       </c>
       <c r="I232" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J232">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K232" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -26861,25 +26861,25 @@
         <v>37</v>
       </c>
       <c r="E233">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F233">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G233" s="1">
-        <v>73</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H233" s="1">
-        <v>27</v>
+        <v>21.6</v>
       </c>
       <c r="I233" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J233">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K233" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -26908,13 +26908,13 @@
         <v>15.8</v>
       </c>
       <c r="I234" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J234">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K234" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -26943,13 +26943,13 @@
         <v>3.8</v>
       </c>
       <c r="I235" s="2">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J235">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K235" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -26963,25 +26963,25 @@
         <v>121</v>
       </c>
       <c r="E236">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F236">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G236" s="1">
-        <v>81.8</v>
+        <v>84.3</v>
       </c>
       <c r="H236" s="1">
-        <v>18.2</v>
+        <v>15.7</v>
       </c>
       <c r="I236" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J236">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K236" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -26998,25 +26998,25 @@
         <v>27</v>
       </c>
       <c r="E237">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F237">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G237" s="1">
-        <v>66.7</v>
+        <v>85.2</v>
       </c>
       <c r="H237" s="1">
-        <v>33.3</v>
+        <v>14.8</v>
       </c>
       <c r="I237" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J237">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K237" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -27033,25 +27033,25 @@
         <v>24</v>
       </c>
       <c r="E238">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F238">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G238" s="1">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="H238" s="1">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="I238" s="2">
         <v>7.5</v>
       </c>
       <c r="J238">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K238" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -27068,25 +27068,25 @@
         <v>39</v>
       </c>
       <c r="E239">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G239" s="1">
-        <v>94.90000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="H239" s="1">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="I239" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J239">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K239" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -27103,25 +27103,25 @@
         <v>30</v>
       </c>
       <c r="E240">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F240">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G240" s="1">
-        <v>86.7</v>
+        <v>96.7</v>
       </c>
       <c r="H240" s="1">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="I240" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J240">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K240" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -27138,25 +27138,25 @@
         <v>25</v>
       </c>
       <c r="E241">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F241">
+        <v>1</v>
+      </c>
+      <c r="G241" s="1">
+        <v>96</v>
+      </c>
+      <c r="H241" s="1">
         <v>4</v>
-      </c>
-      <c r="G241" s="1">
-        <v>84</v>
-      </c>
-      <c r="H241" s="1">
-        <v>16</v>
       </c>
       <c r="I241" s="2">
         <v>8</v>
       </c>
       <c r="J241">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K241" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -27185,13 +27185,13 @@
         <v>0</v>
       </c>
       <c r="I242" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J242">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K242" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -27205,25 +27205,25 @@
         <v>181</v>
       </c>
       <c r="E243">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F243">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G243" s="1">
-        <v>86.2</v>
+        <v>92.8</v>
       </c>
       <c r="H243" s="1">
-        <v>13.8</v>
+        <v>7.2</v>
       </c>
       <c r="I243" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J243">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="K243" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -27482,25 +27482,25 @@
         <v>36</v>
       </c>
       <c r="E251">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F251">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G251" s="1">
-        <v>75</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H251" s="1">
-        <v>25</v>
+        <v>30.6</v>
       </c>
       <c r="I251" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J251">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K251" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -27517,25 +27517,25 @@
         <v>25</v>
       </c>
       <c r="E252">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G252" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H252" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I252" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J252">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K252" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -27552,25 +27552,25 @@
         <v>25</v>
       </c>
       <c r="E253">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G253" s="1">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="H253" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I253" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J253">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K253" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -27599,13 +27599,13 @@
         <v>0</v>
       </c>
       <c r="I254" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J254">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K254" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -27622,25 +27622,25 @@
         <v>28</v>
       </c>
       <c r="E255">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" s="1">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H255" s="1">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I255" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J255">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K255" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -27654,25 +27654,25 @@
         <v>144</v>
       </c>
       <c r="E256">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F256">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G256" s="1">
-        <v>91.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H256" s="1">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I256" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J256">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="K256" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -27704,10 +27704,10 @@
         <v>9</v>
       </c>
       <c r="J257">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K257" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -27736,13 +27736,13 @@
         <v>0</v>
       </c>
       <c r="I258" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J258">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K258" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -27771,13 +27771,13 @@
         <v>0</v>
       </c>
       <c r="I259" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J259">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K259" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -27806,13 +27806,13 @@
         <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J260">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K260" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -27841,13 +27841,13 @@
         <v>0</v>
       </c>
       <c r="I261" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J261">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K261" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -27873,13 +27873,13 @@
         <v>0</v>
       </c>
       <c r="I262" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J262">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="K262" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -7140,25 +7140,25 @@
         <v>13</v>
       </c>
       <c r="E185">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F185">
         <v>0</v>
       </c>
       <c r="G185" s="1">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
       </c>
       <c r="I185" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7172,25 +7172,25 @@
         <v>133</v>
       </c>
       <c r="E186">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F186">
         <v>0</v>
       </c>
       <c r="G186" s="1">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
       </c>
       <c r="I186" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -16180,13 +16180,13 @@
         <v>13</v>
       </c>
       <c r="E185">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F185">
         <v>4</v>
       </c>
       <c r="G185" s="1">
-        <v>61.5</v>
+        <v>69.2</v>
       </c>
       <c r="H185" s="1">
         <v>30.8</v>
@@ -16195,10 +16195,10 @@
         <v>6</v>
       </c>
       <c r="J185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -16212,13 +16212,13 @@
         <v>133</v>
       </c>
       <c r="E186">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F186">
         <v>18</v>
       </c>
       <c r="G186" s="1">
-        <v>85.7</v>
+        <v>86.5</v>
       </c>
       <c r="H186" s="1">
         <v>13.5</v>
@@ -16227,10 +16227,10 @@
         <v>6.5</v>
       </c>
       <c r="J186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K186" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -22497,25 +22497,25 @@
         <v>28</v>
       </c>
       <c r="E106">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F106">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>89.3</v>
+        <v>100</v>
       </c>
       <c r="H106" s="1">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="I106" s="2">
         <v>7.4</v>
       </c>
       <c r="J106">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -22529,25 +22529,25 @@
         <v>188</v>
       </c>
       <c r="E107">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F107">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G107" s="1">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H107" s="1">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="I107" s="2">
         <v>7.6</v>
       </c>
       <c r="J107">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K107" s="1">
-        <v>14.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -24010,25 +24010,25 @@
         <v>28</v>
       </c>
       <c r="E150">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F150">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G150" s="1">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H150" s="1">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I150" s="2">
         <v>7</v>
       </c>
       <c r="J150">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K150" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -24042,25 +24042,25 @@
         <v>28</v>
       </c>
       <c r="E151">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F151">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G151" s="1">
-        <v>85.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H151" s="1">
-        <v>14.3</v>
+        <v>17.9</v>
       </c>
       <c r="I151" s="2">
         <v>7</v>
       </c>
       <c r="J151">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K151" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -25080,25 +25080,25 @@
         <v>28</v>
       </c>
       <c r="E181">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" s="1">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I181" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J181">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K181" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -25150,25 +25150,25 @@
         <v>33</v>
       </c>
       <c r="E183">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F183">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G183" s="1">
-        <v>81.8</v>
+        <v>97</v>
       </c>
       <c r="H183" s="1">
-        <v>18.2</v>
+        <v>3</v>
       </c>
       <c r="I183" s="2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J183">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K183" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -25185,25 +25185,25 @@
         <v>26</v>
       </c>
       <c r="E184">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F184">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G184" s="1">
-        <v>69.2</v>
+        <v>96.2</v>
       </c>
       <c r="H184" s="1">
-        <v>30.8</v>
+        <v>3.8</v>
       </c>
       <c r="I184" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J184">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K184" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -25220,25 +25220,25 @@
         <v>13</v>
       </c>
       <c r="E185">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F185">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G185" s="1">
-        <v>61.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H185" s="1">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="I185" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J185">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K185" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -25252,25 +25252,25 @@
         <v>133</v>
       </c>
       <c r="E186">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F186">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G186" s="1">
-        <v>85.7</v>
+        <v>96.2</v>
       </c>
       <c r="H186" s="1">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="I186" s="2">
         <v>7</v>
       </c>
       <c r="J186">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="K186" s="1">
-        <v>80.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -25681,10 +25681,10 @@
         <v>8</v>
       </c>
       <c r="J198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -25713,10 +25713,10 @@
         <v>7.7</v>
       </c>
       <c r="J199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K199" s="1">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -25838,25 +25838,25 @@
         <v>19</v>
       </c>
       <c r="E203">
+        <v>10</v>
+      </c>
+      <c r="F203">
         <v>9</v>
       </c>
-      <c r="F203">
-        <v>10</v>
-      </c>
       <c r="G203" s="1">
+        <v>52.6</v>
+      </c>
+      <c r="H203" s="1">
         <v>47.4</v>
       </c>
-      <c r="H203" s="1">
-        <v>52.6</v>
-      </c>
       <c r="I203" s="2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J203">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K203" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -25870,25 +25870,25 @@
         <v>133</v>
       </c>
       <c r="E204">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F204">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G204" s="1">
-        <v>44.4</v>
+        <v>45.1</v>
       </c>
       <c r="H204" s="1">
-        <v>55.6</v>
+        <v>54.9</v>
       </c>
       <c r="I204" s="2">
         <v>5.6</v>
       </c>
       <c r="J204">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="K204" s="1">
-        <v>100</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -26179,25 +26179,25 @@
         <v>36</v>
       </c>
       <c r="E213">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F213">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G213" s="1">
-        <v>58.3</v>
+        <v>72.2</v>
       </c>
       <c r="H213" s="1">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="I213" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J213">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K213" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -26211,25 +26211,25 @@
         <v>36</v>
       </c>
       <c r="E214">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F214">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G214" s="1">
-        <v>58.3</v>
+        <v>72.2</v>
       </c>
       <c r="H214" s="1">
-        <v>41.7</v>
+        <v>27.8</v>
       </c>
       <c r="I214" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J214">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K214" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -26313,25 +26313,25 @@
         <v>36</v>
       </c>
       <c r="E217">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F217">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G217" s="1">
-        <v>36.1</v>
+        <v>33.3</v>
       </c>
       <c r="H217" s="1">
-        <v>63.9</v>
+        <v>66.7</v>
       </c>
       <c r="I217" s="2">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J217">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K217" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -26348,25 +26348,25 @@
         <v>37</v>
       </c>
       <c r="E218">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F218">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G218" s="1">
-        <v>37.8</v>
+        <v>51.4</v>
       </c>
       <c r="H218" s="1">
-        <v>62.2</v>
+        <v>48.6</v>
       </c>
       <c r="I218" s="2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J218">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K218" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -26395,13 +26395,13 @@
         <v>31.6</v>
       </c>
       <c r="I219" s="2">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J219">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K219" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -26520,25 +26520,25 @@
         <v>176</v>
       </c>
       <c r="E223">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F223">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G223" s="1">
-        <v>63.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H223" s="1">
-        <v>36.4</v>
+        <v>34.1</v>
       </c>
       <c r="I223" s="2">
         <v>6.6</v>
       </c>
       <c r="J223">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="K223" s="1">
-        <v>100</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="224" spans="1:11">

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -23821,25 +23821,25 @@
         <v>24</v>
       </c>
       <c r="E131">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F131">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G131" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H131" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I131" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J131">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K131" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -23853,25 +23853,25 @@
         <v>24</v>
       </c>
       <c r="E132">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F132">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G132" s="1">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="H132" s="1">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="I132" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J132">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K132" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -24095,25 +24095,25 @@
         <v>39</v>
       </c>
       <c r="E139">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>84.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="H139" s="1">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="I139" s="2">
         <v>6.7</v>
       </c>
       <c r="J139">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K139" s="1">
-        <v>10.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -24267,25 +24267,25 @@
         <v>138</v>
       </c>
       <c r="E144">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F144">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G144" s="1">
-        <v>83.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H144" s="1">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="I144" s="2">
         <v>7.4</v>
       </c>
       <c r="J144">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K144" s="1">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -25785,25 +25785,25 @@
         <v>33</v>
       </c>
       <c r="E189">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G189" s="1">
-        <v>100</v>
+        <v>78.8</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="I189" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J189">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K189" s="1">
-        <v>21.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -25922,25 +25922,25 @@
         <v>133</v>
       </c>
       <c r="E193">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F193">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G193" s="1">
-        <v>96.2</v>
+        <v>91</v>
       </c>
       <c r="H193" s="1">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="I193" s="2">
         <v>7</v>
       </c>
       <c r="J193">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K193" s="1">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -26461,25 +26461,25 @@
         <v>39</v>
       </c>
       <c r="E209">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F209">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G209" s="1">
-        <v>51.3</v>
+        <v>53.8</v>
       </c>
       <c r="H209" s="1">
-        <v>48.7</v>
+        <v>46.2</v>
       </c>
       <c r="I209" s="2">
         <v>5.6</v>
       </c>
       <c r="J209">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K209" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -26586,25 +26586,25 @@
         <v>133</v>
       </c>
       <c r="E213">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F213">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G213" s="1">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="H213" s="1">
-        <v>49.6</v>
+        <v>48.9</v>
       </c>
       <c r="I213" s="2">
         <v>5.6</v>
       </c>
       <c r="J213">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K213" s="1">
-        <v>29.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -28002,25 +28002,25 @@
         <v>39</v>
       </c>
       <c r="E255">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F255">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G255" s="1">
-        <v>56.4</v>
+        <v>87.2</v>
       </c>
       <c r="H255" s="1">
-        <v>43.6</v>
+        <v>12.8</v>
       </c>
       <c r="I255" s="2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="J255">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K255" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -28037,25 +28037,25 @@
         <v>39</v>
       </c>
       <c r="E256">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F256">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G256" s="1">
-        <v>35.9</v>
+        <v>79.5</v>
       </c>
       <c r="H256" s="1">
-        <v>64.09999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="I256" s="2">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J256">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K256" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -28072,25 +28072,25 @@
         <v>37</v>
       </c>
       <c r="E257">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F257">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G257" s="1">
-        <v>40.5</v>
+        <v>83.8</v>
       </c>
       <c r="H257" s="1">
-        <v>59.5</v>
+        <v>16.2</v>
       </c>
       <c r="I257" s="2">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="J257">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K257" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -28107,25 +28107,25 @@
         <v>19</v>
       </c>
       <c r="E258">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F258">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G258" s="1">
-        <v>47.4</v>
+        <v>84.2</v>
       </c>
       <c r="H258" s="1">
-        <v>52.6</v>
+        <v>15.8</v>
       </c>
       <c r="I258" s="2">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="J258">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K258" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -28142,25 +28142,25 @@
         <v>24</v>
       </c>
       <c r="E259">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F259">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G259" s="1">
-        <v>70.8</v>
+        <v>91.7</v>
       </c>
       <c r="H259" s="1">
-        <v>29.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I259" s="2">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="J259">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K259" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -28177,25 +28177,25 @@
         <v>30</v>
       </c>
       <c r="E260">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F260">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G260" s="1">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H260" s="1">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J260">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K260" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -28209,25 +28209,25 @@
         <v>188</v>
       </c>
       <c r="E261">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="F261">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="G261" s="1">
-        <v>55.9</v>
+        <v>87.2</v>
       </c>
       <c r="H261" s="1">
-        <v>44.1</v>
+        <v>12.8</v>
       </c>
       <c r="I261" s="2">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="J261">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K261" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:11">

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -2688,15 +2688,27 @@
         <v>124</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G56" s="1">
+        <v>95</v>
+      </c>
+      <c r="H56" s="1">
+        <v>5</v>
+      </c>
+      <c r="I56" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2778,22 +2790,22 @@
         <v>101</v>
       </c>
       <c r="D59">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="E59">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="F59">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G59" s="1">
-        <v>47.4</v>
+        <v>54.5</v>
       </c>
       <c r="H59" s="1">
-        <v>52.6</v>
+        <v>45.5</v>
       </c>
       <c r="I59" s="2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4265,15 +4277,27 @@
         <v>125</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
+      <c r="G102" s="1">
+        <v>100</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>10</v>
+      </c>
       <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4495,22 +4519,22 @@
         <v>101</v>
       </c>
       <c r="D109">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="E109">
-        <v>154</v>
+        <v>193</v>
       </c>
       <c r="F109">
         <v>34</v>
       </c>
       <c r="G109" s="1">
-        <v>81.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="H109" s="1">
-        <v>18.1</v>
+        <v>15</v>
       </c>
       <c r="I109" s="2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -4565,15 +4589,27 @@
         <v>115</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G111" s="1">
+        <v>75.7</v>
+      </c>
+      <c r="H111" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="I111" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1">
         <v>0</v>
       </c>
     </row>
@@ -4655,22 +4691,22 @@
         <v>101</v>
       </c>
       <c r="D114">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="E114">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="F114">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G114" s="1">
-        <v>77.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="H114" s="1">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="I114" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -5002,15 +5038,27 @@
         <v>116</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
+      <c r="G124" s="1">
+        <v>100</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2">
+        <v>10</v>
+      </c>
       <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1">
         <v>0</v>
       </c>
     </row>
@@ -5197,22 +5245,22 @@
         <v>101</v>
       </c>
       <c r="D130">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E130">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="F130">
         <v>27</v>
       </c>
       <c r="G130" s="1">
-        <v>85.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H130" s="1">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="I130" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -5885,15 +5933,27 @@
         <v>123</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G150" s="1">
+        <v>85.3</v>
+      </c>
+      <c r="H150" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="I150" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6010,22 +6070,22 @@
         <v>101</v>
       </c>
       <c r="D154">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E154">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="F154">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G154" s="1">
-        <v>96.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="I154" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -6561,15 +6621,27 @@
         <v>121</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G170" s="1">
+        <v>85.2</v>
+      </c>
+      <c r="H170" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="I170" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170" s="1">
         <v>0</v>
       </c>
     </row>
@@ -6826,22 +6898,22 @@
         <v>101</v>
       </c>
       <c r="D178">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="E178">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="F178">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G178" s="1">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H178" s="1">
-        <v>29</v>
+        <v>27.8</v>
       </c>
       <c r="I178" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -6966,15 +7038,27 @@
         <v>114</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G182" s="1">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="H182" s="1">
+        <v>5.1</v>
+      </c>
+      <c r="I182" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7126,22 +7210,22 @@
         <v>101</v>
       </c>
       <c r="D187">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="E187">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="F187">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G187" s="1">
-        <v>87.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="H187" s="1">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="I187" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -7540,15 +7624,27 @@
         <v>112</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
+      <c r="G199" s="1">
+        <v>100</v>
+      </c>
+      <c r="H199" s="1">
+        <v>0</v>
+      </c>
+      <c r="I199" s="2">
+        <v>10</v>
+      </c>
       <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7630,22 +7726,22 @@
         <v>101</v>
       </c>
       <c r="D202">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E202">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="F202">
         <v>8</v>
       </c>
       <c r="G202" s="1">
-        <v>89.2</v>
+        <v>92.7</v>
       </c>
       <c r="H202" s="1">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="I202" s="2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -7907,15 +8003,27 @@
         <v>113</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F210">
         <v>0</v>
       </c>
+      <c r="G210" s="1">
+        <v>100</v>
+      </c>
+      <c r="H210" s="1">
+        <v>0</v>
+      </c>
+      <c r="I210" s="2">
+        <v>10</v>
+      </c>
       <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210" s="1">
         <v>0</v>
       </c>
     </row>
@@ -7997,22 +8105,22 @@
         <v>101</v>
       </c>
       <c r="D213">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E213">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="F213">
         <v>49</v>
       </c>
       <c r="G213" s="1">
-        <v>63.2</v>
+        <v>71.5</v>
       </c>
       <c r="H213" s="1">
-        <v>36.8</v>
+        <v>28.5</v>
       </c>
       <c r="I213" s="2">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -8172,15 +8280,27 @@
         <v>126</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F218">
         <v>0</v>
       </c>
+      <c r="G218" s="1">
+        <v>100</v>
+      </c>
+      <c r="H218" s="1">
+        <v>0</v>
+      </c>
+      <c r="I218" s="2">
+        <v>10</v>
+      </c>
       <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8227,22 +8347,22 @@
         <v>101</v>
       </c>
       <c r="D220">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E220">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F220">
         <v>12</v>
       </c>
       <c r="G220" s="1">
-        <v>92.90000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H220" s="1">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="I220" s="2">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -8976,15 +9096,27 @@
         <v>122</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F242">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G242" s="1">
+        <v>95.8</v>
+      </c>
+      <c r="H242" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="I242" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9136,22 +9268,22 @@
         <v>101</v>
       </c>
       <c r="D247">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E247">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="F247">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G247" s="1">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="H247" s="1">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I247" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -11981,15 +12113,27 @@
         <v>124</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G56" s="1">
+        <v>95</v>
+      </c>
+      <c r="H56" s="1">
+        <v>5</v>
+      </c>
+      <c r="I56" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
         <v>0</v>
       </c>
     </row>
@@ -12071,22 +12215,22 @@
         <v>101</v>
       </c>
       <c r="D59">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="E59">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="F59">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G59" s="1">
-        <v>54.4</v>
+        <v>60.4</v>
       </c>
       <c r="H59" s="1">
-        <v>45.6</v>
+        <v>39.6</v>
       </c>
       <c r="I59" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -13558,15 +13702,27 @@
         <v>125</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
+      <c r="G102" s="1">
+        <v>100</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>10</v>
+      </c>
       <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1">
         <v>0</v>
       </c>
     </row>
@@ -13788,22 +13944,22 @@
         <v>101</v>
       </c>
       <c r="D109">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="E109">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="F109">
         <v>32</v>
       </c>
       <c r="G109" s="1">
-        <v>83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H109" s="1">
-        <v>17</v>
+        <v>14.1</v>
       </c>
       <c r="I109" s="2">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -13858,15 +14014,27 @@
         <v>115</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="G111" s="1">
+        <v>86.5</v>
+      </c>
+      <c r="H111" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="I111" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1">
         <v>0</v>
       </c>
     </row>
@@ -13948,22 +14116,22 @@
         <v>101</v>
       </c>
       <c r="D114">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="E114">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="F114">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G114" s="1">
-        <v>77.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H114" s="1">
-        <v>22.9</v>
+        <v>20.4</v>
       </c>
       <c r="I114" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -14295,15 +14463,27 @@
         <v>116</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
+      <c r="G124" s="1">
+        <v>100</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2">
+        <v>10</v>
+      </c>
       <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1">
         <v>0</v>
       </c>
     </row>
@@ -14490,22 +14670,22 @@
         <v>101</v>
       </c>
       <c r="D130">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E130">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="F130">
         <v>25</v>
       </c>
       <c r="G130" s="1">
-        <v>86.8</v>
+        <v>88</v>
       </c>
       <c r="H130" s="1">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="I130" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -15178,15 +15358,27 @@
         <v>123</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G150" s="1">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H150" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="I150" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150" s="1">
         <v>0</v>
       </c>
     </row>
@@ -15303,22 +15495,22 @@
         <v>101</v>
       </c>
       <c r="D154">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E154">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G154" s="1">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H154" s="1">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I154" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -15854,15 +16046,27 @@
         <v>121</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G170" s="1">
+        <v>85.2</v>
+      </c>
+      <c r="H170" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="I170" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170" s="1">
         <v>0</v>
       </c>
     </row>
@@ -16119,22 +16323,22 @@
         <v>101</v>
       </c>
       <c r="D178">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="E178">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="F178">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G178" s="1">
-        <v>77.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H178" s="1">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="I178" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -16259,15 +16463,27 @@
         <v>114</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G182" s="1">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="H182" s="1">
+        <v>5.1</v>
+      </c>
+      <c r="I182" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182" s="1">
         <v>0</v>
       </c>
     </row>
@@ -16419,22 +16635,22 @@
         <v>101</v>
       </c>
       <c r="D187">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="E187">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="F187">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G187" s="1">
-        <v>85.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H187" s="1">
-        <v>14.2</v>
+        <v>12.9</v>
       </c>
       <c r="I187" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -16833,15 +17049,27 @@
         <v>112</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
+      <c r="G199" s="1">
+        <v>100</v>
+      </c>
+      <c r="H199" s="1">
+        <v>0</v>
+      </c>
+      <c r="I199" s="2">
+        <v>10</v>
+      </c>
       <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199" s="1">
         <v>0</v>
       </c>
     </row>
@@ -16923,22 +17151,22 @@
         <v>101</v>
       </c>
       <c r="D202">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E202">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="F202">
         <v>7</v>
       </c>
       <c r="G202" s="1">
-        <v>90.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H202" s="1">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="I202" s="2">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -17200,15 +17428,27 @@
         <v>113</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F210">
         <v>0</v>
       </c>
+      <c r="G210" s="1">
+        <v>100</v>
+      </c>
+      <c r="H210" s="1">
+        <v>0</v>
+      </c>
+      <c r="I210" s="2">
+        <v>9.4</v>
+      </c>
       <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17290,22 +17530,22 @@
         <v>101</v>
       </c>
       <c r="D213">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E213">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="F213">
         <v>74</v>
       </c>
       <c r="G213" s="1">
-        <v>44.4</v>
+        <v>57</v>
       </c>
       <c r="H213" s="1">
-        <v>55.6</v>
+        <v>43</v>
       </c>
       <c r="I213" s="2">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -17465,15 +17705,27 @@
         <v>126</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F218">
         <v>0</v>
       </c>
+      <c r="G218" s="1">
+        <v>100</v>
+      </c>
+      <c r="H218" s="1">
+        <v>0</v>
+      </c>
+      <c r="I218" s="2">
+        <v>10</v>
+      </c>
       <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218" s="1">
         <v>0</v>
       </c>
     </row>
@@ -17520,22 +17772,22 @@
         <v>101</v>
       </c>
       <c r="D220">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E220">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="F220">
         <v>10</v>
       </c>
       <c r="G220" s="1">
-        <v>94</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H220" s="1">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="I220" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -18269,15 +18521,27 @@
         <v>122</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F242">
         <v>0</v>
       </c>
+      <c r="G242" s="1">
+        <v>100</v>
+      </c>
+      <c r="H242" s="1">
+        <v>0</v>
+      </c>
+      <c r="I242" s="2">
+        <v>10</v>
+      </c>
       <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242" s="1">
         <v>0</v>
       </c>
     </row>
@@ -18429,22 +18693,22 @@
         <v>101</v>
       </c>
       <c r="D247">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E247">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F247">
         <v>22</v>
       </c>
       <c r="G247" s="1">
-        <v>81.8</v>
+        <v>84.8</v>
       </c>
       <c r="H247" s="1">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="I247" s="2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -21274,15 +21538,27 @@
         <v>124</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G56" s="1">
+        <v>95</v>
+      </c>
+      <c r="H56" s="1">
+        <v>5</v>
+      </c>
+      <c r="I56" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
         <v>0</v>
       </c>
     </row>
@@ -21364,22 +21640,22 @@
         <v>101</v>
       </c>
       <c r="D59">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="E59">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="F59">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G59" s="1">
-        <v>68.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="H59" s="1">
-        <v>31.1</v>
+        <v>27.2</v>
       </c>
       <c r="I59" s="2">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -22851,15 +23127,27 @@
         <v>125</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
+      <c r="G102" s="1">
+        <v>100</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>10</v>
+      </c>
       <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23081,22 +23369,22 @@
         <v>101</v>
       </c>
       <c r="D109">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="E109">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F109">
         <v>2</v>
       </c>
       <c r="G109" s="1">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H109" s="1">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I109" s="2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -23151,15 +23439,27 @@
         <v>115</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G111" s="1">
+        <v>73</v>
+      </c>
+      <c r="H111" s="1">
+        <v>27</v>
+      </c>
+      <c r="I111" s="2">
+        <v>8.6</v>
       </c>
       <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23241,22 +23541,22 @@
         <v>101</v>
       </c>
       <c r="D114">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="E114">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="F114">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G114" s="1">
-        <v>90.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H114" s="1">
-        <v>9.5</v>
+        <v>14.1</v>
       </c>
       <c r="I114" s="2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -23588,15 +23888,27 @@
         <v>116</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F124">
         <v>0</v>
       </c>
+      <c r="G124" s="1">
+        <v>100</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="2">
+        <v>10</v>
+      </c>
       <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1">
         <v>0</v>
       </c>
     </row>
@@ -23783,22 +24095,22 @@
         <v>101</v>
       </c>
       <c r="D130">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="E130">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="F130">
         <v>12</v>
       </c>
       <c r="G130" s="1">
-        <v>93.7</v>
+        <v>94.3</v>
       </c>
       <c r="H130" s="1">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="I130" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -24471,15 +24783,27 @@
         <v>123</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G150" s="1">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H150" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="I150" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150" s="1">
         <v>0</v>
       </c>
     </row>
@@ -24596,22 +24920,22 @@
         <v>101</v>
       </c>
       <c r="D154">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E154">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F154">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G154" s="1">
-        <v>98</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H154" s="1">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="I154" s="2">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -25147,15 +25471,27 @@
         <v>121</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G170" s="1">
+        <v>85.2</v>
+      </c>
+      <c r="H170" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="I170" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170" s="1">
         <v>0</v>
       </c>
     </row>
@@ -25412,22 +25748,22 @@
         <v>101</v>
       </c>
       <c r="D178">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="E178">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="F178">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G178" s="1">
-        <v>82.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H178" s="1">
-        <v>17.9</v>
+        <v>17.6</v>
       </c>
       <c r="I178" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -25552,15 +25888,27 @@
         <v>114</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G182" s="1">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="H182" s="1">
+        <v>5.1</v>
+      </c>
+      <c r="I182" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182" s="1">
         <v>0</v>
       </c>
     </row>
@@ -25712,22 +26060,22 @@
         <v>101</v>
       </c>
       <c r="D187">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="E187">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="F187">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G187" s="1">
-        <v>88.3</v>
+        <v>89.2</v>
       </c>
       <c r="H187" s="1">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="I187" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -26126,15 +26474,27 @@
         <v>112</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F199">
         <v>0</v>
       </c>
+      <c r="G199" s="1">
+        <v>100</v>
+      </c>
+      <c r="H199" s="1">
+        <v>0</v>
+      </c>
+      <c r="I199" s="2">
+        <v>10</v>
+      </c>
       <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26216,22 +26576,22 @@
         <v>101</v>
       </c>
       <c r="D202">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E202">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="F202">
         <v>4</v>
       </c>
       <c r="G202" s="1">
-        <v>94.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H202" s="1">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="I202" s="2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -26493,15 +26853,27 @@
         <v>113</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="G210" s="1">
+        <v>5.1</v>
+      </c>
+      <c r="H210" s="1">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="I210" s="2">
+        <v>5.3</v>
       </c>
       <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26583,22 +26955,22 @@
         <v>101</v>
       </c>
       <c r="D213">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E213">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F213">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="G213" s="1">
-        <v>51.1</v>
+        <v>40.7</v>
       </c>
       <c r="H213" s="1">
-        <v>48.9</v>
+        <v>59.3</v>
       </c>
       <c r="I213" s="2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -26758,15 +27130,27 @@
         <v>126</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F218">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G218" s="1">
+        <v>96.7</v>
+      </c>
+      <c r="H218" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="I218" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218" s="1">
         <v>0</v>
       </c>
     </row>
@@ -26813,22 +27197,22 @@
         <v>101</v>
       </c>
       <c r="D220">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="E220">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="F220">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G220" s="1">
-        <v>95.8</v>
+        <v>96</v>
       </c>
       <c r="H220" s="1">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I220" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -27562,15 +27946,27 @@
         <v>122</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F242">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G242" s="1">
+        <v>95.8</v>
+      </c>
+      <c r="H242" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="I242" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242" s="1">
         <v>0</v>
       </c>
     </row>
@@ -27722,22 +28118,22 @@
         <v>101</v>
       </c>
       <c r="D247">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E247">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="F247">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G247" s="1">
-        <v>84.3</v>
+        <v>86.2</v>
       </c>
       <c r="H247" s="1">
-        <v>15.7</v>
+        <v>13.8</v>
       </c>
       <c r="I247" s="2">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="J247">
         <v>0</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -19693,7 +19693,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -19728,7 +19728,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -19763,7 +19763,7 @@
         <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -19798,7 +19798,7 @@
         <v>11.8</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -19833,7 +19833,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -19865,7 +19865,7 @@
         <v>6.9</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -19900,7 +19900,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -19935,7 +19935,7 @@
         <v>2.4</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -19970,7 +19970,7 @@
         <v>11.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>9.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -20005,7 +20005,7 @@
         <v>20.9</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -20075,7 +20075,7 @@
         <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -20107,7 +20107,7 @@
         <v>6.8</v>
       </c>
       <c r="I14" s="2">
-        <v>8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -20142,7 +20142,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -20177,7 +20177,7 @@
         <v>2.4</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -20212,7 +20212,7 @@
         <v>5.3</v>
       </c>
       <c r="I17" s="2">
-        <v>7.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -20247,7 +20247,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -20279,7 +20279,7 @@
         <v>3.8</v>
       </c>
       <c r="I19" s="2">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -20314,7 +20314,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -20349,7 +20349,7 @@
         <v>11.1</v>
       </c>
       <c r="I21" s="2">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -20384,7 +20384,7 @@
         <v>3.7</v>
       </c>
       <c r="I22" s="2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -20419,7 +20419,7 @@
         <v>3.8</v>
       </c>
       <c r="I23" s="2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -20451,7 +20451,7 @@
         <v>4.5</v>
       </c>
       <c r="I24" s="2">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -20486,7 +20486,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -20518,7 +20518,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>3.3</v>
       </c>
       <c r="I27" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -20588,7 +20588,7 @@
         <v>3.1</v>
       </c>
       <c r="I28" s="2">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -20623,7 +20623,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -20658,7 +20658,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -20690,7 +20690,7 @@
         <v>1.5</v>
       </c>
       <c r="I31" s="2">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -20725,7 +20725,7 @@
         <v>27.8</v>
       </c>
       <c r="I32" s="2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -20760,7 +20760,7 @@
         <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -20795,7 +20795,7 @@
         <v>23.1</v>
       </c>
       <c r="I34" s="2">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -20830,7 +20830,7 @@
         <v>51.4</v>
       </c>
       <c r="I35" s="2">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -20865,7 +20865,7 @@
         <v>21.1</v>
       </c>
       <c r="I36" s="2">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -20897,7 +20897,7 @@
         <v>28.2</v>
       </c>
       <c r="I37" s="2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -20932,7 +20932,7 @@
         <v>3.1</v>
       </c>
       <c r="I38" s="2">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -20967,7 +20967,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -21002,7 +21002,7 @@
         <v>3.6</v>
       </c>
       <c r="I40" s="2">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -21034,7 +21034,7 @@
         <v>2.2</v>
       </c>
       <c r="I41" s="2">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -21069,7 +21069,7 @@
         <v>5.6</v>
       </c>
       <c r="I42" s="2">
-        <v>7.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>8</v>
       </c>
       <c r="I43" s="2">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -21136,7 +21136,7 @@
         <v>6.6</v>
       </c>
       <c r="I44" s="2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -21171,7 +21171,7 @@
         <v>48.6</v>
       </c>
       <c r="I45" s="2">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -21206,7 +21206,7 @@
         <v>15.2</v>
       </c>
       <c r="I46" s="2">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>12.5</v>
       </c>
       <c r="I47" s="2">
-        <v>7.1</v>
+        <v>9.4</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -21276,7 +21276,7 @@
         <v>3.8</v>
       </c>
       <c r="I48" s="2">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -21311,7 +21311,7 @@
         <v>15.4</v>
       </c>
       <c r="I49" s="2">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -21343,7 +21343,7 @@
         <v>22.4</v>
       </c>
       <c r="I50" s="2">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -21378,7 +21378,7 @@
         <v>51.9</v>
       </c>
       <c r="I51" s="2">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -21413,7 +21413,7 @@
         <v>58.3</v>
       </c>
       <c r="I52" s="2">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -21448,7 +21448,7 @@
         <v>32.4</v>
       </c>
       <c r="I53" s="2">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -21483,7 +21483,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I54" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -21518,7 +21518,7 @@
         <v>25</v>
       </c>
       <c r="I55" s="2">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -21588,7 +21588,7 @@
         <v>23.1</v>
       </c>
       <c r="I57" s="2">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -21623,7 +21623,7 @@
         <v>33.3</v>
       </c>
       <c r="I58" s="2">
-        <v>6.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>27.2</v>
       </c>
       <c r="I59" s="2">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -21690,7 +21690,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I60" s="2">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -21725,7 +21725,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -21757,7 +21757,7 @@
         <v>5.4</v>
       </c>
       <c r="I62" s="2">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -21792,7 +21792,7 @@
         <v>18.5</v>
       </c>
       <c r="I63" s="2">
-        <v>7.4</v>
+        <v>9.1</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -21827,7 +21827,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I64" s="2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -21862,7 +21862,7 @@
         <v>2.5</v>
       </c>
       <c r="I65" s="2">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -21897,7 +21897,7 @@
         <v>5.1</v>
       </c>
       <c r="I66" s="2">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -21932,7 +21932,7 @@
         <v>15.4</v>
       </c>
       <c r="I67" s="2">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -21967,7 +21967,7 @@
         <v>3.1</v>
       </c>
       <c r="I68" s="2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -22002,7 +22002,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="2">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -22037,7 +22037,7 @@
         <v>10.7</v>
       </c>
       <c r="I70" s="2">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -22069,7 +22069,7 @@
         <v>7.8</v>
       </c>
       <c r="I71" s="2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -22104,7 +22104,7 @@
         <v>7.9</v>
       </c>
       <c r="I72" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>6.7</v>
       </c>
       <c r="I73" s="2">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -22174,7 +22174,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -22209,7 +22209,7 @@
         <v>12</v>
       </c>
       <c r="I75" s="2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -22279,7 +22279,7 @@
         <v>3.7</v>
       </c>
       <c r="I77" s="2">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -22314,7 +22314,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -22349,7 +22349,7 @@
         <v>18.8</v>
       </c>
       <c r="I79" s="2">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -22381,7 +22381,7 @@
         <v>5</v>
       </c>
       <c r="I80" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -22416,7 +22416,7 @@
         <v>50</v>
       </c>
       <c r="I81" s="2">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -22451,7 +22451,7 @@
         <v>38.5</v>
       </c>
       <c r="I82" s="2">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -22486,7 +22486,7 @@
         <v>38.5</v>
       </c>
       <c r="I83" s="2">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -22521,7 +22521,7 @@
         <v>45.9</v>
       </c>
       <c r="I84" s="2">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -22556,7 +22556,7 @@
         <v>26.3</v>
       </c>
       <c r="I85" s="2">
-        <v>6.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -22588,7 +22588,7 @@
         <v>41.2</v>
       </c>
       <c r="I86" s="2">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -22623,7 +22623,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -22658,7 +22658,7 @@
         <v>7.1</v>
       </c>
       <c r="I88" s="2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I89" s="2">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>18.2</v>
       </c>
       <c r="I90" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -22763,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="2">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -22798,7 +22798,7 @@
         <v>5.3</v>
       </c>
       <c r="I92" s="2">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -22833,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -22865,7 +22865,7 @@
         <v>6.5</v>
       </c>
       <c r="I94" s="2">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -22900,7 +22900,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -22935,7 +22935,7 @@
         <v>13.9</v>
       </c>
       <c r="I96" s="2">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -22970,7 +22970,7 @@
         <v>3.8</v>
       </c>
       <c r="I97" s="2">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -23005,7 +23005,7 @@
         <v>3.6</v>
       </c>
       <c r="I98" s="2">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -23040,7 +23040,7 @@
         <v>25</v>
       </c>
       <c r="I99" s="2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -23075,7 +23075,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="2">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -23107,7 +23107,7 @@
         <v>7.1</v>
       </c>
       <c r="I101" s="2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>3.3</v>
       </c>
       <c r="I103" s="2">
-        <v>6.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -23212,7 +23212,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -23247,7 +23247,7 @@
         <v>4</v>
       </c>
       <c r="I105" s="2">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -23282,7 +23282,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -23317,7 +23317,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -23352,7 +23352,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="2">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -23384,7 +23384,7 @@
         <v>0.9</v>
       </c>
       <c r="I109" s="2">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -23419,7 +23419,7 @@
         <v>17.9</v>
       </c>
       <c r="I110" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -23489,7 +23489,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I112" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -23524,7 +23524,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -23556,7 +23556,7 @@
         <v>14.1</v>
       </c>
       <c r="I114" s="2">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -23591,7 +23591,7 @@
         <v>29.6</v>
       </c>
       <c r="I115" s="2">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -23626,7 +23626,7 @@
         <v>29.2</v>
       </c>
       <c r="I116" s="2">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -23661,7 +23661,7 @@
         <v>17.6</v>
       </c>
       <c r="I117" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -23696,7 +23696,7 @@
         <v>10</v>
       </c>
       <c r="I118" s="2">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -23731,7 +23731,7 @@
         <v>15.4</v>
       </c>
       <c r="I119" s="2">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>10</v>
       </c>
       <c r="I120" s="2">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -23798,7 +23798,7 @@
         <v>17.5</v>
       </c>
       <c r="I121" s="2">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -23833,7 +23833,7 @@
         <v>11.1</v>
       </c>
       <c r="I122" s="2">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -23868,7 +23868,7 @@
         <v>12.5</v>
       </c>
       <c r="I123" s="2">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -23938,7 +23938,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -23973,7 +23973,7 @@
         <v>3.7</v>
       </c>
       <c r="I126" s="2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -24008,7 +24008,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="2">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -24043,7 +24043,7 @@
         <v>12.1</v>
       </c>
       <c r="I128" s="2">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -24078,7 +24078,7 @@
         <v>7.7</v>
       </c>
       <c r="I129" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -24110,7 +24110,7 @@
         <v>5.7</v>
       </c>
       <c r="I130" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -24145,7 +24145,7 @@
         <v>12.5</v>
       </c>
       <c r="I131" s="2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -24177,7 +24177,7 @@
         <v>12.5</v>
       </c>
       <c r="I132" s="2">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -24212,7 +24212,7 @@
         <v>2.8</v>
       </c>
       <c r="I133" s="2">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -24247,7 +24247,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -24282,7 +24282,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I135" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -24317,7 +24317,7 @@
         <v>3.8</v>
       </c>
       <c r="I136" s="2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -24384,7 +24384,7 @@
         <v>3.3</v>
       </c>
       <c r="I138" s="2">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -24419,7 +24419,7 @@
         <v>12.8</v>
       </c>
       <c r="I139" s="2">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="J139">
         <v>0</v>
@@ -24454,7 +24454,7 @@
         <v>20.8</v>
       </c>
       <c r="I140" s="2">
-        <v>6.9</v>
+        <v>9</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -24489,7 +24489,7 @@
         <v>25</v>
       </c>
       <c r="I141" s="2">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J141">
         <v>0</v>
@@ -24524,7 +24524,7 @@
         <v>16</v>
       </c>
       <c r="I142" s="2">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -24559,7 +24559,7 @@
         <v>7.7</v>
       </c>
       <c r="I143" s="2">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -24591,7 +24591,7 @@
         <v>15.9</v>
       </c>
       <c r="I144" s="2">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -24626,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -24661,7 +24661,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -24731,7 +24731,7 @@
         <v>14.8</v>
       </c>
       <c r="I148" s="2">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -24763,7 +24763,7 @@
         <v>3.2</v>
       </c>
       <c r="I149" s="2">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>2.3</v>
       </c>
       <c r="I151" s="2">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -24868,7 +24868,7 @@
         <v>3.7</v>
       </c>
       <c r="I152" s="2">
-        <v>8.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J152">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>0</v>
       </c>
       <c r="I153" s="2">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         <v>2.9</v>
       </c>
       <c r="I154" s="2">
-        <v>8.9</v>
+        <v>9.9</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>17.9</v>
       </c>
       <c r="I155" s="2">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -25002,7 +25002,7 @@
         <v>17.9</v>
       </c>
       <c r="I156" s="2">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -25037,7 +25037,7 @@
         <v>22.2</v>
       </c>
       <c r="I157" s="2">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -25072,7 +25072,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I158" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -25107,7 +25107,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I159" s="2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -25142,7 +25142,7 @@
         <v>5</v>
       </c>
       <c r="I160" s="2">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -25177,7 +25177,7 @@
         <v>5.1</v>
       </c>
       <c r="I161" s="2">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -25212,7 +25212,7 @@
         <v>3.3</v>
       </c>
       <c r="I162" s="2">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -25244,7 +25244,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I163" s="2">
-        <v>8.1</v>
+        <v>9.6</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -25279,7 +25279,7 @@
         <v>16.7</v>
       </c>
       <c r="I164" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -25314,7 +25314,7 @@
         <v>12.5</v>
       </c>
       <c r="I165" s="2">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -25349,7 +25349,7 @@
         <v>11.5</v>
       </c>
       <c r="I166" s="2">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -25384,7 +25384,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -25416,7 +25416,7 @@
         <v>10.3</v>
       </c>
       <c r="I168" s="2">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -25451,7 +25451,7 @@
         <v>25.9</v>
       </c>
       <c r="I169" s="2">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -25521,7 +25521,7 @@
         <v>33.3</v>
       </c>
       <c r="I171" s="2">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -25556,7 +25556,7 @@
         <v>20.6</v>
       </c>
       <c r="I172" s="2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -25591,7 +25591,7 @@
         <v>7.5</v>
       </c>
       <c r="I173" s="2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -25626,7 +25626,7 @@
         <v>17.9</v>
       </c>
       <c r="I174" s="2">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -25661,7 +25661,7 @@
         <v>30</v>
       </c>
       <c r="I175" s="2">
-        <v>6.6</v>
+        <v>8.5</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -25696,7 +25696,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -25731,7 +25731,7 @@
         <v>20.9</v>
       </c>
       <c r="I177" s="2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="J177">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>17.6</v>
       </c>
       <c r="I178" s="2">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -25798,7 +25798,7 @@
         <v>16.7</v>
       </c>
       <c r="I179" s="2">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -25833,7 +25833,7 @@
         <v>5.1</v>
       </c>
       <c r="I180" s="2">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -25868,7 +25868,7 @@
         <v>15.4</v>
       </c>
       <c r="I181" s="2">
-        <v>6.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -25938,7 +25938,7 @@
         <v>27</v>
       </c>
       <c r="I183" s="2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J183">
         <v>0</v>
@@ -25973,7 +25973,7 @@
         <v>21.1</v>
       </c>
       <c r="I184" s="2">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -26008,7 +26008,7 @@
         <v>0</v>
       </c>
       <c r="I185" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -26043,7 +26043,7 @@
         <v>0</v>
       </c>
       <c r="I186" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -26075,7 +26075,7 @@
         <v>10.8</v>
       </c>
       <c r="I187" s="2">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3.6</v>
       </c>
       <c r="I188" s="2">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -26145,7 +26145,7 @@
         <v>21.2</v>
       </c>
       <c r="I189" s="2">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -26180,7 +26180,7 @@
         <v>3</v>
       </c>
       <c r="I190" s="2">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -26215,7 +26215,7 @@
         <v>3.8</v>
       </c>
       <c r="I191" s="2">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -26250,7 +26250,7 @@
         <v>15.4</v>
       </c>
       <c r="I192" s="2">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -26282,7 +26282,7 @@
         <v>9</v>
       </c>
       <c r="I193" s="2">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -26317,7 +26317,7 @@
         <v>6.7</v>
       </c>
       <c r="I194" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -26352,7 +26352,7 @@
         <v>0</v>
       </c>
       <c r="I195" s="2">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -26387,7 +26387,7 @@
         <v>4.8</v>
       </c>
       <c r="I196" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -26422,7 +26422,7 @@
         <v>12.5</v>
       </c>
       <c r="I197" s="2">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -26454,7 +26454,7 @@
         <v>5.5</v>
       </c>
       <c r="I198" s="2">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J198">
         <v>0</v>
@@ -26524,7 +26524,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I200" s="2">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -26559,7 +26559,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="2">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -26591,7 +26591,7 @@
         <v>3.6</v>
       </c>
       <c r="I202" s="2">
-        <v>8.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -26626,7 +26626,7 @@
         <v>5.6</v>
       </c>
       <c r="I203" s="2">
-        <v>7.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -26661,7 +26661,7 @@
         <v>0</v>
       </c>
       <c r="I204" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -26696,7 +26696,7 @@
         <v>3.3</v>
       </c>
       <c r="I205" s="2">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -26731,7 +26731,7 @@
         <v>4</v>
       </c>
       <c r="I206" s="2">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -26763,7 +26763,7 @@
         <v>3.3</v>
       </c>
       <c r="I207" s="2">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -26798,7 +26798,7 @@
         <v>55.6</v>
       </c>
       <c r="I208" s="2">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="J208">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>46.2</v>
       </c>
       <c r="I209" s="2">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="J209">
         <v>0</v>
@@ -26903,7 +26903,7 @@
         <v>46.2</v>
       </c>
       <c r="I211" s="2">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="J211">
         <v>0</v>
@@ -26938,7 +26938,7 @@
         <v>47.4</v>
       </c>
       <c r="I212" s="2">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -26970,7 +26970,7 @@
         <v>59.3</v>
       </c>
       <c r="I213" s="2">
-        <v>5.5</v>
+        <v>7.1</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -27005,7 +27005,7 @@
         <v>5.9</v>
       </c>
       <c r="I214" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J214">
         <v>0</v>
@@ -27040,7 +27040,7 @@
         <v>2.5</v>
       </c>
       <c r="I215" s="2">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J215">
         <v>0</v>
@@ -27075,7 +27075,7 @@
         <v>5.1</v>
       </c>
       <c r="I216" s="2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J216">
         <v>0</v>
@@ -27110,7 +27110,7 @@
         <v>3.3</v>
       </c>
       <c r="I217" s="2">
-        <v>7.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -27180,7 +27180,7 @@
         <v>4</v>
       </c>
       <c r="I219" s="2">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J219">
         <v>0</v>
@@ -27212,7 +27212,7 @@
         <v>4</v>
       </c>
       <c r="I220" s="2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -27247,7 +27247,7 @@
         <v>7.5</v>
       </c>
       <c r="I221" s="2">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="J221">
         <v>0</v>
@@ -27279,7 +27279,7 @@
         <v>7.5</v>
       </c>
       <c r="I222" s="2">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="J222">
         <v>0</v>
@@ -27314,7 +27314,7 @@
         <v>27.8</v>
       </c>
       <c r="I223" s="2">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="J223">
         <v>0</v>
@@ -27346,7 +27346,7 @@
         <v>27.8</v>
       </c>
       <c r="I224" s="2">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="J224">
         <v>0</v>
@@ -27381,7 +27381,7 @@
         <v>3.8</v>
       </c>
       <c r="I225" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J225">
         <v>0</v>
@@ -27413,7 +27413,7 @@
         <v>3.8</v>
       </c>
       <c r="I226" s="2">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J226">
         <v>0</v>
@@ -27448,7 +27448,7 @@
         <v>66.7</v>
       </c>
       <c r="I227" s="2">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="J227">
         <v>0</v>
@@ -27483,7 +27483,7 @@
         <v>48.6</v>
       </c>
       <c r="I228" s="2">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -27518,7 +27518,7 @@
         <v>31.6</v>
       </c>
       <c r="I229" s="2">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -27553,7 +27553,7 @@
         <v>14.3</v>
       </c>
       <c r="I230" s="2">
-        <v>7.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>7.1</v>
       </c>
       <c r="I231" s="2">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -27623,7 +27623,7 @@
         <v>7.1</v>
       </c>
       <c r="I232" s="2">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -27655,7 +27655,7 @@
         <v>31.8</v>
       </c>
       <c r="I233" s="2">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="J233">
         <v>0</v>
@@ -27690,7 +27690,7 @@
         <v>12</v>
       </c>
       <c r="I234" s="2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J234">
         <v>0</v>
@@ -27725,7 +27725,7 @@
         <v>11.8</v>
       </c>
       <c r="I235" s="2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J235">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>11.9</v>
       </c>
       <c r="I236" s="2">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="J236">
         <v>0</v>
@@ -27792,7 +27792,7 @@
         <v>0</v>
       </c>
       <c r="I237" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J237">
         <v>0</v>
@@ -27827,7 +27827,7 @@
         <v>0</v>
       </c>
       <c r="I238" s="2">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="J238">
         <v>0</v>
@@ -27859,7 +27859,7 @@
         <v>0</v>
       </c>
       <c r="I239" s="2">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="J239">
         <v>0</v>
@@ -27894,7 +27894,7 @@
         <v>15.4</v>
       </c>
       <c r="I240" s="2">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J240">
         <v>0</v>
@@ -27926,7 +27926,7 @@
         <v>15.4</v>
       </c>
       <c r="I241" s="2">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -27996,7 +27996,7 @@
         <v>17.9</v>
       </c>
       <c r="I243" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J243">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>21.6</v>
       </c>
       <c r="I244" s="2">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -28066,7 +28066,7 @@
         <v>15.8</v>
       </c>
       <c r="I245" s="2">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -28101,7 +28101,7 @@
         <v>3.8</v>
       </c>
       <c r="I246" s="2">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -28133,7 +28133,7 @@
         <v>13.8</v>
       </c>
       <c r="I247" s="2">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -28168,7 +28168,7 @@
         <v>14.8</v>
       </c>
       <c r="I248" s="2">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J248">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>16.7</v>
       </c>
       <c r="I249" s="2">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>7.7</v>
       </c>
       <c r="I250" s="2">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -28273,7 +28273,7 @@
         <v>3.3</v>
       </c>
       <c r="I251" s="2">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J251">
         <v>0</v>
@@ -28308,7 +28308,7 @@
         <v>4</v>
       </c>
       <c r="I252" s="2">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J252">
         <v>0</v>
@@ -28343,7 +28343,7 @@
         <v>0</v>
       </c>
       <c r="I253" s="2">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="J253">
         <v>0</v>
@@ -28375,7 +28375,7 @@
         <v>7.2</v>
       </c>
       <c r="I254" s="2">
-        <v>7.7</v>
+        <v>9.6</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -28410,7 +28410,7 @@
         <v>12.8</v>
       </c>
       <c r="I255" s="2">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="J255">
         <v>0</v>
@@ -28445,7 +28445,7 @@
         <v>20.5</v>
       </c>
       <c r="I256" s="2">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -28480,7 +28480,7 @@
         <v>16.2</v>
       </c>
       <c r="I257" s="2">
-        <v>6.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J257">
         <v>0</v>
@@ -28515,7 +28515,7 @@
         <v>15.8</v>
       </c>
       <c r="I258" s="2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J258">
         <v>0</v>
@@ -28550,7 +28550,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I259" s="2">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="J259">
         <v>0</v>
@@ -28585,7 +28585,7 @@
         <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -28617,7 +28617,7 @@
         <v>12.8</v>
       </c>
       <c r="I261" s="2">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -28652,7 +28652,7 @@
         <v>30.6</v>
       </c>
       <c r="I262" s="2">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -28687,7 +28687,7 @@
         <v>0</v>
       </c>
       <c r="I263" s="2">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -28722,7 +28722,7 @@
         <v>0</v>
       </c>
       <c r="I264" s="2">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="J264">
         <v>0</v>
@@ -28757,7 +28757,7 @@
         <v>0</v>
       </c>
       <c r="I265" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -28792,7 +28792,7 @@
         <v>0</v>
       </c>
       <c r="I266" s="2">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -28824,7 +28824,7 @@
         <v>7.6</v>
       </c>
       <c r="I267" s="2">
-        <v>7.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -28859,7 +28859,7 @@
         <v>0</v>
       </c>
       <c r="I268" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J268">
         <v>0</v>
@@ -28894,7 +28894,7 @@
         <v>0</v>
       </c>
       <c r="I269" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J269">
         <v>0</v>
@@ -28929,7 +28929,7 @@
         <v>0</v>
       </c>
       <c r="I270" s="2">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J270">
         <v>0</v>
@@ -28964,7 +28964,7 @@
         <v>0</v>
       </c>
       <c r="I271" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J271">
         <v>0</v>
@@ -28999,7 +28999,7 @@
         <v>0</v>
       </c>
       <c r="I272" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J272">
         <v>0</v>
@@ -29031,7 +29031,7 @@
         <v>0</v>
       </c>
       <c r="I273" s="2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J273">
         <v>0</v>

--- a/DetalleXDocente20231.xlsx
+++ b/DetalleXDocente20231.xlsx
@@ -19693,7 +19693,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -19728,7 +19728,7 @@
         <v>12</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -19763,7 +19763,7 @@
         <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -19798,7 +19798,7 @@
         <v>11.8</v>
       </c>
       <c r="I5" s="2">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -19833,7 +19833,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -19865,7 +19865,7 @@
         <v>6.9</v>
       </c>
       <c r="I7" s="2">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -19900,7 +19900,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -19935,7 +19935,7 @@
         <v>2.4</v>
       </c>
       <c r="I9" s="2">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -19970,7 +19970,7 @@
         <v>11.1</v>
       </c>
       <c r="I10" s="2">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -20005,7 +20005,7 @@
         <v>20.9</v>
       </c>
       <c r="I11" s="2">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -20040,7 +20040,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -20075,7 +20075,7 @@
         <v>2.6</v>
       </c>
       <c r="I13" s="2">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -20107,7 +20107,7 @@
         <v>6.8</v>
       </c>
       <c r="I14" s="2">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -20142,7 +20142,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -20177,7 +20177,7 @@
         <v>2.4</v>
       </c>
       <c r="I16" s="2">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -20212,7 +20212,7 @@
         <v>5.3</v>
       </c>
       <c r="I17" s="2">
-        <v>9.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -20247,7 +20247,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -20279,7 +20279,7 @@
         <v>3.8</v>
       </c>
       <c r="I19" s="2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -20314,7 +20314,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -20349,7 +20349,7 @@
         <v>11.1</v>
       </c>
       <c r="I21" s="2">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -20384,7 +20384,7 @@
         <v>3.7</v>
       </c>
       <c r="I22" s="2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -20419,7 +20419,7 @@
         <v>3.8</v>
       </c>
       <c r="I23" s="2">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -20451,7 +20451,7 @@
         <v>4.5</v>
       </c>
       <c r="I24" s="2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -20486,7 +20486,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -20518,7 +20518,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>3.3</v>
       </c>
       <c r="I27" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -20588,7 +20588,7 @@
         <v>3.1</v>
       </c>
       <c r="I28" s="2">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -20623,7 +20623,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -20658,7 +20658,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -20690,7 +20690,7 @@
         <v>1.5</v>
       </c>
       <c r="I31" s="2">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -20725,7 +20725,7 @@
         <v>27.8</v>
       </c>
       <c r="I32" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -20760,7 +20760,7 @@
         <v>15.4</v>
       </c>
       <c r="I33" s="2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -20795,7 +20795,7 @@
         <v>23.1</v>
       </c>
       <c r="I34" s="2">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -20830,7 +20830,7 @@
         <v>51.4</v>
       </c>
       <c r="I35" s="2">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -20865,7 +20865,7 @@
         <v>21.1</v>
       </c>
       <c r="I36" s="2">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -20897,7 +20897,7 @@
         <v>28.2</v>
       </c>
       <c r="I37" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -20932,7 +20932,7 @@
         <v>3.1</v>
       </c>
       <c r="I38" s="2">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -20967,7 +20967,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -21002,7 +21002,7 @@
         <v>3.6</v>
       </c>
       <c r="I40" s="2">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -21034,7 +21034,7 @@
         <v>2.2</v>
       </c>
       <c r="I41" s="2">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -21069,7 +21069,7 @@
         <v>5.6</v>
       </c>
       <c r="I42" s="2">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>8</v>
       </c>
       <c r="I43" s="2">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -21136,7 +21136,7 @@
         <v>6.6</v>
       </c>
       <c r="I44" s="2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -21171,7 +21171,7 @@
         <v>48.6</v>
       </c>
       <c r="I45" s="2">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -21206,7 +21206,7 @@
         <v>15.2</v>
       </c>
       <c r="I46" s="2">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>12.5</v>
       </c>
       <c r="I47" s="2">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -21276,7 +21276,7 @@
         <v>3.8</v>
       </c>
       <c r="I48" s="2">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -21311,7 +21311,7 @@
         <v>15.4</v>
       </c>
       <c r="I49" s="2">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -21343,7 +21343,7 @@
         <v>22.4</v>
       </c>
       <c r="I50" s="2">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -21378,7 +21378,7 @@
         <v>51.9</v>
       </c>
       <c r="I51" s="2">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -21413,7 +21413,7 @@
         <v>58.3</v>
       </c>
       <c r="I52" s="2">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -21448,7 +21448,7 @@
         <v>32.4</v>
       </c>
       <c r="I53" s="2">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -21483,7 +21483,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I54" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -21518,7 +21518,7 @@
         <v>25</v>
       </c>
       <c r="I55" s="2">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -21588,7 +21588,7 @@
         <v>23.1</v>
       </c>
       <c r="I57" s="2">
-        <v>8.800000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -21623,7 +21623,7 @@
         <v>33.3</v>
       </c>
       <c r="I58" s="2">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>27.2</v>
       </c>
       <c r="I59" s="2">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -21690,7 +21690,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I60" s="2">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -21725,7 +21725,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -21757,7 +21757,7 @@
         <v>5.4</v>
       </c>
       <c r="I62" s="2">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -21792,7 +21792,7 @@
         <v>18.5</v>
       </c>
       <c r="I63" s="2">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -21827,7 +21827,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I64" s="2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -21862,7 +21862,7 @@
         <v>2.5</v>
       </c>
       <c r="I65" s="2">
-        <v>9.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -21897,7 +21897,7 @@
         <v>5.1</v>
       </c>
       <c r="I66" s="2">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -21932,7 +21932,7 @@
         <v>15.4</v>
       </c>
       <c r="I67" s="2">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -21967,7 +21967,7 @@
         <v>3.1</v>
       </c>
       <c r="I68" s="2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -22002,7 +22002,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="2">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -22037,7 +22037,7 @@
         <v>10.7</v>
       </c>
       <c r="I70" s="2">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -22069,7 +22069,7 @@
         <v>7.8</v>
       </c>
       <c r="I71" s="2">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -22104,7 +22104,7 @@
         <v>7.9</v>
       </c>
       <c r="I72" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -22139,7 +22139,7 @@
         <v>6.7</v>
       </c>
       <c r="I73" s="2">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -22174,7 +22174,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -22209,7 +22209,7 @@
         <v>12</v>
       </c>
       <c r="I75" s="2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -22244,7 +22244,7 @@
         <v>0</v>
       </c>
       <c r="I76" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -22279,7 +22279,7 @@
         <v>3.7</v>
       </c>
       <c r="I77" s="2">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -22314,7 +22314,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -22349,7 +22349,7 @@
         <v>18.8</v>
       </c>
       <c r="I79" s="2">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -22381,7 +22381,7 @@
         <v>5</v>
       </c>
       <c r="I80" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -22404,19 +22404,19 @@
         <v>36</v>
       </c>
       <c r="E81">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F81">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G81" s="1">
-        <v>50</v>
+        <v>52.8</v>
       </c>
       <c r="H81" s="1">
-        <v>50</v>
+        <v>47.2</v>
       </c>
       <c r="I81" s="2">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -22451,7 +22451,7 @@
         <v>38.5</v>
       </c>
       <c r="I82" s="2">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -22474,19 +22474,19 @@
         <v>39</v>
       </c>
       <c r="E83">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F83">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G83" s="1">
-        <v>61.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H83" s="1">
-        <v>38.5</v>
+        <v>35.9</v>
       </c>
       <c r="I83" s="2">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -22521,7 +22521,7 @@
         <v>45.9</v>
       </c>
       <c r="I84" s="2">
-        <v>7.7</v>
+        <v>5.8</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -22556,7 +22556,7 @@
         <v>26.3</v>
       </c>
       <c r="I85" s="2">
-        <v>8.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -22576,19 +22576,19 @@
         <v>170</v>
       </c>
       <c r="E86">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F86">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G86" s="1">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="H86" s="1">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="I86" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -22623,7 +22623,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -22658,7 +22658,7 @@
         <v>7.1</v>
       </c>
       <c r="I88" s="2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -22693,7 +22693,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I89" s="2">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>18.2</v>
       </c>
       <c r="I90" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -22763,7 +22763,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="2">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -22798,7 +22798,7 @@
         <v>5.3</v>
       </c>
       <c r="I92" s="2">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -22833,7 +22833,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="2">
-        <v>10</v>
+        <v>6.9</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -22865,7 +22865,7 @@
         <v>6.5</v>
       </c>
       <c r="I94" s="2">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -22900,7 +22900,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="2">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -22935,7 +22935,7 @@
         <v>13.9</v>
       </c>
       <c r="I96" s="2">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -22970,7 +22970,7 @@
         <v>3.8</v>
       </c>
       <c r="I97" s="2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -23005,7 +23005,7 @@
         <v>3.6</v>
       </c>
       <c r="I98" s="2">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -23040,7 +23040,7 @@
         <v>25</v>
       </c>
       <c r="I99" s="2">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -23075,7 +23075,7 @@
         <v>0</v>
       </c>
       <c r="I100" s="2">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -23107,7 +23107,7 @@
         <v>7.1</v>
       </c>
       <c r="I101" s="2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>3.3</v>
       </c>
       <c r="I103" s="2">
-        <v>9.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -23212,7 +23212,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -23247,7 +23247,7 @@
         <v>4</v>
       </c>
       <c r="I105" s="2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -23282,7 +23282,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -23317,7 +23317,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -23352,7 +23352,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -23384,7 +23384,7 @@
         <v>0.9</v>
       </c>
       <c r="I109" s="2">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -23419,7 +23419,7 @@
         <v>17.9</v>
       </c>
       <c r="I110" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -23489,7 +23489,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I112" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -23524,7 +23524,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -23556,7 +23556,7 @@
         <v>14.1</v>
       </c>
       <c r="I114" s="2">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -23591,7 +23591,7 @@
         <v>29.6</v>
       </c>
       <c r="I115" s="2">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -23626,7 +23626,7 @@
         <v>29.2</v>
       </c>
       <c r="I116" s="2">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -23661,7 +23661,7 @@
         <v>17.6</v>
       </c>
       <c r="I117" s="2">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -23696,7 +23696,7 @@
         <v>10</v>
       </c>
       <c r="I118" s="2">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -23731,7 +23731,7 @@
         <v>15.4</v>
       </c>
       <c r="I119" s="2">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -23766,7 +23766,7 @@
         <v>10</v>
       </c>
       <c r="I120" s="2">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -23798,7 +23798,7 @@
         <v>17.5</v>
       </c>
       <c r="I121" s="2">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -23833,7 +23833,7 @@
         <v>11.1</v>
       </c>
       <c r="I122" s="2">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -23868,7 +23868,7 @@
         <v>12.5</v>
       </c>
       <c r="I123" s="2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -23938,7 +23938,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="2">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -23973,7 +23973,7 @@
         <v>3.7</v>
       </c>
       <c r="I126" s="2">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -24008,7 +24008,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="2">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -24043,7 +24043,7 @@
         <v>12.1</v>
       </c>
       <c r="I128" s="2">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -24078,7 +24078,7 @@
         <v>7.7</v>
       </c>
       <c r="I129" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -24110,7 +24110,7 @@
         <v>5.7</v>
       </c>
       <c r="I130" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -24145,7 +24145,7 @@
         <v>12.5</v>
       </c>
       <c r="I131" s="2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -24177,7 +24177,7 @@
         <v>12.5</v>
       </c>
       <c r="I132" s="2">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -24212,7 +24212,7 @@
         <v>2.8</v>
       </c>
       <c r="I133" s="2">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -24247,7 +24247,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -24282,7 +24282,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I135" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -24317,7 +24317,7 @@
         <v>3.8</v>
       </c>
       <c r="I136" s="2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -24352,7 +24352,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -24384,7 +24384,7 @@
         <v>3.3</v>
       </c>
       <c r="I138" s="2">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -24419,7 +24419,7 @@
         <v>12.8</v>
       </c>
       <c r="I139" s="2">
-        <v>9.4</v>
+        <v>6.7</v>
       </c>
       <c r="J139">
         <v>0</v>
@@ -24454,7 +24454,7 @@
         <v>20.8</v>
       </c>
       <c r="I140" s="2">
-        <v>9</v>
+        <v>6.9</v>
       </c>
       <c r="J140">
         <v>0</v>
@@ -24489,7 +24489,7 @@
         <v>25</v>
       </c>
       <c r="I141" s="2">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="J141">
         <v>0</v>
@@ -24524,7 +24524,7 @@
         <v>16</v>
       </c>
       <c r="I142" s="2">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -24547,19 +24547,19 @@
         <v>26</v>
       </c>
       <c r="E143">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F143">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G143" s="1">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="H143" s="1">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="I143" s="2">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J143">
         <v>0</v>
@@ -24579,19 +24579,19 @@
         <v>138</v>
       </c>
       <c r="E144">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F144">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G144" s="1">
-        <v>84.09999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="H144" s="1">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="I144" s="2">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J144">
         <v>0</v>
@@ -24626,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J145">
         <v>0</v>
@@ -24661,7 +24661,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="2">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="J146">
         <v>0</v>
@@ -24696,7 +24696,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -24719,19 +24719,19 @@
         <v>27</v>
       </c>
       <c r="E148">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F148">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G148" s="1">
-        <v>85.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H148" s="1">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="I148" s="2">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="J148">
         <v>0</v>
@@ -24751,19 +24751,19 @@
         <v>126</v>
       </c>
       <c r="E149">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G149" s="1">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H149" s="1">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I149" s="2">
-        <v>9.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>2.3</v>
       </c>
       <c r="I151" s="2">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -24868,7 +24868,7 @@
         <v>3.7</v>
       </c>
       <c r="I152" s="2">
-        <v>9.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J152">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>0</v>
       </c>
       <c r="I153" s="2">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J153">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         <v>2.9</v>
       </c>
       <c r="I154" s="2">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="J154">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>17.9</v>
       </c>
       <c r="I155" s="2">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="J155">
         <v>0</v>
@@ -25002,7 +25002,7 @@
         <v>17.9</v>
       </c>
       <c r="I156" s="2">
-        <v>9.1</v>
+        <v>7</v>
       </c>
       <c r="J156">
         <v>0</v>
@@ -25037,7 +25037,7 @@
         <v>22.2</v>
       </c>
       <c r="I157" s="2">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -25072,7 +25072,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I158" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J158">
         <v>0</v>
@@ -25107,7 +25107,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I159" s="2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -25142,7 +25142,7 @@
         <v>5</v>
       </c>
       <c r="I160" s="2">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -25177,7 +25177,7 @@
         <v>5.1</v>
       </c>
       <c r="I161" s="2">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -25212,7 +25212,7 @@
         <v>3.3</v>
       </c>
       <c r="I162" s="2">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J162">
         <v>0</v>
@@ -25244,7 +25244,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I163" s="2">
-        <v>9.6</v>
+        <v>8.1</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -25279,7 +25279,7 @@
         <v>16.7</v>
       </c>
       <c r="I164" s="2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J164">
         <v>0</v>
@@ -25314,7 +25314,7 @@
         <v>12.5</v>
       </c>
       <c r="I165" s="2">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="J165">
         <v>0</v>
@@ -25349,7 +25349,7 @@
         <v>11.5</v>
       </c>
       <c r="I166" s="2">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J166">
         <v>0</v>
@@ -25384,7 +25384,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -25416,7 +25416,7 @@
         <v>10.3</v>
       </c>
       <c r="I168" s="2">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="J168">
         <v>0</v>
@@ -25451,7 +25451,7 @@
         <v>25.9</v>
       </c>
       <c r="I169" s="2">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -25521,7 +25521,7 @@
         <v>33.3</v>
       </c>
       <c r="I171" s="2">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J171">
         <v>0</v>
@@ -25556,7 +25556,7 @@
         <v>20.6</v>
       </c>
       <c r="I172" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -25591,7 +25591,7 @@
         <v>7.5</v>
       </c>
       <c r="I173" s="2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="J173">
         <v>0</v>
@@ -25626,7 +25626,7 @@
         <v>17.9</v>
       </c>
       <c r="I174" s="2">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -25661,7 +25661,7 @@
         <v>30</v>
       </c>
       <c r="I175" s="2">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="J175">
         <v>0</v>
@@ -25696,7 +25696,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J176">
         <v>0</v>
@@ -25731,7 +25731,7 @@
         <v>20.9</v>
       </c>
       <c r="I177" s="2">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="J177">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>17.6</v>
       </c>
       <c r="I178" s="2">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -25798,7 +25798,7 @@
         <v>16.7</v>
       </c>
       <c r="I179" s="2">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J179">
         <v>0</v>
@@ -25833,7 +25833,7 @@
         <v>5.1</v>
       </c>
       <c r="I180" s="2">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -25868,7 +25868,7 @@
         <v>15.4</v>
       </c>
       <c r="I181" s="2">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -25938,7 +25938,7 @@
         <v>27</v>
       </c>
       <c r="I183" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J183">
         <v>0</v>
@@ -25973,7 +25973,7 @@
         <v>21.1</v>
       </c>
       <c r="I184" s="2">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -26008,7 +26008,7 @@
         <v>0</v>
       </c>
       <c r="I185" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -26043,7 +26043,7 @@
         <v>0</v>
       </c>
       <c r="I186" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -26075,7 +26075,7 @@
         <v>10.8</v>
       </c>
       <c r="I187" s="2">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3.6</v>
       </c>
       <c r="I188" s="2">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -26145,7 +26145,7 @@
         <v>21.2</v>
       </c>
       <c r="I189" s="2">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -26180,7 +26180,7 @@
         <v>3</v>
       </c>
       <c r="I190" s="2">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -26215,7 +26215,7 @@
         <v>3.8</v>
       </c>
       <c r="I191" s="2">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -26250,7 +26250,7 @@
         <v>15.4</v>
       </c>
       <c r="I192" s="2">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -26282,7 +26282,7 @@
         <v>9</v>
       </c>
       <c r="I193" s="2">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -26317,7 +26317,7 @@
         <v>6.7</v>
       </c>
       <c r="I194" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -26352,7 +26352,7 @@
         <v>0</v>
       </c>
       <c r="I195" s="2">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J195">
         <v>0</v>
@@ -26387,7 +26387,7 @@
         <v>4.8</v>
       </c>
       <c r="I196" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J196">
         <v>0</v>
@@ -26422,7 +26422,7 @@
         <v>12.5</v>
       </c>
       <c r="I197" s="2">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="J197">
         <v>0</v>
@@ -26454,7 +26454,7 @@
         <v>5.5</v>
       </c>
       <c r="I198" s="2">
-        <v>9.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J198">
         <v>0</v>
@@ -26524,7 +26524,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I200" s="2">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -26559,7 +26559,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -26591,7 +26591,7 @@
         <v>3.6</v>
       </c>
       <c r="I202" s="2">
-        <v>9.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -26626,7 +26626,7 @@
         <v>5.6</v>
       </c>
       <c r="I203" s="2">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -26661,7 +26661,7 @@
         <v>0</v>
       </c>
       <c r="I204" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -26696,7 +26696,7 @@
         <v>3.3</v>
       </c>
       <c r="I205" s="2">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -26731,7 +26731,7 @@
         <v>4</v>
       </c>
       <c r="I206" s="2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J206">
         <v>0</v>
@@ -26763,7 +26763,7 @@
         <v>3.3</v>
       </c>
       <c r="I207" s="2">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J207">
         <v>0</v>
@@ -26798,7 +26798,7 @@
         <v>55.6</v>
       </c>
       <c r="I208" s="2">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="J208">
         <v>0</v>
@@ -26833,7 +26833,7 @@
         <v>46.2</v>
       </c>
       <c r="I209" s="2">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J209">
         <v>0</v>
@@ -26903,7 +26903,7 @@
         <v>46.2</v>
       </c>
       <c r="I211" s="2">
-        <v>7.7</v>
+        <v>5.6</v>
       </c>
       <c r="J211">
         <v>0</v>
@@ -26938,7 +26938,7 @@
         <v>47.4</v>
       </c>
       <c r="I212" s="2">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="J212">
         <v>0</v>
@@ -26970,7 +26970,7 @@
         <v>59.3</v>
       </c>
       <c r="I213" s="2">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
       <c r="J213">
         <v>0</v>
@@ -27005,7 +27005,7 @@
         <v>5.9</v>
       </c>
       <c r="I214" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J214">
         <v>0</v>
@@ -27040,7 +27040,7 @@
         <v>2.5</v>
       </c>
       <c r="I215" s="2">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J215">
         <v>0</v>
@@ -27075,7 +27075,7 @@
         <v>5.1</v>
       </c>
       <c r="I216" s="2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J216">
         <v>0</v>
@@ -27110,7 +27110,7 @@
         <v>3.3</v>
       </c>
       <c r="I217" s="2">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -27180,7 +27180,7 @@
         <v>4</v>
       </c>
       <c r="I219" s="2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J219">
         <v>0</v>
@@ -27212,7 +27212,7 @@
         <v>4</v>
       </c>
       <c r="I220" s="2">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -27247,7 +27247,7 @@
         <v>7.5</v>
       </c>
       <c r="I221" s="2">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J221">
         <v>0</v>
@@ -27279,7 +27279,7 @@
         <v>7.5</v>
       </c>
       <c r="I222" s="2">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J222">
         <v>0</v>
@@ -27314,7 +27314,7 @@
         <v>27.8</v>
       </c>
       <c r="I223" s="2">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="J223">
         <v>0</v>
@@ -27346,7 +27346,7 @@
         <v>27.8</v>
       </c>
       <c r="I224" s="2">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="J224">
         <v>0</v>
@@ -27381,7 +27381,7 @@
         <v>3.8</v>
       </c>
       <c r="I225" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J225">
         <v>0</v>
@@ -27413,7 +27413,7 @@
         <v>3.8</v>
       </c>
       <c r="I226" s="2">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J226">
         <v>0</v>
@@ -27448,7 +27448,7 @@
         <v>66.7</v>
       </c>
       <c r="I227" s="2">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="J227">
         <v>0</v>
@@ -27483,7 +27483,7 @@
         <v>48.6</v>
       </c>
       <c r="I228" s="2">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="J228">
         <v>0</v>
@@ -27518,7 +27518,7 @@
         <v>31.6</v>
       </c>
       <c r="I229" s="2">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="J229">
         <v>0</v>
@@ -27553,7 +27553,7 @@
         <v>14.3</v>
       </c>
       <c r="I230" s="2">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J230">
         <v>0</v>
@@ -27588,7 +27588,7 @@
         <v>7.1</v>
       </c>
       <c r="I231" s="2">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="J231">
         <v>0</v>
@@ -27623,7 +27623,7 @@
         <v>7.1</v>
       </c>
       <c r="I232" s="2">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="J232">
         <v>0</v>
@@ -27655,7 +27655,7 @@
         <v>31.8</v>
       </c>
       <c r="I233" s="2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="J233">
         <v>0</v>
@@ -27690,7 +27690,7 @@
         <v>12</v>
       </c>
       <c r="I234" s="2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J234">
         <v>0</v>
@@ -27725,7 +27725,7 @@
         <v>11.8</v>
       </c>
       <c r="I235" s="2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J235">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>11.9</v>
       </c>
       <c r="I236" s="2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="J236">
         <v>0</v>
@@ -27792,7 +27792,7 @@
         <v>0</v>
       </c>
       <c r="I237" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J237">
         <v>0</v>
@@ -27827,7 +27827,7 @@
         <v>0</v>
       </c>
       <c r="I238" s="2">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J238">
         <v>0</v>
@@ -27859,7 +27859,7 @@
         <v>0</v>
       </c>
       <c r="I239" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J239">
         <v>0</v>
@@ -27894,7 +27894,7 @@
         <v>15.4</v>
       </c>
       <c r="I240" s="2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J240">
         <v>0</v>
@@ -27926,7 +27926,7 @@
         <v>15.4</v>
       </c>
       <c r="I241" s="2">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J241">
         <v>0</v>
@@ -27996,7 +27996,7 @@
         <v>17.9</v>
       </c>
       <c r="I243" s="2">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="J243">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>21.6</v>
       </c>
       <c r="I244" s="2">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -28066,7 +28066,7 @@
         <v>15.8</v>
       </c>
       <c r="I245" s="2">
-        <v>9.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -28101,7 +28101,7 @@
         <v>3.8</v>
       </c>
       <c r="I246" s="2">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -28133,7 +28133,7 @@
         <v>13.8</v>
       </c>
       <c r="I247" s="2">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -28168,7 +28168,7 @@
         <v>14.8</v>
       </c>
       <c r="I248" s="2">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="J248">
         <v>0</v>
@@ -28203,7 +28203,7 @@
         <v>16.7</v>
       </c>
       <c r="I249" s="2">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>7.7</v>
       </c>
       <c r="I250" s="2">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -28273,7 +28273,7 @@
         <v>3.3</v>
       </c>
       <c r="I251" s="2">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J251">
         <v>0</v>
@@ -28308,7 +28308,7 @@
         <v>4</v>
       </c>
       <c r="I252" s="2">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J252">
         <v>0</v>
@@ -28343,7 +28343,7 @@
         <v>0</v>
       </c>
       <c r="I253" s="2">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="J253">
         <v>0</v>
@@ -28375,7 +28375,7 @@
         <v>7.2</v>
       </c>
       <c r="I254" s="2">
-        <v>9.6</v>
+        <v>7.7</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -28410,7 +28410,7 @@
         <v>12.8</v>
       </c>
       <c r="I255" s="2">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="J255">
         <v>0</v>
@@ -28445,7 +28445,7 @@
         <v>20.5</v>
       </c>
       <c r="I256" s="2">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -28480,7 +28480,7 @@
         <v>16.2</v>
       </c>
       <c r="I257" s="2">
-        <v>9.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="J257">
         <v>0</v>
@@ -28515,7 +28515,7 @@
         <v>15.8</v>
       </c>
       <c r="I258" s="2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J258">
         <v>0</v>
@@ -28550,7 +28550,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I259" s="2">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="J259">
         <v>0</v>
@@ -28585,7 +28585,7 @@
         <v>0</v>
       </c>
       <c r="I260" s="2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -28617,7 +28617,7 @@
         <v>12.8</v>
       </c>
       <c r="I261" s="2">
-        <v>9.4</v>
+        <v>6.9</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -28652,7 +28652,7 @@
         <v>30.6</v>
       </c>
       <c r="I262" s="2">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -28687,7 +28687,7 @@
         <v>0</v>
       </c>
       <c r="I263" s="2">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -28722,7 +28722,7 @@
         <v>0</v>
       </c>
       <c r="I264" s="2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="J264">
         <v>0</v>
@@ -28757,7 +28757,7 @@
         <v>0</v>
       </c>
       <c r="I265" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -28792,7 +28792,7 @@
         <v>0</v>
       </c>
       <c r="I266" s="2">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -28824,7 +28824,7 @@
         <v>7.6</v>
       </c>
       <c r="I267" s="2">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -28859,7 +28859,7 @@
         <v>0</v>
       </c>
       <c r="I268" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J268">
         <v>0</v>
@@ -28894,7 +28894,7 @@
         <v>0</v>
       </c>
       <c r="I269" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J269">
         <v>0</v>
@@ -28929,7 +28929,7 @@
         <v>0</v>
       </c>
       <c r="I270" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J270">
         <v>0</v>
@@ -28964,7 +28964,7 @@
         <v>0</v>
       </c>
       <c r="I271" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J271">
         <v>0</v>
@@ -28999,7 +28999,7 @@
         <v>0</v>
       </c>
       <c r="I272" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J272">
         <v>0</v>
@@ -29031,7 +29031,7 @@
         <v>0</v>
       </c>
       <c r="I273" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J273">
         <v>0</v>
